--- a/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
+++ b/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
@@ -63,6 +63,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'ONR 5'!$B$2:$V$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'ONR 5'!$4:$6,'ONR 5'!$B:$C</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Résultats synthèse'!$B$2:$M$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Cibles métier'!$B$2:$V$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Cibles métier'!$4:$6,'Cibles métier'!$B:$C</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1" calcMode="auto" forceFullCalc="1"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -456,10 +458,11 @@
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Utilisateur invité</author>
     <author>Utilisateur</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{EB80FB45-ED39-4EE0-B694-4C8CBE5F9519}">
       <text>
         <r>
           <rPr>
@@ -467,47 +470,47 @@
             <color rgb="FF000000"/>
             <rFont val="Helv"/>
           </rPr>
-          <t>Parce que les services numériques peuvent être sources d’exclusion sociale, d’individualisation et d’obsolescence matérielle et logicielle, nous nous engageons à développer des offres de services accessibles pour tous, inclusives et durables.</t>
+          <t>Parce que le numérique est un acteur majeur d’émissions de Gaz à Effet de Serre, d’épuisement des ressources et d’affaissement de la biodiversité, participant activement au changement climatique, nous nous engageons à optimiser les outils numériques pour limiter leurs impacts et consommations.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+    <comment ref="D5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <t>Décrire les opportunités et les menaces associées à cette cible pour l’organisation : enjeux économiques, sociaux, environnementaux, réglementaires ou opérationnels.</t>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+    <comment ref="E5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <t>Évaluer l’importance de la cible pour l’organisation.
 0 : non applicable ; 1 : peu importante ; 2 : importante ; 3 : très importante.
 Une importance de 0 classe la cible comme non applicable, même sans note de performance.</t>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="F5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <t>Évaluer la situation actuelle à partir d’éléments documentés.
 1 : pas du tout atteinte ; 2 : atteinte en partie ; 3 : en voie d’être atteinte ; 4 : atteinte.
 Laisser vide si la cible n’est pas évaluée ou n’est pas applicable.</t>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+    <comment ref="G5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <t>Justifier la note de performance avec les mesures déjà en place, les résultats observés, les indicateurs disponibles et les sources datées. Distinguer les actions réalisées des actions seulement prévues.</t>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
+    <comment ref="I5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <t>Décrire les forces et les faiblesses internes : compétences, moyens humains, financiers et techniques, et partenaires disponibles pour agir sur la cible.</t>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+    <comment ref="J5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <t>Calcul automatique à partir de l’importance et de la performance, selon la matrice de l’onglet Priorisation.
 Importance 0 : non applicable. Sinon, deux notes valides sont nécessaires.
 Consulter Résultats détaillés et Résultats synthèse pour les résultats consolidés.</t>
       </text>
     </comment>
-    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000A000000}">
+    <comment ref="V5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
       <text>
         <t>Proposer des actions contribuant à l’atteinte de la cible. Préciser, si possible, un responsable, une échéance et un résultat attendu.
 Une proposition renseignée ne signifie pas que l’action a été validée ou réalisée.</t>
@@ -27544,7 +27547,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Version « Collectivités territoriales » co-éditée par l'Institut du Numérique Responsable (INR) et LaNum Pays Basque, dans le cadre du projet NÉONUM, d'après la GPC-ONR de l'INR. Les cibles métier (feuille « Cibles métier ») ne sont pas reprises dans les feuilles de résultats.</a:t>
+            <a:t>Version « Collectivités territoriales » proposée par LaNum Pays Basque pour les publics qu'elle accompagne dans le projet européen NÉONUM, et co-éditée avec l'INR, d'après la GPC-ONR. Les cibles métier (feuille « Cibles métier ») ne sont pas reprises dans les feuilles de résultats.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -27569,76 +27572,22 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="57e11928-67da-43e8-bf4d-cd8442aff663"/>
+        <xdr:cNvPr id="3" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="officialLogoINR20261007"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="bandeauCoedition"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>708025</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>791604</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -30094,76 +30043,22 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="9bd40fee-3145-48bd-b262-f6546a52b031"/>
+        <xdr:cNvPr id="3" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="officialLogoINR20261007"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="bandeauCoedition"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>708025</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>791604</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -30378,75 +30273,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="1a59bba7-19d6-49ba-821e-248463433195"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd0f8b23f0a7a4abc"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30524,75 +30365,21 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>498475</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="966d4c1d-e16d-4837-80a0-1444665fbe1b"/>
+        <xdr:cNvPr id="3" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4133cfea2974438b"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>135109</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>875913</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30615,70 +30402,16 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="ad6eca7f-2512-4327-a38b-5fd4332cec7e"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R88a94acdc061494d"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>708025</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>791604</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30696,75 +30429,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>7156450</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="253580d9-a043-4736-af34-c3bf36bb7bd2"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1641b25ecc3940ba"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>5907259</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>8419713</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30782,75 +30461,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="5ba0819c-73d0-49f8-9222-16d663e15aa0"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R34c26571c7014388"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1182859</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30868,75 +30493,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="1a59bba7-19d6-49ba-821e-248463433195"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd0f8b23f0a7a4abc"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30954,75 +30525,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="1b76089d-f7b4-461a-bc2a-0b97e5c05474"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf6467eda94464bb5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -31040,75 +30557,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="9b925086-4e52-4a38-8282-40c16f0a476c"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5e03a6a319674c4e"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -31126,75 +30589,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="67e8ff89-b205-4e84-b992-af3db7ffe8a1"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R009525bc9d6e404c"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -31212,75 +30621,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>212725</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="e81248c7-2f0d-494e-9b17-442281be75de"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8c85558606f24767"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>468484</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>723513</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -42545,7 +41900,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor theme="9"/>
+    <x:tabColor theme="4"/>
     <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
   <x:sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="12"/>
@@ -42561,8 +41916,8 @@
     <x:col min="9" max="9" width="32" style="871" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="23" style="871" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="5.6640625" style="866" hidden="1" customWidth="1"/>
-    <x:col min="12" max="12" width="5.6640625" style="866" hidden="1" customWidth="1"/>
-    <x:col min="13" max="13" width="5.6640625" style="866" hidden="1" customWidth="1"/>
+    <x:col min="12" max="12" width="16.6640625" style="866" hidden="1" customWidth="1"/>
+    <x:col min="13" max="13" width="17.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="14" max="14" width="5.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="15" max="15" width="5.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="16" max="16" width="5.6640625" style="866" hidden="1" customWidth="1"/>
@@ -42572,8 +41927,8 @@
     <x:col min="20" max="20" width="5.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="21" max="21" width="5.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="22" max="22" width="46" style="871" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="42.6640625" style="871" hidden="1" customWidth="1"/>
-    <x:col min="24" max="24" width="42.6640625" style="866" hidden="1" customWidth="1"/>
+    <x:col min="23" max="23" width="68.6640625" style="871" hidden="1" customWidth="1"/>
+    <x:col min="24" max="24" width="78.5" style="866" hidden="1" customWidth="1"/>
     <x:col min="25" max="25" width="10.6640625" style="866" customWidth="0" hidden="0"/>
     <x:col min="26" max="26" width="10.6640625" style="866" customWidth="0" hidden="0"/>
     <x:col min="27" max="27" width="10.6640625" style="866" customWidth="0" hidden="0"/>
@@ -42669,10 +42024,10 @@
     </x:row>
     <x:row r="4" ht="27" customHeight="1">
       <x:c r="A4" s="861"/>
-      <x:c r="B4" s="1822" t="str">
+      <x:c r="B4" s="1731" t="str">
         <x:v>Cibles à évaluer</x:v>
       </x:c>
-      <x:c r="C4" s="1823"/>
+      <x:c r="C4" s="1732"/>
       <x:c r="D4" s="1735" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Importance de la cible</x:t>
@@ -42715,8 +42070,8 @@
     </x:row>
     <x:row r="5" s="868" customFormat="1" ht="56" customHeight="1">
       <x:c r="A5" s="867"/>
-      <x:c r="B5" s="1824"/>
-      <x:c r="C5" s="1825"/>
+      <x:c r="B5" s="1733"/>
+      <x:c r="C5" s="1734"/>
       <x:c r="D5" s="1737" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Avantages possibles et risques</x:t>
@@ -42807,54 +42162,50 @@
           <x:t xml:space="preserve">Code priorité et compétences</x:t>
         </x:is>
       </x:c>
-      <x:c r="V5" s="1826" t="inlineStr">
+      <x:c r="V5" s="1751" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Actions proposées pour atteindre la cible</x:t>
         </x:is>
       </x:c>
-      <x:c r="W5" s="1753" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Adhérence</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="W5" s="1752"/>
       <x:c r="X5" s="1753"/>
     </x:row>
     <x:row r="6" s="875" customFormat="1" ht="34" customHeight="1">
       <x:c r="A6" s="874"/>
-      <x:c r="B6" s="1832" t="str">
+      <x:c r="B6" s="1764" t="str">
         <x:v>Renseigner les cellules jaunes pour les notes, puis les textes utiles. La priorité se calcule automatiquement. Faire défiler vers la droite pour proposer des actions.</x:v>
       </x:c>
-      <x:c r="C6" s="1833"/>
-      <x:c r="D6" s="1834"/>
-      <x:c r="E6" s="1834"/>
-      <x:c r="F6" s="1834"/>
-      <x:c r="G6" s="1834"/>
-      <x:c r="H6" s="1834"/>
-      <x:c r="I6" s="1834"/>
-      <x:c r="J6" s="1834"/>
-      <x:c r="K6" s="1834"/>
-      <x:c r="L6" s="1834"/>
-      <x:c r="M6" s="1834"/>
-      <x:c r="N6" s="1834"/>
-      <x:c r="O6" s="1834"/>
-      <x:c r="P6" s="1834"/>
-      <x:c r="Q6" s="1834"/>
-      <x:c r="R6" s="1834"/>
-      <x:c r="S6" s="1834"/>
-      <x:c r="T6" s="1834"/>
-      <x:c r="U6" s="1834"/>
-      <x:c r="V6" s="1835"/>
-      <x:c r="W6" s="1836"/>
-      <x:c r="X6" s="1129"/>
+      <x:c r="C6" s="1765"/>
+      <x:c r="D6" s="1766"/>
+      <x:c r="E6" s="1766"/>
+      <x:c r="F6" s="1766"/>
+      <x:c r="G6" s="1766"/>
+      <x:c r="H6" s="1766"/>
+      <x:c r="I6" s="1766"/>
+      <x:c r="J6" s="1766"/>
+      <x:c r="K6" s="1766"/>
+      <x:c r="L6" s="1766"/>
+      <x:c r="M6" s="1766"/>
+      <x:c r="N6" s="1766"/>
+      <x:c r="O6" s="1766"/>
+      <x:c r="P6" s="1766"/>
+      <x:c r="Q6" s="1766"/>
+      <x:c r="R6" s="1766"/>
+      <x:c r="S6" s="1766"/>
+      <x:c r="T6" s="1766"/>
+      <x:c r="U6" s="1766"/>
+      <x:c r="V6" s="1766"/>
+      <x:c r="W6" s="1765"/>
+      <x:c r="X6" s="1107"/>
     </x:row>
-    <x:row r="7" s="952" customFormat="1" ht="70" customHeight="1">
+    <x:row r="7" s="952" customFormat="1" ht="76" customHeight="1">
       <x:c r="A7" s="951"/>
-      <x:c r="B7" s="1804" t="inlineStr">
+      <x:c r="B7" s="1803" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="1796" t="inlineStr">
+      <x:c r="C7" s="1795" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Évaluer l'utilité environnementale et sociale des objets connectés et des projets de « territoire intelligent » avant de les déployer : capteurs, éclairage, vidéoprotection, plateformes de données.</x:t>
         </x:is>
@@ -42864,55 +42215,55 @@
       <x:c r="F7" s="1802"/>
       <x:c r="G7" s="1798"/>
       <x:c r="H7" s="1802"/>
-      <x:c r="I7" s="1798"/>
+      <x:c r="I7" s="1799"/>
       <x:c r="J7" s="1806" t="str">
-        <x:f t="shared" ref="J7:J9" si="0">S7</x:f>
-      </x:c>
-      <x:c r="K7" s="1783" t="str">
+        <x:f>S7</x:f>
+      </x:c>
+      <x:c r="K7" s="1777" t="str">
         <x:f>IF(IF(ISNUMBER(E7),AND(E7&gt;=0,E7&lt;=3,MOD(E7,1)=0),FALSE),IF(E7=0,0,IF(IF(ISNUMBER(F7),AND(F7&gt;=1,F7&lt;=4,MOD(F7,1)=0),FALSE),E7*10+F7,"")),"")</x:f>
       </x:c>
-      <x:c r="L7" s="1783" t="b">
+      <x:c r="L7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),K7=31,FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M7" s="1783" t="b">
+      <x:c r="M7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=21,K7=32),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N7" s="1783" t="b">
+      <x:c r="N7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=22,K7=33),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O7" s="1783" t="b">
+      <x:c r="O7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=11,K7=12),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P7" s="1783" t="b">
+      <x:c r="P7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=23,K7=34),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q7" s="1783" t="b">
+      <x:c r="Q7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=13,K7=14,K7=24),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R7" s="1783" t="b">
+      <x:c r="R7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),K7=0,FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S7" s="1783" t="str">
-        <x:f>IF(ISNUMBER(T7),INDEX($L$5:$R$5,1,7-T7),"")</x:f>
-      </x:c>
-      <x:c r="T7" s="1783" t="str">
-        <x:f>IF(ISNUMBER(K7),IF(L7,6,IF(M7,5,IF(N7,4,IF(O7,3,IF(P7,2,IF(Q7,1,0)))))),"")</x:f>
-      </x:c>
-      <x:c r="U7" s="1783" t="str">
+      <x:c r="S7" s="1777" t="str">
+        <x:f t="shared" ref="S7:S12" si="0">IF(ISNUMBER(T7),INDEX($L$5:$R$5,1,7-T7),"")</x:f>
+      </x:c>
+      <x:c r="T7" s="1777" t="str">
+        <x:f t="shared" ref="T7:T12" si="1">IF(ISNUMBER(K7),IF(L7,6,IF(M7,5,IF(N7,4,IF(O7,3,IF(P7,2,IF(Q7,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U7" s="1790" t="str">
         <x:f>IF(AND(ISNUMBER(T7),ISNUMBER(H7)),IF(AND(H7&gt;=1,H7&lt;=4,MOD(H7,1)=0),T7*10+H7,""),"")</x:f>
       </x:c>
-      <x:c r="V7" s="1798"/>
-      <x:c r="W7" s="1123"/>
-      <x:c r="X7" s="1113"/>
+      <x:c r="V7" s="1799"/>
+      <x:c r="W7" s="1103"/>
+      <x:c r="X7" s="903"/>
     </x:row>
-    <x:row r="8" s="952" customFormat="1" ht="76" customHeight="1">
+    <x:row r="8" s="952" customFormat="1" ht="77" customHeight="1">
       <x:c r="A8" s="951"/>
       <x:c r="B8" s="1804" t="inlineStr">
         <x:is>
@@ -42921,7 +42272,7 @@
       </x:c>
       <x:c r="C8" s="1796" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Lutter contre l'illectronisme : financer la médiation numérique, garder un accueil physique et une solution non numérique pour chaque démarche.</x:t>
+          <x:t xml:space="preserve">Lutter contre l'illectronisme : soutenir la médiation numérique (conseillers numériques, espaces France Services, Aidants Connect), garder un accueil physique et une solution non numérique pour chaque démarche.</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" s="1798"/>
@@ -42929,53 +42280,53 @@
       <x:c r="F8" s="1802"/>
       <x:c r="G8" s="1798"/>
       <x:c r="H8" s="1802"/>
-      <x:c r="I8" s="1798"/>
+      <x:c r="I8" s="1799"/>
       <x:c r="J8" s="1806" t="str">
-        <x:f t="shared" si="0">S8</x:f>
-      </x:c>
-      <x:c r="K8" s="1783" t="str">
-        <x:f>IF(IF(ISNUMBER(E8),AND(E8&gt;=0,E8&lt;=3,MOD(E8,1)=0),FALSE),IF(E8=0,0,IF(IF(ISNUMBER(F8),AND(F8&gt;=1,F8&lt;=4,MOD(F8,1)=0),FALSE),E8*10+F8,"")),"")</x:f>
-      </x:c>
-      <x:c r="L8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),K8=31,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=21,K8=32),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=22,K8=33),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=11,K8=12),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=23,K8=34),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=13,K8=14,K8=24),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),K8=0,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S8" s="1783" t="str">
-        <x:f>IF(ISNUMBER(T8),INDEX($L$5:$R$5,1,7-T8),"")</x:f>
-      </x:c>
-      <x:c r="T8" s="1783" t="str">
-        <x:f>IF(ISNUMBER(K8),IF(L8,6,IF(M8,5,IF(N8,4,IF(O8,3,IF(P8,2,IF(Q8,1,0)))))),"")</x:f>
-      </x:c>
-      <x:c r="U8" s="1783" t="str">
-        <x:f>IF(AND(ISNUMBER(T8),ISNUMBER(H8)),IF(AND(H8&gt;=1,H8&lt;=4,MOD(H8,1)=0),T8*10+H8,""),"")</x:f>
-      </x:c>
-      <x:c r="V8" s="1798"/>
-      <x:c r="W8" s="1109"/>
-      <x:c r="X8" s="1108"/>
+        <x:f t="shared" ref="J8:J12" si="2">S8</x:f>
+      </x:c>
+      <x:c r="K8" s="1777" t="str">
+        <x:f t="shared" ref="K8:K12" si="3">IF(IF(ISNUMBER(E8),AND(E8&gt;=0,E8&lt;=3,MOD(E8,1)=0),FALSE),IF(E8=0,0,IF(IF(ISNUMBER(F8),AND(F8&gt;=1,F8&lt;=4,MOD(F8,1)=0),FALSE),E8*10+F8,"")),"")</x:f>
+      </x:c>
+      <x:c r="L8" s="1777" t="b">
+        <x:f t="shared" ref="L8:L12" si="4">IF(ISNUMBER(K8),K8=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="1777" t="b">
+        <x:f t="shared" ref="M8:M12" si="5">IF(ISNUMBER(K8),OR(K8=21,K8=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="1777" t="b">
+        <x:f t="shared" ref="N8:N12" si="6">IF(ISNUMBER(K8),OR(K8=22,K8=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="1777" t="b">
+        <x:f t="shared" ref="O8:O12" si="7">IF(ISNUMBER(K8),OR(K8=11,K8=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="1777" t="b">
+        <x:f t="shared" ref="P8:P12" si="8">IF(ISNUMBER(K8),OR(K8=23,K8=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="1777" t="b">
+        <x:f t="shared" ref="Q8:Q12" si="9">IF(ISNUMBER(K8),OR(K8=13,K8=14,K8=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="1777" t="b">
+        <x:f t="shared" ref="R8:R12" si="10">IF(ISNUMBER(K8),K8=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="1777" t="str">
+        <x:f t="shared" si="0">IF(ISNUMBER(T8),INDEX($L$5:$R$5,1,7-T8),"")</x:f>
+      </x:c>
+      <x:c r="T8" s="1777" t="str">
+        <x:f t="shared" si="1">IF(ISNUMBER(K8),IF(L8,6,IF(M8,5,IF(N8,4,IF(O8,3,IF(P8,2,IF(Q8,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U8" s="1790" t="str">
+        <x:f t="shared" ref="U8:U12" si="11">IF(AND(ISNUMBER(T8),ISNUMBER(H8)),IF(AND(H8&gt;=1,H8&lt;=4,MOD(H8,1)=0),T8*10+H8,""),"")</x:f>
+      </x:c>
+      <x:c r="V8" s="1799"/>
+      <x:c r="W8" s="1118"/>
+      <x:c r="X8" s="1117"/>
     </x:row>
     <x:row r="9" s="952" customFormat="1" ht="76" customHeight="1">
       <x:c r="A9" s="951"/>
@@ -42994,53 +42345,53 @@
       <x:c r="F9" s="1802"/>
       <x:c r="G9" s="1798"/>
       <x:c r="H9" s="1802"/>
-      <x:c r="I9" s="1798"/>
+      <x:c r="I9" s="1799"/>
       <x:c r="J9" s="1806" t="str">
-        <x:f t="shared" si="0">S9</x:f>
+        <x:f t="shared" si="2">S9</x:f>
       </x:c>
       <x:c r="K9" s="1783" t="str">
-        <x:f>IF(IF(ISNUMBER(E9),AND(E9&gt;=0,E9&lt;=3,MOD(E9,1)=0),FALSE),IF(E9=0,0,IF(IF(ISNUMBER(F9),AND(F9&gt;=1,F9&lt;=4,MOD(F9,1)=0),FALSE),E9*10+F9,"")),"")</x:f>
+        <x:f t="shared" si="3">IF(IF(ISNUMBER(E9),AND(E9&gt;=0,E9&lt;=3,MOD(E9,1)=0),FALSE),IF(E9=0,0,IF(IF(ISNUMBER(F9),AND(F9&gt;=1,F9&lt;=4,MOD(F9,1)=0),FALSE),E9*10+F9,"")),"")</x:f>
       </x:c>
       <x:c r="L9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),K9=31,FALSE)</x:f>
+        <x:f t="shared" si="4">IF(ISNUMBER(K9),K9=31,FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=21,K9=32),FALSE)</x:f>
+        <x:f t="shared" si="5">IF(ISNUMBER(K9),OR(K9=21,K9=32),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=22,K9=33),FALSE)</x:f>
+        <x:f t="shared" si="6">IF(ISNUMBER(K9),OR(K9=22,K9=33),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=11,K9=12),FALSE)</x:f>
+        <x:f t="shared" si="7">IF(ISNUMBER(K9),OR(K9=11,K9=12),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=23,K9=34),FALSE)</x:f>
+        <x:f t="shared" si="8">IF(ISNUMBER(K9),OR(K9=23,K9=34),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=13,K9=14,K9=24),FALSE)</x:f>
+        <x:f t="shared" si="9">IF(ISNUMBER(K9),OR(K9=13,K9=14,K9=24),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),K9=0,FALSE)</x:f>
+        <x:f t="shared" si="10">IF(ISNUMBER(K9),K9=0,FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S9" s="1783" t="str">
-        <x:f>IF(ISNUMBER(T9),INDEX($L$5:$R$5,1,7-T9),"")</x:f>
+        <x:f t="shared" si="0">IF(ISNUMBER(T9),INDEX($L$5:$R$5,1,7-T9),"")</x:f>
       </x:c>
       <x:c r="T9" s="1783" t="str">
-        <x:f>IF(ISNUMBER(K9),IF(L9,6,IF(M9,5,IF(N9,4,IF(O9,3,IF(P9,2,IF(Q9,1,0)))))),"")</x:f>
+        <x:f t="shared" si="1">IF(ISNUMBER(K9),IF(L9,6,IF(M9,5,IF(N9,4,IF(O9,3,IF(P9,2,IF(Q9,1,0)))))),"")</x:f>
       </x:c>
       <x:c r="U9" s="1783" t="str">
-        <x:f>IF(AND(ISNUMBER(T9),ISNUMBER(H9)),IF(AND(H9&gt;=1,H9&lt;=4,MOD(H9,1)=0),T9*10+H9,""),"")</x:f>
-      </x:c>
-      <x:c r="V9" s="1798"/>
-      <x:c r="W9" s="1122"/>
-      <x:c r="X9" s="1114"/>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(T9),ISNUMBER(H9)),IF(AND(H9&gt;=1,H9&lt;=4,MOD(H9,1)=0),T9*10+H9,""),"")</x:f>
+      </x:c>
+      <x:c r="V9" s="1799"/>
+      <x:c r="W9" s="1104"/>
+      <x:c r="X9" s="1116"/>
     </x:row>
     <x:row r="10" s="952" customFormat="1" ht="70" customHeight="1">
       <x:c r="A10" s="951"/>
@@ -43059,64 +42410,64 @@
       <x:c r="F10" s="1802"/>
       <x:c r="G10" s="1798"/>
       <x:c r="H10" s="1802"/>
-      <x:c r="I10" s="1798"/>
+      <x:c r="I10" s="1799"/>
       <x:c r="J10" s="1806" t="str">
-        <x:f>S10</x:f>
-      </x:c>
-      <x:c r="K10" s="1777" t="str">
-        <x:f>IF(IF(ISNUMBER(E10),AND(E10&gt;=0,E10&lt;=3,MOD(E10,1)=0),FALSE),IF(E10=0,0,IF(IF(ISNUMBER(F10),AND(F10&gt;=1,F10&lt;=4,MOD(F10,1)=0),FALSE),E10*10+F10,"")),"")</x:f>
-      </x:c>
-      <x:c r="L10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),K10=31,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=21,K10=32),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=22,K10=33),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=11,K10=12),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=23,K10=34),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=13,K10=14,K10=24),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),K10=0,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S10" s="1777" t="str">
-        <x:f>IF(ISNUMBER(T10),INDEX($L$5:$R$5,1,7-T10),"")</x:f>
-      </x:c>
-      <x:c r="T10" s="1777" t="str">
-        <x:f>IF(ISNUMBER(K10),IF(L10,6,IF(M10,5,IF(N10,4,IF(O10,3,IF(P10,2,IF(Q10,1,0)))))),"")</x:f>
+        <x:f t="shared" si="2">S10</x:f>
+      </x:c>
+      <x:c r="K10" s="1786" t="str">
+        <x:f t="shared" si="3">IF(IF(ISNUMBER(E10),AND(E10&gt;=0,E10&lt;=3,MOD(E10,1)=0),FALSE),IF(E10=0,0,IF(IF(ISNUMBER(F10),AND(F10&gt;=1,F10&lt;=4,MOD(F10,1)=0),FALSE),E10*10+F10,"")),"")</x:f>
+      </x:c>
+      <x:c r="L10" s="1786" t="b">
+        <x:f t="shared" si="4">IF(ISNUMBER(K10),K10=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="1786" t="b">
+        <x:f t="shared" si="5">IF(ISNUMBER(K10),OR(K10=21,K10=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="1786" t="b">
+        <x:f t="shared" si="6">IF(ISNUMBER(K10),OR(K10=22,K10=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="1786" t="b">
+        <x:f t="shared" si="7">IF(ISNUMBER(K10),OR(K10=11,K10=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="1786" t="b">
+        <x:f t="shared" si="8">IF(ISNUMBER(K10),OR(K10=23,K10=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="1786" t="b">
+        <x:f t="shared" si="9">IF(ISNUMBER(K10),OR(K10=13,K10=14,K10=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R10" s="1786" t="b">
+        <x:f t="shared" si="10">IF(ISNUMBER(K10),K10=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" s="1786" t="str">
+        <x:f t="shared" si="0">IF(ISNUMBER(T10),INDEX($L$5:$R$5,1,7-T10),"")</x:f>
+      </x:c>
+      <x:c r="T10" s="1786" t="str">
+        <x:f t="shared" si="1">IF(ISNUMBER(K10),IF(L10,6,IF(M10,5,IF(N10,4,IF(O10,3,IF(P10,2,IF(Q10,1,0)))))),"")</x:f>
       </x:c>
       <x:c r="U10" s="1790" t="str">
-        <x:f>IF(AND(ISNUMBER(T10),ISNUMBER(H10)),IF(AND(H10&gt;=1,H10&lt;=4,MOD(H10,1)=0),T10*10+H10,""),"")</x:f>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(T10),ISNUMBER(H10)),IF(AND(H10&gt;=1,H10&lt;=4,MOD(H10,1)=0),T10*10+H10,""),"")</x:f>
       </x:c>
       <x:c r="V10" s="1798"/>
-      <x:c r="W10" s="1109"/>
-      <x:c r="X10" s="1108"/>
+      <x:c r="W10" s="1105"/>
+      <x:c r="X10" s="903"/>
     </x:row>
-    <x:row r="11" s="952" customFormat="1" ht="70" customHeight="1">
+    <x:row r="11" s="952" customFormat="1" ht="100" customHeight="1">
       <x:c r="A11" s="951"/>
-      <x:c r="B11" s="1804" t="inlineStr">
+      <x:c r="B11" s="1805" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C.5</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="1796" t="inlineStr">
+      <x:c r="C11" s="1797" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Former les élus et les agents au numérique responsable, et l'inscrire dans la stratégie numérique responsable prévue par la loi REEN.</x:t>
+          <x:t xml:space="preserve">Adopter et faire vivre la stratégie numérique responsable prévue par la loi REEN : obligatoire pour les communes et intercommunalités de plus de 50 000 habitants, recommandée pour les autres. Fixer des objectifs de réduction de l'empreinte du numérique, suivre leur mise en œuvre et former les élus et les agents.</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" s="1798"/>
@@ -43124,98 +42475,289 @@
       <x:c r="F11" s="1802"/>
       <x:c r="G11" s="1798"/>
       <x:c r="H11" s="1802"/>
-      <x:c r="I11" s="1798"/>
-      <x:c r="J11" s="1806" t="n">
-        <x:f>S11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="1777" t="str">
-        <x:f>IF(IF(ISNUMBER(E11),AND(E11&gt;=0,E11&lt;=3,MOD(E11,1)=0),FALSE),IF(E11=0,0,IF(IF(ISNUMBER(F11),AND(F11&gt;=1,F11&lt;=4,MOD(F11,1)=0),FALSE),E11*10+F11,"")),"")</x:f>
-      </x:c>
-      <x:c r="L11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),K11=31,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=21,K11=32),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=22,K11=33),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=11,K11=12),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=23,K11=34),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=13,K11=14,K11=24),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),K11=0,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S11" s="1777" t="str">
-        <x:f>IF(ISNUMBER(T11),INDEX($L$5:$R$5,1,7-T11),"")</x:f>
-      </x:c>
-      <x:c r="T11" s="1777" t="str">
-        <x:f>IF(ISNUMBER(K11),IF(L11,6,IF(M11,5,IF(N11,4,IF(O11,3,IF(P11,2,IF(Q11,1,0)))))),"")</x:f>
+      <x:c r="I11" s="1799"/>
+      <x:c r="J11" s="1806" t="str">
+        <x:f t="shared" si="2">S11</x:f>
+      </x:c>
+      <x:c r="K11" s="1786" t="str">
+        <x:f t="shared" si="3">IF(IF(ISNUMBER(E11),AND(E11&gt;=0,E11&lt;=3,MOD(E11,1)=0),FALSE),IF(E11=0,0,IF(IF(ISNUMBER(F11),AND(F11&gt;=1,F11&lt;=4,MOD(F11,1)=0),FALSE),E11*10+F11,"")),"")</x:f>
+      </x:c>
+      <x:c r="L11" s="1786" t="b">
+        <x:f t="shared" si="4">IF(ISNUMBER(K11),K11=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="1786" t="b">
+        <x:f t="shared" si="5">IF(ISNUMBER(K11),OR(K11=21,K11=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" s="1786" t="b">
+        <x:f t="shared" si="6">IF(ISNUMBER(K11),OR(K11=22,K11=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="1786" t="b">
+        <x:f t="shared" si="7">IF(ISNUMBER(K11),OR(K11=11,K11=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="1786" t="b">
+        <x:f t="shared" si="8">IF(ISNUMBER(K11),OR(K11=23,K11=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="1786" t="b">
+        <x:f t="shared" si="9">IF(ISNUMBER(K11),OR(K11=13,K11=14,K11=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R11" s="1786" t="b">
+        <x:f t="shared" si="10">IF(ISNUMBER(K11),K11=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="1786" t="str">
+        <x:f t="shared" si="0">IF(ISNUMBER(T11),INDEX($L$5:$R$5,1,7-T11),"")</x:f>
+      </x:c>
+      <x:c r="T11" s="1786" t="str">
+        <x:f t="shared" si="1">IF(ISNUMBER(K11),IF(L11,6,IF(M11,5,IF(N11,4,IF(O11,3,IF(P11,2,IF(Q11,1,0)))))),"")</x:f>
       </x:c>
       <x:c r="U11" s="1790" t="str">
-        <x:f>IF(AND(ISNUMBER(T11),ISNUMBER(H11)),IF(AND(H11&gt;=1,H11&lt;=4,MOD(H11,1)=0),T11*10+H11,""),"")</x:f>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(T11),ISNUMBER(H11)),IF(AND(H11&gt;=1,H11&lt;=4,MOD(H11,1)=0),T11*10+H11,""),"")</x:f>
       </x:c>
       <x:c r="V11" s="1798"/>
-      <x:c r="W11" s="1109"/>
-      <x:c r="X11" s="1108"/>
+      <x:c r="W11" s="1119"/>
+      <x:c r="X11" s="1114"/>
     </x:row>
-    <x:row r="12">
-      <x:c r="V12" s="893"/>
+    <x:row r="12" s="953" customFormat="1" ht="100" customHeight="1">
+      <x:c r="A12" s="951"/>
+      <x:c r="B12" s="1804" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">C.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="1797" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rendre accessibles les contenus que la collectivité produit chaque jour : documents, publications sur les réseaux sociaux, vidéos sous-titrées, textes en facile à lire et à comprendre (FALC). Former les agents qui les produisent et offrir un accueil accessible, y compris aux personnes sourdes et malentendantes.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="1798"/>
+      <x:c r="E12" s="1802"/>
+      <x:c r="F12" s="1802"/>
+      <x:c r="G12" s="1798"/>
+      <x:c r="H12" s="1802"/>
+      <x:c r="I12" s="1799"/>
+      <x:c r="J12" s="1806" t="str">
+        <x:f t="shared" si="2">S12</x:f>
+      </x:c>
+      <x:c r="K12" s="1786" t="str">
+        <x:f t="shared" si="3">IF(IF(ISNUMBER(E12),AND(E12&gt;=0,E12&lt;=3,MOD(E12,1)=0),FALSE),IF(E12=0,0,IF(IF(ISNUMBER(F12),AND(F12&gt;=1,F12&lt;=4,MOD(F12,1)=0),FALSE),E12*10+F12,"")),"")</x:f>
+      </x:c>
+      <x:c r="L12" s="1786" t="b">
+        <x:f t="shared" si="4">IF(ISNUMBER(K12),K12=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="1786" t="b">
+        <x:f t="shared" si="5">IF(ISNUMBER(K12),OR(K12=21,K12=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="1786" t="b">
+        <x:f t="shared" si="6">IF(ISNUMBER(K12),OR(K12=22,K12=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="1786" t="b">
+        <x:f t="shared" si="7">IF(ISNUMBER(K12),OR(K12=11,K12=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="1786" t="b">
+        <x:f t="shared" si="8">IF(ISNUMBER(K12),OR(K12=23,K12=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="1786" t="b">
+        <x:f t="shared" si="9">IF(ISNUMBER(K12),OR(K12=13,K12=14,K12=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R12" s="1786" t="b">
+        <x:f t="shared" si="10">IF(ISNUMBER(K12),K12=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" s="1786" t="str">
+        <x:f t="shared" si="0">IF(ISNUMBER(T12),INDEX($L$5:$R$5,1,7-T12),"")</x:f>
+      </x:c>
+      <x:c r="T12" s="1786" t="str">
+        <x:f t="shared" si="1">IF(ISNUMBER(K12),IF(L12,6,IF(M12,5,IF(N12,4,IF(O12,3,IF(P12,2,IF(Q12,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U12" s="1790" t="str">
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(T12),ISNUMBER(H12)),IF(AND(H12&gt;=1,H12&lt;=4,MOD(H12,1)=0),T12*10+H12,""),"")</x:f>
+      </x:c>
+      <x:c r="V12" s="1798"/>
+      <x:c r="W12" s="1120"/>
+      <x:c r="X12" s="1114"/>
+    </x:row>
+    <x:row r="13" ht="88.5" customHeight="1">
+      <x:c r="B13" s="1804" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">C.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="1797" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Recenser les usages de l'intelligence artificielle dans la collectivité, y compris l'IA générative utilisée par les agents. Les encadrer par une charte, vérifier les obligations du règlement européen sur l'IA, et informer les habitants des usages qui les concernent.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="1798"/>
+      <x:c r="E13" s="1802"/>
+      <x:c r="F13" s="1802"/>
+      <x:c r="G13" s="1798"/>
+      <x:c r="H13" s="1802"/>
+      <x:c r="I13" s="1799"/>
+      <x:c r="J13" s="1806" t="str">
+        <x:f t="shared" ref="J13" si="12">S13</x:f>
+      </x:c>
+      <x:c r="K13" s="1786" t="str">
+        <x:f t="shared" ref="K13" si="13">IF(IF(ISNUMBER(E13),AND(E13&gt;=0,E13&lt;=3,MOD(E13,1)=0),FALSE),IF(E13=0,0,IF(IF(ISNUMBER(F13),AND(F13&gt;=1,F13&lt;=4,MOD(F13,1)=0),FALSE),E13*10+F13,"")),"")</x:f>
+      </x:c>
+      <x:c r="L13" s="1786" t="b">
+        <x:f t="shared" ref="L13" si="14">IF(ISNUMBER(K13),K13=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="1786" t="b">
+        <x:f t="shared" ref="M13" si="15">IF(ISNUMBER(K13),OR(K13=21,K13=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="1786" t="b">
+        <x:f t="shared" ref="N13" si="16">IF(ISNUMBER(K13),OR(K13=22,K13=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="1786" t="b">
+        <x:f t="shared" ref="O13" si="17">IF(ISNUMBER(K13),OR(K13=11,K13=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="1786" t="b">
+        <x:f t="shared" ref="P13" si="18">IF(ISNUMBER(K13),OR(K13=23,K13=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="1786" t="b">
+        <x:f t="shared" ref="Q13" si="19">IF(ISNUMBER(K13),OR(K13=13,K13=14,K13=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="1786" t="b">
+        <x:f t="shared" ref="R13" si="20">IF(ISNUMBER(K13),K13=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="1786" t="str">
+        <x:f t="shared" ref="S13" si="21">IF(ISNUMBER(T13),INDEX($L$5:$R$5,1,7-T13),"")</x:f>
+      </x:c>
+      <x:c r="T13" s="1786" t="str">
+        <x:f t="shared" ref="T13" si="22">IF(ISNUMBER(K13),IF(L13,6,IF(M13,5,IF(N13,4,IF(O13,3,IF(P13,2,IF(Q13,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U13" s="1790" t="str">
+        <x:f t="shared" ref="U13" si="23">IF(AND(ISNUMBER(T13),ISNUMBER(H13)),IF(AND(H13&gt;=1,H13&lt;=4,MOD(H13,1)=0),T13*10+H13,""),"")</x:f>
+      </x:c>
+      <x:c r="V13" s="1798"/>
+      <x:c r="W13" s="1121"/>
+      <x:c r="X13" s="1114"/>
+    </x:row>
+    <x:row r="14" ht="88.5" customHeight="1">
+      <x:c r="B14" s="1804" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">C.8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="1797" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ouvrir la décision publique avec des outils de participation citoyenne (civic tech) : consultations, budgets participatifs, signalements. Choisir des outils ouverts, accessibles et sobres, comme les logiciels libres, et les compléter par des temps d'échange en présentiel.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="1798"/>
+      <x:c r="E14" s="1802"/>
+      <x:c r="F14" s="1802"/>
+      <x:c r="G14" s="1798"/>
+      <x:c r="H14" s="1802"/>
+      <x:c r="I14" s="1799"/>
+      <x:c r="J14" s="1806" t="n">
+        <x:f>S14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="1786" t="str">
+        <x:f>IF(IF(ISNUMBER(E14),AND(E14&gt;=0,E14&lt;=3,MOD(E14,1)=0),FALSE),IF(E14=0,0,IF(IF(ISNUMBER(F14),AND(F14&gt;=1,F14&lt;=4,MOD(F14,1)=0),FALSE),E14*10+F14,"")),"")</x:f>
+      </x:c>
+      <x:c r="L14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),K14=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=21,K14=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=22,K14=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=11,K14=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=23,K14=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=13,K14=14,K14=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),K14=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S14" s="1786" t="str">
+        <x:f>IF(ISNUMBER(T14),INDEX($L$5:$R$5,1,7-T14),"")</x:f>
+      </x:c>
+      <x:c r="T14" s="1786" t="str">
+        <x:f>IF(ISNUMBER(K14),IF(L14,6,IF(M14,5,IF(N14,4,IF(O14,3,IF(P14,2,IF(Q14,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U14" s="1790" t="str">
+        <x:f>IF(AND(ISNUMBER(T14),ISNUMBER(H14)),IF(AND(H14&gt;=1,H14&lt;=4,MOD(H14,1)=0),T14*10+H14,""),"")</x:f>
+      </x:c>
+      <x:c r="V14" s="1798"/>
+      <x:c r="W14" s="1121"/>
+      <x:c r="X14" s="1114"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="V4:X4"/>
+    <x:mergeCell ref="B6:W6"/>
     <x:mergeCell ref="B4:C5"/>
     <x:mergeCell ref="D4:E4"/>
     <x:mergeCell ref="F4:G4"/>
     <x:mergeCell ref="H4:I4"/>
+    <x:mergeCell ref="V4:X4"/>
     <x:mergeCell ref="B2:J3"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="J7:J11">
-    <x:cfRule type="expression" dxfId="1633" priority="498">
+  <x:conditionalFormatting sqref="J7:J14">
+    <x:cfRule type="expression" dxfId="1626" priority="271">
       <x:formula>AND(ISNUMBER($T7),$T7=6)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1634" priority="499">
+    <x:cfRule type="expression" dxfId="1627" priority="272">
       <x:formula>AND(ISNUMBER($T7),$T7=5)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1635" priority="500">
+    <x:cfRule type="expression" dxfId="1628" priority="273">
       <x:formula>AND(ISNUMBER($T7),$T7=4)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1636" priority="501">
+    <x:cfRule type="expression" dxfId="1629" priority="274">
       <x:formula>AND(ISNUMBER($T7),$T7=3)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1637" priority="502">
+    <x:cfRule type="expression" dxfId="1630" priority="275">
       <x:formula>AND(ISNUMBER($T7),$T7=2)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1638" priority="503">
+    <x:cfRule type="expression" dxfId="1631" priority="276">
       <x:formula>AND(ISNUMBER($T7),$T7=1)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1639" priority="504">
+    <x:cfRule type="expression" dxfId="1632" priority="277">
       <x:formula>AND(ISNUMBER($T7),$T7=0)</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="E7:E11" promptTitle="Importance de la cible" prompt="0 : non applicable&#10;1 : peu importante&#10;2 : importante&#10;3 : très importante&#10;Si 0, la performance peut rester vide." errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="E7:E14" promptTitle="Importance de la cible" prompt="0 : non applicable&#10;1 : peu importante&#10;2 : importante&#10;3 : très importante&#10;Si 0, la performance peut rester vide." errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
       <x:formula1>"0,1,2,3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="F7:F11" promptTitle="Performance actuelle" prompt="1 : pas du tout atteinte&#10;2 : atteinte en partie&#10;3 : en voie d’être atteinte&#10;4 : atteinte&#10;Laisser vide si non évaluée ou non applicable." errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="F7:F14" promptTitle="Performance actuelle" prompt="1 : pas du tout atteinte&#10;2 : atteinte en partie&#10;3 : en voie d’être atteinte&#10;4 : atteinte&#10;Laisser vide si non évaluée ou non applicable." errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
       <x:formula1>"1,2,3,4"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="H7:H11" promptTitle="Compétences mobilisées" prompt="1 : équipe NR / RSE&#10;2 : NR / RSE et DSI&#10;3 : NR / RSE et équipe hors DSI&#10;4 : intervention extérieure" errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="H7:H14" promptTitle="Compétences mobilisées" prompt="1 : équipe NR / RSE&#10;2 : NR / RSE et DSI&#10;3 : NR / RSE et équipe hors DSI&#10;4 : intervention extérieure" errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
       <x:formula1>"1,2,3,4"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
+++ b/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
@@ -27547,7 +27547,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Version « Collectivités territoriales » proposée par LaNum Pays Basque pour les publics qu'elle accompagne dans le projet européen NÉONUM, et co-éditée avec l'INR, d'après la GPC-ONR. Les cibles métier (feuille « Cibles métier ») ne sont pas reprises dans les feuilles de résultats.</a:t>
+            <a:t>Version « Collectivités territoriales » : LaNum Pays Basque l'a conçue pour les publics qu'elle accompagne dans le projet européen NÉONUM, à partir de la GPC-ONR ; l'INR la co-édite. Les feuilles de résultats ne reprennent pas les cibles de la feuille « Cibles métier ».</a:t>
           </a:r>
         </a:p>
         <a:p>

--- a/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
+++ b/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
@@ -63,6 +63,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'ONR 5'!$B$2:$V$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'ONR 5'!$4:$6,'ONR 5'!$B:$C</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Résultats synthèse'!$B$2:$M$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Cibles métier'!$B$2:$V$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Cibles métier'!$4:$6,'Cibles métier'!$B:$C</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1" calcMode="auto" forceFullCalc="1"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -456,10 +458,11 @@
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Utilisateur invité</author>
     <author>Utilisateur</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{EB80FB45-ED39-4EE0-B694-4C8CBE5F9519}">
       <text>
         <r>
           <rPr>
@@ -467,47 +470,47 @@
             <color rgb="FF000000"/>
             <rFont val="Helv"/>
           </rPr>
-          <t>Parce que les services numériques peuvent être sources d’exclusion sociale, d’individualisation et d’obsolescence matérielle et logicielle, nous nous engageons à développer des offres de services accessibles pour tous, inclusives et durables.</t>
+          <t>Parce que le numérique est un acteur majeur d’émissions de Gaz à Effet de Serre, d’épuisement des ressources et d’affaissement de la biodiversité, participant activement au changement climatique, nous nous engageons à optimiser les outils numériques pour limiter leurs impacts et consommations.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+    <comment ref="D5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <t>Décrire les opportunités et les menaces associées à cette cible pour l’organisation : enjeux économiques, sociaux, environnementaux, réglementaires ou opérationnels.</t>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+    <comment ref="E5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <t>Évaluer l’importance de la cible pour l’organisation.
 0 : non applicable ; 1 : peu importante ; 2 : importante ; 3 : très importante.
 Une importance de 0 classe la cible comme non applicable, même sans note de performance.</t>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="F5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <t>Évaluer la situation actuelle à partir d’éléments documentés.
 1 : pas du tout atteinte ; 2 : atteinte en partie ; 3 : en voie d’être atteinte ; 4 : atteinte.
 Laisser vide si la cible n’est pas évaluée ou n’est pas applicable.</t>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+    <comment ref="G5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <t>Justifier la note de performance avec les mesures déjà en place, les résultats observés, les indicateurs disponibles et les sources datées. Distinguer les actions réalisées des actions seulement prévues.</t>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
+    <comment ref="I5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <t>Décrire les forces et les faiblesses internes : compétences, moyens humains, financiers et techniques, et partenaires disponibles pour agir sur la cible.</t>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+    <comment ref="J5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <t>Calcul automatique à partir de l’importance et de la performance, selon la matrice de l’onglet Priorisation.
 Importance 0 : non applicable. Sinon, deux notes valides sont nécessaires.
 Consulter Résultats détaillés et Résultats synthèse pour les résultats consolidés.</t>
       </text>
     </comment>
-    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000A000000}">
+    <comment ref="V5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
       <text>
         <t>Proposer des actions contribuant à l’atteinte de la cible. Préciser, si possible, un responsable, une échéance et un résultat attendu.
 Une proposition renseignée ne signifie pas que l’action a été validée ou réalisée.</t>
@@ -27544,7 +27547,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Version « Collectivités territoriales » co-éditée par l'Institut du Numérique Responsable (INR) et LaNum Pays Basque, dans le cadre du projet NÉONUM, d'après la GPC-ONR de l'INR. Les cibles métier (feuille « Cibles métier ») ne sont pas reprises dans les feuilles de résultats.</a:t>
+            <a:t>Version « Collectivités territoriales » : LaNum Pays Basque l'a conçue pour les publics qu'elle accompagne dans le projet européen NÉONUM, à partir de la GPC-ONR ; l'INR la co-édite. Les feuilles de résultats ne reprennent pas les cibles de la feuille « Cibles métier ».</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -27569,76 +27572,22 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="57e11928-67da-43e8-bf4d-cd8442aff663"/>
+        <xdr:cNvPr id="3" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="officialLogoINR20261007"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="bandeauCoedition"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>708025</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>791604</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -30094,76 +30043,22 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="9bd40fee-3145-48bd-b262-f6546a52b031"/>
+        <xdr:cNvPr id="3" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="officialLogoINR20261007"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="bandeauCoedition"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>708025</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>791604</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -30378,75 +30273,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="1a59bba7-19d6-49ba-821e-248463433195"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd0f8b23f0a7a4abc"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30524,75 +30365,21 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>498475</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="966d4c1d-e16d-4837-80a0-1444665fbe1b"/>
+        <xdr:cNvPr id="3" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4133cfea2974438b"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>135109</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>875913</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30615,70 +30402,16 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="ad6eca7f-2512-4327-a38b-5fd4332cec7e"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R88a94acdc061494d"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>708025</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>791604</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30696,75 +30429,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>7156450</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="253580d9-a043-4736-af34-c3bf36bb7bd2"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1641b25ecc3940ba"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>5907259</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>8419713</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30782,75 +30461,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="5ba0819c-73d0-49f8-9222-16d663e15aa0"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R34c26571c7014388"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1182859</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30868,75 +30493,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="1a59bba7-19d6-49ba-821e-248463433195"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd0f8b23f0a7a4abc"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -30954,75 +30525,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="1b76089d-f7b4-461a-bc2a-0b97e5c05474"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf6467eda94464bb5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -31040,75 +30557,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="9b925086-4e52-4a38-8282-40c16f0a476c"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5e03a6a319674c4e"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -31126,75 +30589,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="67e8ff89-b205-4e84-b992-af3db7ffe8a1"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R009525bc9d6e404c"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>382759</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>380613</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -31212,75 +30621,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>212725</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="638175"/>
+    <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="e81248c7-2f0d-494e-9b17-442281be75de"/>
+        <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8c85558606f24767"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>468484</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2299729" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="900" name="LaNum Pays Basque" descr="Logo LaNum Pays Basque"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>723513</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="778262" cy="638175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="901" name="NÉONUM" descr="Logo NÉONUM"/>
-        <xdr:cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="logoCoediteur2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="bandeauCoedition"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -42545,7 +41900,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor theme="9"/>
+    <x:tabColor theme="4"/>
     <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
   <x:sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="12"/>
@@ -42561,8 +41916,8 @@
     <x:col min="9" max="9" width="32" style="871" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="23" style="871" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="5.6640625" style="866" hidden="1" customWidth="1"/>
-    <x:col min="12" max="12" width="5.6640625" style="866" hidden="1" customWidth="1"/>
-    <x:col min="13" max="13" width="5.6640625" style="866" hidden="1" customWidth="1"/>
+    <x:col min="12" max="12" width="16.6640625" style="866" hidden="1" customWidth="1"/>
+    <x:col min="13" max="13" width="17.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="14" max="14" width="5.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="15" max="15" width="5.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="16" max="16" width="5.6640625" style="866" hidden="1" customWidth="1"/>
@@ -42572,8 +41927,8 @@
     <x:col min="20" max="20" width="5.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="21" max="21" width="5.6640625" style="866" hidden="1" customWidth="1"/>
     <x:col min="22" max="22" width="46" style="871" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="42.6640625" style="871" hidden="1" customWidth="1"/>
-    <x:col min="24" max="24" width="42.6640625" style="866" hidden="1" customWidth="1"/>
+    <x:col min="23" max="23" width="68.6640625" style="871" hidden="1" customWidth="1"/>
+    <x:col min="24" max="24" width="78.5" style="866" hidden="1" customWidth="1"/>
     <x:col min="25" max="25" width="10.6640625" style="866" customWidth="0" hidden="0"/>
     <x:col min="26" max="26" width="10.6640625" style="866" customWidth="0" hidden="0"/>
     <x:col min="27" max="27" width="10.6640625" style="866" customWidth="0" hidden="0"/>
@@ -42669,10 +42024,10 @@
     </x:row>
     <x:row r="4" ht="27" customHeight="1">
       <x:c r="A4" s="861"/>
-      <x:c r="B4" s="1822" t="str">
+      <x:c r="B4" s="1731" t="str">
         <x:v>Cibles à évaluer</x:v>
       </x:c>
-      <x:c r="C4" s="1823"/>
+      <x:c r="C4" s="1732"/>
       <x:c r="D4" s="1735" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Importance de la cible</x:t>
@@ -42715,8 +42070,8 @@
     </x:row>
     <x:row r="5" s="868" customFormat="1" ht="56" customHeight="1">
       <x:c r="A5" s="867"/>
-      <x:c r="B5" s="1824"/>
-      <x:c r="C5" s="1825"/>
+      <x:c r="B5" s="1733"/>
+      <x:c r="C5" s="1734"/>
       <x:c r="D5" s="1737" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Avantages possibles et risques</x:t>
@@ -42807,54 +42162,50 @@
           <x:t xml:space="preserve">Code priorité et compétences</x:t>
         </x:is>
       </x:c>
-      <x:c r="V5" s="1826" t="inlineStr">
+      <x:c r="V5" s="1751" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Actions proposées pour atteindre la cible</x:t>
         </x:is>
       </x:c>
-      <x:c r="W5" s="1753" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Adhérence</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="W5" s="1752"/>
       <x:c r="X5" s="1753"/>
     </x:row>
     <x:row r="6" s="875" customFormat="1" ht="34" customHeight="1">
       <x:c r="A6" s="874"/>
-      <x:c r="B6" s="1832" t="str">
+      <x:c r="B6" s="1764" t="str">
         <x:v>Renseigner les cellules jaunes pour les notes, puis les textes utiles. La priorité se calcule automatiquement. Faire défiler vers la droite pour proposer des actions.</x:v>
       </x:c>
-      <x:c r="C6" s="1833"/>
-      <x:c r="D6" s="1834"/>
-      <x:c r="E6" s="1834"/>
-      <x:c r="F6" s="1834"/>
-      <x:c r="G6" s="1834"/>
-      <x:c r="H6" s="1834"/>
-      <x:c r="I6" s="1834"/>
-      <x:c r="J6" s="1834"/>
-      <x:c r="K6" s="1834"/>
-      <x:c r="L6" s="1834"/>
-      <x:c r="M6" s="1834"/>
-      <x:c r="N6" s="1834"/>
-      <x:c r="O6" s="1834"/>
-      <x:c r="P6" s="1834"/>
-      <x:c r="Q6" s="1834"/>
-      <x:c r="R6" s="1834"/>
-      <x:c r="S6" s="1834"/>
-      <x:c r="T6" s="1834"/>
-      <x:c r="U6" s="1834"/>
-      <x:c r="V6" s="1835"/>
-      <x:c r="W6" s="1836"/>
-      <x:c r="X6" s="1129"/>
+      <x:c r="C6" s="1765"/>
+      <x:c r="D6" s="1766"/>
+      <x:c r="E6" s="1766"/>
+      <x:c r="F6" s="1766"/>
+      <x:c r="G6" s="1766"/>
+      <x:c r="H6" s="1766"/>
+      <x:c r="I6" s="1766"/>
+      <x:c r="J6" s="1766"/>
+      <x:c r="K6" s="1766"/>
+      <x:c r="L6" s="1766"/>
+      <x:c r="M6" s="1766"/>
+      <x:c r="N6" s="1766"/>
+      <x:c r="O6" s="1766"/>
+      <x:c r="P6" s="1766"/>
+      <x:c r="Q6" s="1766"/>
+      <x:c r="R6" s="1766"/>
+      <x:c r="S6" s="1766"/>
+      <x:c r="T6" s="1766"/>
+      <x:c r="U6" s="1766"/>
+      <x:c r="V6" s="1766"/>
+      <x:c r="W6" s="1765"/>
+      <x:c r="X6" s="1107"/>
     </x:row>
-    <x:row r="7" s="952" customFormat="1" ht="70" customHeight="1">
+    <x:row r="7" s="952" customFormat="1" ht="76" customHeight="1">
       <x:c r="A7" s="951"/>
-      <x:c r="B7" s="1804" t="inlineStr">
+      <x:c r="B7" s="1803" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="1796" t="inlineStr">
+      <x:c r="C7" s="1795" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Évaluer l'utilité environnementale et sociale des objets connectés et des projets de « territoire intelligent » avant de les déployer : capteurs, éclairage, vidéoprotection, plateformes de données.</x:t>
         </x:is>
@@ -42864,55 +42215,55 @@
       <x:c r="F7" s="1802"/>
       <x:c r="G7" s="1798"/>
       <x:c r="H7" s="1802"/>
-      <x:c r="I7" s="1798"/>
+      <x:c r="I7" s="1799"/>
       <x:c r="J7" s="1806" t="str">
-        <x:f t="shared" ref="J7:J9" si="0">S7</x:f>
-      </x:c>
-      <x:c r="K7" s="1783" t="str">
+        <x:f>S7</x:f>
+      </x:c>
+      <x:c r="K7" s="1777" t="str">
         <x:f>IF(IF(ISNUMBER(E7),AND(E7&gt;=0,E7&lt;=3,MOD(E7,1)=0),FALSE),IF(E7=0,0,IF(IF(ISNUMBER(F7),AND(F7&gt;=1,F7&lt;=4,MOD(F7,1)=0),FALSE),E7*10+F7,"")),"")</x:f>
       </x:c>
-      <x:c r="L7" s="1783" t="b">
+      <x:c r="L7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),K7=31,FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M7" s="1783" t="b">
+      <x:c r="M7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=21,K7=32),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N7" s="1783" t="b">
+      <x:c r="N7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=22,K7=33),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O7" s="1783" t="b">
+      <x:c r="O7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=11,K7=12),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P7" s="1783" t="b">
+      <x:c r="P7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=23,K7=34),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q7" s="1783" t="b">
+      <x:c r="Q7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),OR(K7=13,K7=14,K7=24),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R7" s="1783" t="b">
+      <x:c r="R7" s="1777" t="b">
         <x:f>IF(ISNUMBER(K7),K7=0,FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S7" s="1783" t="str">
-        <x:f>IF(ISNUMBER(T7),INDEX($L$5:$R$5,1,7-T7),"")</x:f>
-      </x:c>
-      <x:c r="T7" s="1783" t="str">
-        <x:f>IF(ISNUMBER(K7),IF(L7,6,IF(M7,5,IF(N7,4,IF(O7,3,IF(P7,2,IF(Q7,1,0)))))),"")</x:f>
-      </x:c>
-      <x:c r="U7" s="1783" t="str">
+      <x:c r="S7" s="1777" t="str">
+        <x:f t="shared" ref="S7:S12" si="0">IF(ISNUMBER(T7),INDEX($L$5:$R$5,1,7-T7),"")</x:f>
+      </x:c>
+      <x:c r="T7" s="1777" t="str">
+        <x:f t="shared" ref="T7:T12" si="1">IF(ISNUMBER(K7),IF(L7,6,IF(M7,5,IF(N7,4,IF(O7,3,IF(P7,2,IF(Q7,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U7" s="1790" t="str">
         <x:f>IF(AND(ISNUMBER(T7),ISNUMBER(H7)),IF(AND(H7&gt;=1,H7&lt;=4,MOD(H7,1)=0),T7*10+H7,""),"")</x:f>
       </x:c>
-      <x:c r="V7" s="1798"/>
-      <x:c r="W7" s="1123"/>
-      <x:c r="X7" s="1113"/>
+      <x:c r="V7" s="1799"/>
+      <x:c r="W7" s="1103"/>
+      <x:c r="X7" s="903"/>
     </x:row>
-    <x:row r="8" s="952" customFormat="1" ht="76" customHeight="1">
+    <x:row r="8" s="952" customFormat="1" ht="77" customHeight="1">
       <x:c r="A8" s="951"/>
       <x:c r="B8" s="1804" t="inlineStr">
         <x:is>
@@ -42921,7 +42272,7 @@
       </x:c>
       <x:c r="C8" s="1796" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Lutter contre l'illectronisme : financer la médiation numérique, garder un accueil physique et une solution non numérique pour chaque démarche.</x:t>
+          <x:t xml:space="preserve">Lutter contre l'illectronisme : soutenir la médiation numérique (conseillers numériques, espaces France Services, Aidants Connect), garder un accueil physique et une solution non numérique pour chaque démarche.</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" s="1798"/>
@@ -42929,53 +42280,53 @@
       <x:c r="F8" s="1802"/>
       <x:c r="G8" s="1798"/>
       <x:c r="H8" s="1802"/>
-      <x:c r="I8" s="1798"/>
+      <x:c r="I8" s="1799"/>
       <x:c r="J8" s="1806" t="str">
-        <x:f t="shared" si="0">S8</x:f>
-      </x:c>
-      <x:c r="K8" s="1783" t="str">
-        <x:f>IF(IF(ISNUMBER(E8),AND(E8&gt;=0,E8&lt;=3,MOD(E8,1)=0),FALSE),IF(E8=0,0,IF(IF(ISNUMBER(F8),AND(F8&gt;=1,F8&lt;=4,MOD(F8,1)=0),FALSE),E8*10+F8,"")),"")</x:f>
-      </x:c>
-      <x:c r="L8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),K8=31,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=21,K8=32),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=22,K8=33),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=11,K8=12),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=23,K8=34),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),OR(K8=13,K8=14,K8=24),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R8" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K8),K8=0,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S8" s="1783" t="str">
-        <x:f>IF(ISNUMBER(T8),INDEX($L$5:$R$5,1,7-T8),"")</x:f>
-      </x:c>
-      <x:c r="T8" s="1783" t="str">
-        <x:f>IF(ISNUMBER(K8),IF(L8,6,IF(M8,5,IF(N8,4,IF(O8,3,IF(P8,2,IF(Q8,1,0)))))),"")</x:f>
-      </x:c>
-      <x:c r="U8" s="1783" t="str">
-        <x:f>IF(AND(ISNUMBER(T8),ISNUMBER(H8)),IF(AND(H8&gt;=1,H8&lt;=4,MOD(H8,1)=0),T8*10+H8,""),"")</x:f>
-      </x:c>
-      <x:c r="V8" s="1798"/>
-      <x:c r="W8" s="1109"/>
-      <x:c r="X8" s="1108"/>
+        <x:f t="shared" ref="J8:J12" si="2">S8</x:f>
+      </x:c>
+      <x:c r="K8" s="1777" t="str">
+        <x:f t="shared" ref="K8:K12" si="3">IF(IF(ISNUMBER(E8),AND(E8&gt;=0,E8&lt;=3,MOD(E8,1)=0),FALSE),IF(E8=0,0,IF(IF(ISNUMBER(F8),AND(F8&gt;=1,F8&lt;=4,MOD(F8,1)=0),FALSE),E8*10+F8,"")),"")</x:f>
+      </x:c>
+      <x:c r="L8" s="1777" t="b">
+        <x:f t="shared" ref="L8:L12" si="4">IF(ISNUMBER(K8),K8=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="1777" t="b">
+        <x:f t="shared" ref="M8:M12" si="5">IF(ISNUMBER(K8),OR(K8=21,K8=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="1777" t="b">
+        <x:f t="shared" ref="N8:N12" si="6">IF(ISNUMBER(K8),OR(K8=22,K8=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="1777" t="b">
+        <x:f t="shared" ref="O8:O12" si="7">IF(ISNUMBER(K8),OR(K8=11,K8=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="1777" t="b">
+        <x:f t="shared" ref="P8:P12" si="8">IF(ISNUMBER(K8),OR(K8=23,K8=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="1777" t="b">
+        <x:f t="shared" ref="Q8:Q12" si="9">IF(ISNUMBER(K8),OR(K8=13,K8=14,K8=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="1777" t="b">
+        <x:f t="shared" ref="R8:R12" si="10">IF(ISNUMBER(K8),K8=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="1777" t="str">
+        <x:f t="shared" si="0">IF(ISNUMBER(T8),INDEX($L$5:$R$5,1,7-T8),"")</x:f>
+      </x:c>
+      <x:c r="T8" s="1777" t="str">
+        <x:f t="shared" si="1">IF(ISNUMBER(K8),IF(L8,6,IF(M8,5,IF(N8,4,IF(O8,3,IF(P8,2,IF(Q8,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U8" s="1790" t="str">
+        <x:f t="shared" ref="U8:U12" si="11">IF(AND(ISNUMBER(T8),ISNUMBER(H8)),IF(AND(H8&gt;=1,H8&lt;=4,MOD(H8,1)=0),T8*10+H8,""),"")</x:f>
+      </x:c>
+      <x:c r="V8" s="1799"/>
+      <x:c r="W8" s="1118"/>
+      <x:c r="X8" s="1117"/>
     </x:row>
     <x:row r="9" s="952" customFormat="1" ht="76" customHeight="1">
       <x:c r="A9" s="951"/>
@@ -42994,53 +42345,53 @@
       <x:c r="F9" s="1802"/>
       <x:c r="G9" s="1798"/>
       <x:c r="H9" s="1802"/>
-      <x:c r="I9" s="1798"/>
+      <x:c r="I9" s="1799"/>
       <x:c r="J9" s="1806" t="str">
-        <x:f t="shared" si="0">S9</x:f>
+        <x:f t="shared" si="2">S9</x:f>
       </x:c>
       <x:c r="K9" s="1783" t="str">
-        <x:f>IF(IF(ISNUMBER(E9),AND(E9&gt;=0,E9&lt;=3,MOD(E9,1)=0),FALSE),IF(E9=0,0,IF(IF(ISNUMBER(F9),AND(F9&gt;=1,F9&lt;=4,MOD(F9,1)=0),FALSE),E9*10+F9,"")),"")</x:f>
+        <x:f t="shared" si="3">IF(IF(ISNUMBER(E9),AND(E9&gt;=0,E9&lt;=3,MOD(E9,1)=0),FALSE),IF(E9=0,0,IF(IF(ISNUMBER(F9),AND(F9&gt;=1,F9&lt;=4,MOD(F9,1)=0),FALSE),E9*10+F9,"")),"")</x:f>
       </x:c>
       <x:c r="L9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),K9=31,FALSE)</x:f>
+        <x:f t="shared" si="4">IF(ISNUMBER(K9),K9=31,FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=21,K9=32),FALSE)</x:f>
+        <x:f t="shared" si="5">IF(ISNUMBER(K9),OR(K9=21,K9=32),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=22,K9=33),FALSE)</x:f>
+        <x:f t="shared" si="6">IF(ISNUMBER(K9),OR(K9=22,K9=33),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=11,K9=12),FALSE)</x:f>
+        <x:f t="shared" si="7">IF(ISNUMBER(K9),OR(K9=11,K9=12),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=23,K9=34),FALSE)</x:f>
+        <x:f t="shared" si="8">IF(ISNUMBER(K9),OR(K9=23,K9=34),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),OR(K9=13,K9=14,K9=24),FALSE)</x:f>
+        <x:f t="shared" si="9">IF(ISNUMBER(K9),OR(K9=13,K9=14,K9=24),FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R9" s="1783" t="b">
-        <x:f>IF(ISNUMBER(K9),K9=0,FALSE)</x:f>
+        <x:f t="shared" si="10">IF(ISNUMBER(K9),K9=0,FALSE)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S9" s="1783" t="str">
-        <x:f>IF(ISNUMBER(T9),INDEX($L$5:$R$5,1,7-T9),"")</x:f>
+        <x:f t="shared" si="0">IF(ISNUMBER(T9),INDEX($L$5:$R$5,1,7-T9),"")</x:f>
       </x:c>
       <x:c r="T9" s="1783" t="str">
-        <x:f>IF(ISNUMBER(K9),IF(L9,6,IF(M9,5,IF(N9,4,IF(O9,3,IF(P9,2,IF(Q9,1,0)))))),"")</x:f>
+        <x:f t="shared" si="1">IF(ISNUMBER(K9),IF(L9,6,IF(M9,5,IF(N9,4,IF(O9,3,IF(P9,2,IF(Q9,1,0)))))),"")</x:f>
       </x:c>
       <x:c r="U9" s="1783" t="str">
-        <x:f>IF(AND(ISNUMBER(T9),ISNUMBER(H9)),IF(AND(H9&gt;=1,H9&lt;=4,MOD(H9,1)=0),T9*10+H9,""),"")</x:f>
-      </x:c>
-      <x:c r="V9" s="1798"/>
-      <x:c r="W9" s="1122"/>
-      <x:c r="X9" s="1114"/>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(T9),ISNUMBER(H9)),IF(AND(H9&gt;=1,H9&lt;=4,MOD(H9,1)=0),T9*10+H9,""),"")</x:f>
+      </x:c>
+      <x:c r="V9" s="1799"/>
+      <x:c r="W9" s="1104"/>
+      <x:c r="X9" s="1116"/>
     </x:row>
     <x:row r="10" s="952" customFormat="1" ht="70" customHeight="1">
       <x:c r="A10" s="951"/>
@@ -43059,64 +42410,64 @@
       <x:c r="F10" s="1802"/>
       <x:c r="G10" s="1798"/>
       <x:c r="H10" s="1802"/>
-      <x:c r="I10" s="1798"/>
+      <x:c r="I10" s="1799"/>
       <x:c r="J10" s="1806" t="str">
-        <x:f>S10</x:f>
-      </x:c>
-      <x:c r="K10" s="1777" t="str">
-        <x:f>IF(IF(ISNUMBER(E10),AND(E10&gt;=0,E10&lt;=3,MOD(E10,1)=0),FALSE),IF(E10=0,0,IF(IF(ISNUMBER(F10),AND(F10&gt;=1,F10&lt;=4,MOD(F10,1)=0),FALSE),E10*10+F10,"")),"")</x:f>
-      </x:c>
-      <x:c r="L10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),K10=31,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=21,K10=32),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=22,K10=33),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=11,K10=12),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=23,K10=34),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),OR(K10=13,K10=14,K10=24),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R10" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K10),K10=0,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S10" s="1777" t="str">
-        <x:f>IF(ISNUMBER(T10),INDEX($L$5:$R$5,1,7-T10),"")</x:f>
-      </x:c>
-      <x:c r="T10" s="1777" t="str">
-        <x:f>IF(ISNUMBER(K10),IF(L10,6,IF(M10,5,IF(N10,4,IF(O10,3,IF(P10,2,IF(Q10,1,0)))))),"")</x:f>
+        <x:f t="shared" si="2">S10</x:f>
+      </x:c>
+      <x:c r="K10" s="1786" t="str">
+        <x:f t="shared" si="3">IF(IF(ISNUMBER(E10),AND(E10&gt;=0,E10&lt;=3,MOD(E10,1)=0),FALSE),IF(E10=0,0,IF(IF(ISNUMBER(F10),AND(F10&gt;=1,F10&lt;=4,MOD(F10,1)=0),FALSE),E10*10+F10,"")),"")</x:f>
+      </x:c>
+      <x:c r="L10" s="1786" t="b">
+        <x:f t="shared" si="4">IF(ISNUMBER(K10),K10=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="1786" t="b">
+        <x:f t="shared" si="5">IF(ISNUMBER(K10),OR(K10=21,K10=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="1786" t="b">
+        <x:f t="shared" si="6">IF(ISNUMBER(K10),OR(K10=22,K10=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="1786" t="b">
+        <x:f t="shared" si="7">IF(ISNUMBER(K10),OR(K10=11,K10=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="1786" t="b">
+        <x:f t="shared" si="8">IF(ISNUMBER(K10),OR(K10=23,K10=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="1786" t="b">
+        <x:f t="shared" si="9">IF(ISNUMBER(K10),OR(K10=13,K10=14,K10=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R10" s="1786" t="b">
+        <x:f t="shared" si="10">IF(ISNUMBER(K10),K10=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" s="1786" t="str">
+        <x:f t="shared" si="0">IF(ISNUMBER(T10),INDEX($L$5:$R$5,1,7-T10),"")</x:f>
+      </x:c>
+      <x:c r="T10" s="1786" t="str">
+        <x:f t="shared" si="1">IF(ISNUMBER(K10),IF(L10,6,IF(M10,5,IF(N10,4,IF(O10,3,IF(P10,2,IF(Q10,1,0)))))),"")</x:f>
       </x:c>
       <x:c r="U10" s="1790" t="str">
-        <x:f>IF(AND(ISNUMBER(T10),ISNUMBER(H10)),IF(AND(H10&gt;=1,H10&lt;=4,MOD(H10,1)=0),T10*10+H10,""),"")</x:f>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(T10),ISNUMBER(H10)),IF(AND(H10&gt;=1,H10&lt;=4,MOD(H10,1)=0),T10*10+H10,""),"")</x:f>
       </x:c>
       <x:c r="V10" s="1798"/>
-      <x:c r="W10" s="1109"/>
-      <x:c r="X10" s="1108"/>
+      <x:c r="W10" s="1105"/>
+      <x:c r="X10" s="903"/>
     </x:row>
-    <x:row r="11" s="952" customFormat="1" ht="70" customHeight="1">
+    <x:row r="11" s="952" customFormat="1" ht="100" customHeight="1">
       <x:c r="A11" s="951"/>
-      <x:c r="B11" s="1804" t="inlineStr">
+      <x:c r="B11" s="1805" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">C.5</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="1796" t="inlineStr">
+      <x:c r="C11" s="1797" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Former les élus et les agents au numérique responsable, et l'inscrire dans la stratégie numérique responsable prévue par la loi REEN.</x:t>
+          <x:t xml:space="preserve">Adopter et faire vivre la stratégie numérique responsable prévue par la loi REEN : obligatoire pour les communes et intercommunalités de plus de 50 000 habitants, recommandée pour les autres. Fixer des objectifs de réduction de l'empreinte du numérique, suivre leur mise en œuvre et former les élus et les agents.</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" s="1798"/>
@@ -43124,98 +42475,289 @@
       <x:c r="F11" s="1802"/>
       <x:c r="G11" s="1798"/>
       <x:c r="H11" s="1802"/>
-      <x:c r="I11" s="1798"/>
-      <x:c r="J11" s="1806" t="n">
-        <x:f>S11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="1777" t="str">
-        <x:f>IF(IF(ISNUMBER(E11),AND(E11&gt;=0,E11&lt;=3,MOD(E11,1)=0),FALSE),IF(E11=0,0,IF(IF(ISNUMBER(F11),AND(F11&gt;=1,F11&lt;=4,MOD(F11,1)=0),FALSE),E11*10+F11,"")),"")</x:f>
-      </x:c>
-      <x:c r="L11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),K11=31,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=21,K11=32),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=22,K11=33),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=11,K11=12),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=23,K11=34),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),OR(K11=13,K11=14,K11=24),FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R11" s="1777" t="b">
-        <x:f>IF(ISNUMBER(K11),K11=0,FALSE)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S11" s="1777" t="str">
-        <x:f>IF(ISNUMBER(T11),INDEX($L$5:$R$5,1,7-T11),"")</x:f>
-      </x:c>
-      <x:c r="T11" s="1777" t="str">
-        <x:f>IF(ISNUMBER(K11),IF(L11,6,IF(M11,5,IF(N11,4,IF(O11,3,IF(P11,2,IF(Q11,1,0)))))),"")</x:f>
+      <x:c r="I11" s="1799"/>
+      <x:c r="J11" s="1806" t="str">
+        <x:f t="shared" si="2">S11</x:f>
+      </x:c>
+      <x:c r="K11" s="1786" t="str">
+        <x:f t="shared" si="3">IF(IF(ISNUMBER(E11),AND(E11&gt;=0,E11&lt;=3,MOD(E11,1)=0),FALSE),IF(E11=0,0,IF(IF(ISNUMBER(F11),AND(F11&gt;=1,F11&lt;=4,MOD(F11,1)=0),FALSE),E11*10+F11,"")),"")</x:f>
+      </x:c>
+      <x:c r="L11" s="1786" t="b">
+        <x:f t="shared" si="4">IF(ISNUMBER(K11),K11=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="1786" t="b">
+        <x:f t="shared" si="5">IF(ISNUMBER(K11),OR(K11=21,K11=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" s="1786" t="b">
+        <x:f t="shared" si="6">IF(ISNUMBER(K11),OR(K11=22,K11=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="1786" t="b">
+        <x:f t="shared" si="7">IF(ISNUMBER(K11),OR(K11=11,K11=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="1786" t="b">
+        <x:f t="shared" si="8">IF(ISNUMBER(K11),OR(K11=23,K11=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="1786" t="b">
+        <x:f t="shared" si="9">IF(ISNUMBER(K11),OR(K11=13,K11=14,K11=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R11" s="1786" t="b">
+        <x:f t="shared" si="10">IF(ISNUMBER(K11),K11=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="1786" t="str">
+        <x:f t="shared" si="0">IF(ISNUMBER(T11),INDEX($L$5:$R$5,1,7-T11),"")</x:f>
+      </x:c>
+      <x:c r="T11" s="1786" t="str">
+        <x:f t="shared" si="1">IF(ISNUMBER(K11),IF(L11,6,IF(M11,5,IF(N11,4,IF(O11,3,IF(P11,2,IF(Q11,1,0)))))),"")</x:f>
       </x:c>
       <x:c r="U11" s="1790" t="str">
-        <x:f>IF(AND(ISNUMBER(T11),ISNUMBER(H11)),IF(AND(H11&gt;=1,H11&lt;=4,MOD(H11,1)=0),T11*10+H11,""),"")</x:f>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(T11),ISNUMBER(H11)),IF(AND(H11&gt;=1,H11&lt;=4,MOD(H11,1)=0),T11*10+H11,""),"")</x:f>
       </x:c>
       <x:c r="V11" s="1798"/>
-      <x:c r="W11" s="1109"/>
-      <x:c r="X11" s="1108"/>
+      <x:c r="W11" s="1119"/>
+      <x:c r="X11" s="1114"/>
     </x:row>
-    <x:row r="12">
-      <x:c r="V12" s="893"/>
+    <x:row r="12" s="953" customFormat="1" ht="100" customHeight="1">
+      <x:c r="A12" s="951"/>
+      <x:c r="B12" s="1804" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">C.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="1797" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rendre accessibles les contenus que la collectivité produit chaque jour : documents, publications sur les réseaux sociaux, vidéos sous-titrées, textes en facile à lire et à comprendre (FALC). Former les agents qui les produisent et offrir un accueil accessible, y compris aux personnes sourdes et malentendantes.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="1798"/>
+      <x:c r="E12" s="1802"/>
+      <x:c r="F12" s="1802"/>
+      <x:c r="G12" s="1798"/>
+      <x:c r="H12" s="1802"/>
+      <x:c r="I12" s="1799"/>
+      <x:c r="J12" s="1806" t="str">
+        <x:f t="shared" si="2">S12</x:f>
+      </x:c>
+      <x:c r="K12" s="1786" t="str">
+        <x:f t="shared" si="3">IF(IF(ISNUMBER(E12),AND(E12&gt;=0,E12&lt;=3,MOD(E12,1)=0),FALSE),IF(E12=0,0,IF(IF(ISNUMBER(F12),AND(F12&gt;=1,F12&lt;=4,MOD(F12,1)=0),FALSE),E12*10+F12,"")),"")</x:f>
+      </x:c>
+      <x:c r="L12" s="1786" t="b">
+        <x:f t="shared" si="4">IF(ISNUMBER(K12),K12=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="1786" t="b">
+        <x:f t="shared" si="5">IF(ISNUMBER(K12),OR(K12=21,K12=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="1786" t="b">
+        <x:f t="shared" si="6">IF(ISNUMBER(K12),OR(K12=22,K12=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="1786" t="b">
+        <x:f t="shared" si="7">IF(ISNUMBER(K12),OR(K12=11,K12=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="1786" t="b">
+        <x:f t="shared" si="8">IF(ISNUMBER(K12),OR(K12=23,K12=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="1786" t="b">
+        <x:f t="shared" si="9">IF(ISNUMBER(K12),OR(K12=13,K12=14,K12=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R12" s="1786" t="b">
+        <x:f t="shared" si="10">IF(ISNUMBER(K12),K12=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" s="1786" t="str">
+        <x:f t="shared" si="0">IF(ISNUMBER(T12),INDEX($L$5:$R$5,1,7-T12),"")</x:f>
+      </x:c>
+      <x:c r="T12" s="1786" t="str">
+        <x:f t="shared" si="1">IF(ISNUMBER(K12),IF(L12,6,IF(M12,5,IF(N12,4,IF(O12,3,IF(P12,2,IF(Q12,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U12" s="1790" t="str">
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(T12),ISNUMBER(H12)),IF(AND(H12&gt;=1,H12&lt;=4,MOD(H12,1)=0),T12*10+H12,""),"")</x:f>
+      </x:c>
+      <x:c r="V12" s="1798"/>
+      <x:c r="W12" s="1120"/>
+      <x:c r="X12" s="1114"/>
+    </x:row>
+    <x:row r="13" ht="88.5" customHeight="1">
+      <x:c r="B13" s="1804" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">C.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="1797" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Recenser les usages de l'intelligence artificielle dans la collectivité, y compris l'IA générative utilisée par les agents. Les encadrer par une charte, vérifier les obligations du règlement européen sur l'IA, et informer les habitants des usages qui les concernent.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="1798"/>
+      <x:c r="E13" s="1802"/>
+      <x:c r="F13" s="1802"/>
+      <x:c r="G13" s="1798"/>
+      <x:c r="H13" s="1802"/>
+      <x:c r="I13" s="1799"/>
+      <x:c r="J13" s="1806" t="str">
+        <x:f t="shared" ref="J13" si="12">S13</x:f>
+      </x:c>
+      <x:c r="K13" s="1786" t="str">
+        <x:f t="shared" ref="K13" si="13">IF(IF(ISNUMBER(E13),AND(E13&gt;=0,E13&lt;=3,MOD(E13,1)=0),FALSE),IF(E13=0,0,IF(IF(ISNUMBER(F13),AND(F13&gt;=1,F13&lt;=4,MOD(F13,1)=0),FALSE),E13*10+F13,"")),"")</x:f>
+      </x:c>
+      <x:c r="L13" s="1786" t="b">
+        <x:f t="shared" ref="L13" si="14">IF(ISNUMBER(K13),K13=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="1786" t="b">
+        <x:f t="shared" ref="M13" si="15">IF(ISNUMBER(K13),OR(K13=21,K13=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="1786" t="b">
+        <x:f t="shared" ref="N13" si="16">IF(ISNUMBER(K13),OR(K13=22,K13=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="1786" t="b">
+        <x:f t="shared" ref="O13" si="17">IF(ISNUMBER(K13),OR(K13=11,K13=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="1786" t="b">
+        <x:f t="shared" ref="P13" si="18">IF(ISNUMBER(K13),OR(K13=23,K13=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="1786" t="b">
+        <x:f t="shared" ref="Q13" si="19">IF(ISNUMBER(K13),OR(K13=13,K13=14,K13=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="1786" t="b">
+        <x:f t="shared" ref="R13" si="20">IF(ISNUMBER(K13),K13=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="1786" t="str">
+        <x:f t="shared" ref="S13" si="21">IF(ISNUMBER(T13),INDEX($L$5:$R$5,1,7-T13),"")</x:f>
+      </x:c>
+      <x:c r="T13" s="1786" t="str">
+        <x:f t="shared" ref="T13" si="22">IF(ISNUMBER(K13),IF(L13,6,IF(M13,5,IF(N13,4,IF(O13,3,IF(P13,2,IF(Q13,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U13" s="1790" t="str">
+        <x:f t="shared" ref="U13" si="23">IF(AND(ISNUMBER(T13),ISNUMBER(H13)),IF(AND(H13&gt;=1,H13&lt;=4,MOD(H13,1)=0),T13*10+H13,""),"")</x:f>
+      </x:c>
+      <x:c r="V13" s="1798"/>
+      <x:c r="W13" s="1121"/>
+      <x:c r="X13" s="1114"/>
+    </x:row>
+    <x:row r="14" ht="88.5" customHeight="1">
+      <x:c r="B14" s="1804" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">C.8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="1797" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ouvrir la décision publique avec des outils de participation citoyenne (civic tech) : consultations, budgets participatifs, signalements. Choisir des outils ouverts, accessibles et sobres, comme les logiciels libres, et les compléter par des temps d'échange en présentiel.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="1798"/>
+      <x:c r="E14" s="1802"/>
+      <x:c r="F14" s="1802"/>
+      <x:c r="G14" s="1798"/>
+      <x:c r="H14" s="1802"/>
+      <x:c r="I14" s="1799"/>
+      <x:c r="J14" s="1806" t="n">
+        <x:f>S14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="1786" t="str">
+        <x:f>IF(IF(ISNUMBER(E14),AND(E14&gt;=0,E14&lt;=3,MOD(E14,1)=0),FALSE),IF(E14=0,0,IF(IF(ISNUMBER(F14),AND(F14&gt;=1,F14&lt;=4,MOD(F14,1)=0),FALSE),E14*10+F14,"")),"")</x:f>
+      </x:c>
+      <x:c r="L14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),K14=31,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=21,K14=32),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=22,K14=33),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=11,K14=12),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=23,K14=34),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),OR(K14=13,K14=14,K14=24),FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R14" s="1786" t="b">
+        <x:f>IF(ISNUMBER(K14),K14=0,FALSE)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S14" s="1786" t="str">
+        <x:f>IF(ISNUMBER(T14),INDEX($L$5:$R$5,1,7-T14),"")</x:f>
+      </x:c>
+      <x:c r="T14" s="1786" t="str">
+        <x:f>IF(ISNUMBER(K14),IF(L14,6,IF(M14,5,IF(N14,4,IF(O14,3,IF(P14,2,IF(Q14,1,0)))))),"")</x:f>
+      </x:c>
+      <x:c r="U14" s="1790" t="str">
+        <x:f>IF(AND(ISNUMBER(T14),ISNUMBER(H14)),IF(AND(H14&gt;=1,H14&lt;=4,MOD(H14,1)=0),T14*10+H14,""),"")</x:f>
+      </x:c>
+      <x:c r="V14" s="1798"/>
+      <x:c r="W14" s="1121"/>
+      <x:c r="X14" s="1114"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="V4:X4"/>
+    <x:mergeCell ref="B6:W6"/>
     <x:mergeCell ref="B4:C5"/>
     <x:mergeCell ref="D4:E4"/>
     <x:mergeCell ref="F4:G4"/>
     <x:mergeCell ref="H4:I4"/>
+    <x:mergeCell ref="V4:X4"/>
     <x:mergeCell ref="B2:J3"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="J7:J11">
-    <x:cfRule type="expression" dxfId="1633" priority="498">
+  <x:conditionalFormatting sqref="J7:J14">
+    <x:cfRule type="expression" dxfId="1626" priority="271">
       <x:formula>AND(ISNUMBER($T7),$T7=6)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1634" priority="499">
+    <x:cfRule type="expression" dxfId="1627" priority="272">
       <x:formula>AND(ISNUMBER($T7),$T7=5)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1635" priority="500">
+    <x:cfRule type="expression" dxfId="1628" priority="273">
       <x:formula>AND(ISNUMBER($T7),$T7=4)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1636" priority="501">
+    <x:cfRule type="expression" dxfId="1629" priority="274">
       <x:formula>AND(ISNUMBER($T7),$T7=3)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1637" priority="502">
+    <x:cfRule type="expression" dxfId="1630" priority="275">
       <x:formula>AND(ISNUMBER($T7),$T7=2)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1638" priority="503">
+    <x:cfRule type="expression" dxfId="1631" priority="276">
       <x:formula>AND(ISNUMBER($T7),$T7=1)</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1639" priority="504">
+    <x:cfRule type="expression" dxfId="1632" priority="277">
       <x:formula>AND(ISNUMBER($T7),$T7=0)</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="E7:E11" promptTitle="Importance de la cible" prompt="0 : non applicable&#10;1 : peu importante&#10;2 : importante&#10;3 : très importante&#10;Si 0, la performance peut rester vide." errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="E7:E14" promptTitle="Importance de la cible" prompt="0 : non applicable&#10;1 : peu importante&#10;2 : importante&#10;3 : très importante&#10;Si 0, la performance peut rester vide." errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
       <x:formula1>"0,1,2,3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="F7:F11" promptTitle="Performance actuelle" prompt="1 : pas du tout atteinte&#10;2 : atteinte en partie&#10;3 : en voie d’être atteinte&#10;4 : atteinte&#10;Laisser vide si non évaluée ou non applicable." errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="F7:F14" promptTitle="Performance actuelle" prompt="1 : pas du tout atteinte&#10;2 : atteinte en partie&#10;3 : en voie d’être atteinte&#10;4 : atteinte&#10;Laisser vide si non évaluée ou non applicable." errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
       <x:formula1>"1,2,3,4"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="H7:H11" promptTitle="Compétences mobilisées" prompt="1 : équipe NR / RSE&#10;2 : NR / RSE et DSI&#10;3 : NR / RSE et équipe hors DSI&#10;4 : intervention extérieure" errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
+    <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" showDropDown="0" sqref="H7:H14" promptTitle="Compétences mobilisées" prompt="1 : équipe NR / RSE&#10;2 : NR / RSE et DSI&#10;3 : NR / RSE et équipe hors DSI&#10;4 : intervention extérieure" errorTitle="Note invalide" error="Choisir une note dans la liste ou laisser la cellule vide.">
       <x:formula1>"1,2,3,4"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
+++ b/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
@@ -31306,7 +31306,7 @@
         <f>IF(ISBLANK('ONR 1'!J7),"",'ONR 1'!J7)</f>
       </c>
       <c r="K5" s="227" t="str">
-        <f t="shared" ref="K5:K9" si="1">IF(ISBLANK('ONR 1'!K7),"",'ONR 1'!K7)</f>
+        <f>IF(ISBLANK('ONR 1'!K7),"",'ONR 1'!K7)</f>
       </c>
       <c r="L5" s="227" t="b">
         <f>IF(ISBLANK('ONR 1'!L7),"",'ONR 1'!L7)</f>
@@ -31337,16 +31337,16 @@
         <v>0</v>
       </c>
       <c r="S5" s="228" t="str">
-        <f t="shared" ref="S5:S9" si="2">IF(ISBLANK('ONR 1'!S7),"",'ONR 1'!S7)</f>
+        <f>IF(ISBLANK('ONR 1'!S7),"",'ONR 1'!S7)</f>
       </c>
       <c r="T5" s="226" t="str">
-        <f t="shared" ref="T5:T9" si="3">IF(ISBLANK('ONR 1'!T7),"",'ONR 1'!T7)</f>
+        <f>IF(ISBLANK('ONR 1'!T7),"",'ONR 1'!T7)</f>
       </c>
       <c r="U5" s="227" t="str">
-        <f t="shared" ref="U5:U9" si="4">IF(ISBLANK('ONR 1'!U7),"",'ONR 1'!U7)</f>
+        <f>IF(ISBLANK('ONR 1'!U7),"",'ONR 1'!U7)</f>
       </c>
       <c r="V5" s="229" t="str">
-        <f t="shared" ref="V5:V11" si="5">IF(ISBLANK('ONR 1'!G7),"",'ONR 1'!G7)</f>
+        <f>IF(ISBLANK('ONR 1'!G7),"",'ONR 1'!G7)</f>
       </c>
       <c r="W5" s="203" t="str">
         <f>IF(ISBLANK('ONR 1'!V7),"",'ONR 1'!V7)</f>
@@ -31355,42 +31355,34 @@
         <f>IF(ISBLANK('ONR 1'!W7),"",'ONR 1'!W7)</f>
       </c>
       <c r="Y5" s="230" t="str">
-        <f t="shared" ref="Y5:Y11" si="6">IF(ISBLANK('ONR 1'!I7),"",'ONR 1'!I7)</f>
+        <f>IF(ISBLANK('ONR 1'!I7),"",'ONR 1'!I7)</f>
       </c>
       <c r="Z5" s="230" t="str">
-        <f t="shared" ref="Z5:Z11" si="7">IF(ISBLANK('ONR 1'!D7),"",'ONR 1'!D7)</f>
+        <f>IF(ISBLANK('ONR 1'!D7),"",'ONR 1'!D7)</f>
       </c>
       <c r="AE5" s="206" t="n">
-        <f t="shared" ref="AE5:AE11" si="8">IF(ISNUMBER(T5),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T5),0,1)</f>
       </c>
       <c r="AF5" s="206" t="n">
-        <f t="shared" ref="AF5:AL11" si="9">IF(L5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L5=TRUE,1,0)</f>
       </c>
       <c r="AG5" s="206" t="n">
-        <f t="shared" si="9">IF(M5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M5=TRUE,1,0)</f>
       </c>
       <c r="AH5" s="206" t="n">
-        <f t="shared" si="9">IF(N5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N5=TRUE,1,0)</f>
       </c>
       <c r="AI5" s="206" t="n">
-        <f t="shared" si="9">IF(O5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O5=TRUE,1,0)</f>
       </c>
       <c r="AJ5" s="206" t="n">
-        <f t="shared" si="9">IF(P5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P5=TRUE,1,0)</f>
       </c>
       <c r="AK5" s="206" t="n">
-        <f t="shared" si="9">IF(Q5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q5=TRUE,1,0)</f>
       </c>
       <c r="AL5" s="206" t="n">
-        <f t="shared" si="9">IF(R5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R5=TRUE,1,0)</f>
       </c>
       <c r="AM5" t="n">
         <f>IF(LEN(TRIM(W5))&gt;0,1,0)</f>
@@ -31426,50 +31418,43 @@
         <f>IF(ISBLANK('ONR 1'!I8),"",'ONR 1'!I8)</f>
       </c>
       <c r="J6" s="232" t="str">
-        <f t="shared" ref="J6:J9" si="10">IF(ISBLANK('ONR 1'!J8),"",'ONR 1'!J8)</f>
+        <f>IF(ISBLANK('ONR 1'!J8),"",'ONR 1'!J8)</f>
       </c>
       <c r="K6" s="233" t="str">
-        <f t="shared" si="1">IF(ISBLANK('ONR 1'!K8),"",'ONR 1'!K8)</f>
+        <f>IF(ISBLANK('ONR 1'!K8),"",'ONR 1'!K8)</f>
       </c>
       <c r="L6" s="233" t="b">
-        <f t="shared" ref="L6:L9" si="11">IF(ISBLANK('ONR 1'!L8),"",'ONR 1'!L8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L8),"",'ONR 1'!L8)</f>
       </c>
       <c r="M6" s="233" t="b">
-        <f t="shared" ref="M6:M9" si="12">IF(ISBLANK('ONR 1'!M8),"",'ONR 1'!M8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M8),"",'ONR 1'!M8)</f>
       </c>
       <c r="N6" s="233" t="b">
-        <f t="shared" ref="N6:N9" si="13">IF(ISBLANK('ONR 1'!N8),"",'ONR 1'!N8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N8),"",'ONR 1'!N8)</f>
       </c>
       <c r="O6" s="233" t="b">
-        <f t="shared" ref="O6:O9" si="14">IF(ISBLANK('ONR 1'!O8),"",'ONR 1'!O8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O8),"",'ONR 1'!O8)</f>
       </c>
       <c r="P6" s="233" t="b">
-        <f t="shared" ref="P6:P9" si="15">IF(ISBLANK('ONR 1'!P8),"",'ONR 1'!P8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P8),"",'ONR 1'!P8)</f>
       </c>
       <c r="Q6" s="233" t="b">
-        <f t="shared" ref="Q6:Q9" si="16">IF(ISBLANK('ONR 1'!Q8),"",'ONR 1'!Q8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q8),"",'ONR 1'!Q8)</f>
       </c>
       <c r="R6" s="233" t="b">
-        <f t="shared" ref="R6:R9" si="17">IF(ISBLANK('ONR 1'!R8),"",'ONR 1'!R8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R8),"",'ONR 1'!R8)</f>
       </c>
       <c r="S6" s="234" t="str">
-        <f t="shared" si="2">IF(ISBLANK('ONR 1'!S8),"",'ONR 1'!S8)</f>
+        <f>IF(ISBLANK('ONR 1'!S8),"",'ONR 1'!S8)</f>
       </c>
       <c r="T6" s="232" t="str">
-        <f t="shared" si="3">IF(ISBLANK('ONR 1'!T8),"",'ONR 1'!T8)</f>
+        <f>IF(ISBLANK('ONR 1'!T8),"",'ONR 1'!T8)</f>
       </c>
       <c r="U6" s="233" t="str">
-        <f t="shared" si="4">IF(ISBLANK('ONR 1'!U8),"",'ONR 1'!U8)</f>
+        <f>IF(ISBLANK('ONR 1'!U8),"",'ONR 1'!U8)</f>
       </c>
       <c r="V6" s="235" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G8),"",'ONR 1'!G8)</f>
+        <f>IF(ISBLANK('ONR 1'!G8),"",'ONR 1'!G8)</f>
       </c>
       <c r="W6" s="235" t="str">
         <f>IF(ISBLANK('ONR 1'!V8),"",'ONR 1'!V8)</f>
@@ -31478,42 +31463,34 @@
         <f>IF(ISBLANK('ONR 1'!W8),"",'ONR 1'!W8)</f>
       </c>
       <c r="Y6" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I8),"",'ONR 1'!I8)</f>
+        <f>IF(ISBLANK('ONR 1'!I8),"",'ONR 1'!I8)</f>
       </c>
       <c r="Z6" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D8),"",'ONR 1'!D8)</f>
+        <f>IF(ISBLANK('ONR 1'!D8),"",'ONR 1'!D8)</f>
       </c>
       <c r="AE6" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T6),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T6),0,1)</f>
       </c>
       <c r="AF6" s="206" t="n">
-        <f t="shared" si="9">IF(L6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L6=TRUE,1,0)</f>
       </c>
       <c r="AG6" s="206" t="n">
-        <f t="shared" si="9">IF(M6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M6=TRUE,1,0)</f>
       </c>
       <c r="AH6" s="206" t="n">
-        <f t="shared" si="9">IF(N6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N6=TRUE,1,0)</f>
       </c>
       <c r="AI6" s="206" t="n">
-        <f t="shared" si="9">IF(O6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O6=TRUE,1,0)</f>
       </c>
       <c r="AJ6" s="206" t="n">
-        <f t="shared" si="9">IF(P6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P6=TRUE,1,0)</f>
       </c>
       <c r="AK6" s="206" t="n">
-        <f t="shared" si="9">IF(Q6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q6=TRUE,1,0)</f>
       </c>
       <c r="AL6" s="206" t="n">
-        <f t="shared" si="9">IF(R6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R6=TRUE,1,0)</f>
       </c>
       <c r="AM6" t="n">
         <f>IF(LEN(TRIM(W6))&gt;0,1,0)</f>
@@ -31549,50 +31526,43 @@
         <f>IF(ISBLANK('ONR 1'!I9),"",'ONR 1'!I9)</f>
       </c>
       <c r="J7" s="232" t="str">
-        <f t="shared" si="10">IF(ISBLANK('ONR 1'!J9),"",'ONR 1'!J9)</f>
+        <f>IF(ISBLANK('ONR 1'!J9),"",'ONR 1'!J9)</f>
       </c>
       <c r="K7" s="233" t="str">
-        <f t="shared" si="1">IF(ISBLANK('ONR 1'!K9),"",'ONR 1'!K9)</f>
+        <f>IF(ISBLANK('ONR 1'!K9),"",'ONR 1'!K9)</f>
       </c>
       <c r="L7" s="233" t="b">
-        <f t="shared" si="11">IF(ISBLANK('ONR 1'!L9),"",'ONR 1'!L9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L9),"",'ONR 1'!L9)</f>
       </c>
       <c r="M7" s="233" t="b">
-        <f t="shared" si="12">IF(ISBLANK('ONR 1'!M9),"",'ONR 1'!M9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M9),"",'ONR 1'!M9)</f>
       </c>
       <c r="N7" s="233" t="b">
-        <f t="shared" si="13">IF(ISBLANK('ONR 1'!N9),"",'ONR 1'!N9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N9),"",'ONR 1'!N9)</f>
       </c>
       <c r="O7" s="233" t="b">
-        <f t="shared" si="14">IF(ISBLANK('ONR 1'!O9),"",'ONR 1'!O9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O9),"",'ONR 1'!O9)</f>
       </c>
       <c r="P7" s="233" t="b">
-        <f t="shared" si="15">IF(ISBLANK('ONR 1'!P9),"",'ONR 1'!P9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P9),"",'ONR 1'!P9)</f>
       </c>
       <c r="Q7" s="233" t="b">
-        <f t="shared" si="16">IF(ISBLANK('ONR 1'!Q9),"",'ONR 1'!Q9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q9),"",'ONR 1'!Q9)</f>
       </c>
       <c r="R7" s="233" t="b">
-        <f t="shared" si="17">IF(ISBLANK('ONR 1'!R9),"",'ONR 1'!R9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R9),"",'ONR 1'!R9)</f>
       </c>
       <c r="S7" s="234" t="str">
-        <f t="shared" si="2">IF(ISBLANK('ONR 1'!S9),"",'ONR 1'!S9)</f>
+        <f>IF(ISBLANK('ONR 1'!S9),"",'ONR 1'!S9)</f>
       </c>
       <c r="T7" s="232" t="str">
-        <f t="shared" si="3">IF(ISBLANK('ONR 1'!T9),"",'ONR 1'!T9)</f>
+        <f>IF(ISBLANK('ONR 1'!T9),"",'ONR 1'!T9)</f>
       </c>
       <c r="U7" s="233" t="str">
-        <f t="shared" si="4">IF(ISBLANK('ONR 1'!U9),"",'ONR 1'!U9)</f>
+        <f>IF(ISBLANK('ONR 1'!U9),"",'ONR 1'!U9)</f>
       </c>
       <c r="V7" s="235" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G9),"",'ONR 1'!G9)</f>
+        <f>IF(ISBLANK('ONR 1'!G9),"",'ONR 1'!G9)</f>
       </c>
       <c r="W7" s="142" t="str">
         <f>IF(ISBLANK('ONR 1'!V9),"",'ONR 1'!V9)</f>
@@ -31601,42 +31571,34 @@
         <f>IF(ISBLANK('ONR 1'!W9),"",'ONR 1'!W9)</f>
       </c>
       <c r="Y7" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I9),"",'ONR 1'!I9)</f>
+        <f>IF(ISBLANK('ONR 1'!I9),"",'ONR 1'!I9)</f>
       </c>
       <c r="Z7" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D9),"",'ONR 1'!D9)</f>
+        <f>IF(ISBLANK('ONR 1'!D9),"",'ONR 1'!D9)</f>
       </c>
       <c r="AE7" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T7),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T7),0,1)</f>
       </c>
       <c r="AF7" s="206" t="n">
-        <f t="shared" si="9">IF(L7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L7=TRUE,1,0)</f>
       </c>
       <c r="AG7" s="206" t="n">
-        <f t="shared" si="9">IF(M7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M7=TRUE,1,0)</f>
       </c>
       <c r="AH7" s="206" t="n">
-        <f t="shared" si="9">IF(N7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N7=TRUE,1,0)</f>
       </c>
       <c r="AI7" s="206" t="n">
-        <f t="shared" si="9">IF(O7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O7=TRUE,1,0)</f>
       </c>
       <c r="AJ7" s="206" t="n">
-        <f t="shared" si="9">IF(P7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P7=TRUE,1,0)</f>
       </c>
       <c r="AK7" s="206" t="n">
-        <f t="shared" si="9">IF(Q7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q7=TRUE,1,0)</f>
       </c>
       <c r="AL7" s="206" t="n">
-        <f t="shared" si="9">IF(R7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R7=TRUE,1,0)</f>
       </c>
       <c r="AM7" t="n">
         <f>IF(LEN(TRIM(W7))&gt;0,1,0)</f>
@@ -31672,50 +31634,43 @@
         <f>IF(ISBLANK('ONR 1'!I10),"",'ONR 1'!I10)</f>
       </c>
       <c r="J8" s="232" t="str">
-        <f t="shared" si="10">IF(ISBLANK('ONR 1'!J10),"",'ONR 1'!J10)</f>
+        <f>IF(ISBLANK('ONR 1'!J10),"",'ONR 1'!J10)</f>
       </c>
       <c r="K8" s="233" t="str">
-        <f t="shared" si="1">IF(ISBLANK('ONR 1'!K10),"",'ONR 1'!K10)</f>
+        <f>IF(ISBLANK('ONR 1'!K10),"",'ONR 1'!K10)</f>
       </c>
       <c r="L8" s="233" t="b">
-        <f t="shared" si="11">IF(ISBLANK('ONR 1'!L10),"",'ONR 1'!L10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L10),"",'ONR 1'!L10)</f>
       </c>
       <c r="M8" s="233" t="b">
-        <f t="shared" si="12">IF(ISBLANK('ONR 1'!M10),"",'ONR 1'!M10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M10),"",'ONR 1'!M10)</f>
       </c>
       <c r="N8" s="233" t="b">
-        <f t="shared" si="13">IF(ISBLANK('ONR 1'!N10),"",'ONR 1'!N10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N10),"",'ONR 1'!N10)</f>
       </c>
       <c r="O8" s="233" t="b">
-        <f t="shared" si="14">IF(ISBLANK('ONR 1'!O10),"",'ONR 1'!O10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O10),"",'ONR 1'!O10)</f>
       </c>
       <c r="P8" s="233" t="b">
-        <f t="shared" si="15">IF(ISBLANK('ONR 1'!P10),"",'ONR 1'!P10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P10),"",'ONR 1'!P10)</f>
       </c>
       <c r="Q8" s="233" t="b">
-        <f t="shared" si="16">IF(ISBLANK('ONR 1'!Q10),"",'ONR 1'!Q10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q10),"",'ONR 1'!Q10)</f>
       </c>
       <c r="R8" s="233" t="b">
-        <f t="shared" si="17">IF(ISBLANK('ONR 1'!R10),"",'ONR 1'!R10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R10),"",'ONR 1'!R10)</f>
       </c>
       <c r="S8" s="234" t="str">
-        <f t="shared" si="2">IF(ISBLANK('ONR 1'!S10),"",'ONR 1'!S10)</f>
+        <f>IF(ISBLANK('ONR 1'!S10),"",'ONR 1'!S10)</f>
       </c>
       <c r="T8" s="232" t="str">
-        <f t="shared" si="3">IF(ISBLANK('ONR 1'!T10),"",'ONR 1'!T10)</f>
+        <f>IF(ISBLANK('ONR 1'!T10),"",'ONR 1'!T10)</f>
       </c>
       <c r="U8" s="233" t="str">
-        <f t="shared" si="4">IF(ISBLANK('ONR 1'!U10),"",'ONR 1'!U10)</f>
+        <f>IF(ISBLANK('ONR 1'!U10),"",'ONR 1'!U10)</f>
       </c>
       <c r="V8" s="239" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G10),"",'ONR 1'!G10)</f>
+        <f>IF(ISBLANK('ONR 1'!G10),"",'ONR 1'!G10)</f>
       </c>
       <c r="W8" s="210" t="str">
         <f>IF(ISBLANK('ONR 1'!V10),"",'ONR 1'!V10)</f>
@@ -31724,42 +31679,34 @@
         <f>IF(ISBLANK('ONR 1'!W10),"",'ONR 1'!W10)</f>
       </c>
       <c r="Y8" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I10),"",'ONR 1'!I10)</f>
+        <f>IF(ISBLANK('ONR 1'!I10),"",'ONR 1'!I10)</f>
       </c>
       <c r="Z8" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D10),"",'ONR 1'!D10)</f>
+        <f>IF(ISBLANK('ONR 1'!D10),"",'ONR 1'!D10)</f>
       </c>
       <c r="AE8" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T8),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T8),0,1)</f>
       </c>
       <c r="AF8" s="206" t="n">
-        <f t="shared" si="9">IF(L8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L8=TRUE,1,0)</f>
       </c>
       <c r="AG8" s="206" t="n">
-        <f t="shared" si="9">IF(M8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M8=TRUE,1,0)</f>
       </c>
       <c r="AH8" s="206" t="n">
-        <f t="shared" si="9">IF(N8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N8=TRUE,1,0)</f>
       </c>
       <c r="AI8" s="206" t="n">
-        <f t="shared" si="9">IF(O8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O8=TRUE,1,0)</f>
       </c>
       <c r="AJ8" s="206" t="n">
-        <f t="shared" si="9">IF(P8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P8=TRUE,1,0)</f>
       </c>
       <c r="AK8" s="206" t="n">
-        <f t="shared" si="9">IF(Q8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q8=TRUE,1,0)</f>
       </c>
       <c r="AL8" s="206" t="n">
-        <f t="shared" si="9">IF(R8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R8=TRUE,1,0)</f>
       </c>
       <c r="AM8" t="n">
         <f>IF(LEN(TRIM(W8))&gt;0,1,0)</f>
@@ -31795,50 +31742,43 @@
         <f>IF(ISBLANK('ONR 1'!I11),"",'ONR 1'!I11)</f>
       </c>
       <c r="J9" s="232" t="str">
-        <f t="shared" si="10">IF(ISBLANK('ONR 1'!J11),"",'ONR 1'!J11)</f>
+        <f>IF(ISBLANK('ONR 1'!J11),"",'ONR 1'!J11)</f>
       </c>
       <c r="K9" s="233" t="str">
-        <f t="shared" si="1">IF(ISBLANK('ONR 1'!K11),"",'ONR 1'!K11)</f>
+        <f>IF(ISBLANK('ONR 1'!K11),"",'ONR 1'!K11)</f>
       </c>
       <c r="L9" s="233" t="b">
-        <f t="shared" si="11">IF(ISBLANK('ONR 1'!L11),"",'ONR 1'!L11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L11),"",'ONR 1'!L11)</f>
       </c>
       <c r="M9" s="233" t="b">
-        <f t="shared" si="12">IF(ISBLANK('ONR 1'!M11),"",'ONR 1'!M11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M11),"",'ONR 1'!M11)</f>
       </c>
       <c r="N9" s="233" t="b">
-        <f t="shared" si="13">IF(ISBLANK('ONR 1'!N11),"",'ONR 1'!N11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N11),"",'ONR 1'!N11)</f>
       </c>
       <c r="O9" s="233" t="b">
-        <f t="shared" si="14">IF(ISBLANK('ONR 1'!O11),"",'ONR 1'!O11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O11),"",'ONR 1'!O11)</f>
       </c>
       <c r="P9" s="233" t="b">
-        <f t="shared" si="15">IF(ISBLANK('ONR 1'!P11),"",'ONR 1'!P11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P11),"",'ONR 1'!P11)</f>
       </c>
       <c r="Q9" s="233" t="b">
-        <f t="shared" si="16">IF(ISBLANK('ONR 1'!Q11),"",'ONR 1'!Q11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q11),"",'ONR 1'!Q11)</f>
       </c>
       <c r="R9" s="233" t="b">
-        <f t="shared" si="17">IF(ISBLANK('ONR 1'!R11),"",'ONR 1'!R11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R11),"",'ONR 1'!R11)</f>
       </c>
       <c r="S9" s="234" t="str">
-        <f t="shared" si="2">IF(ISBLANK('ONR 1'!S11),"",'ONR 1'!S11)</f>
+        <f>IF(ISBLANK('ONR 1'!S11),"",'ONR 1'!S11)</f>
       </c>
       <c r="T9" s="232" t="str">
-        <f t="shared" si="3">IF(ISBLANK('ONR 1'!T11),"",'ONR 1'!T11)</f>
+        <f>IF(ISBLANK('ONR 1'!T11),"",'ONR 1'!T11)</f>
       </c>
       <c r="U9" s="233" t="str">
-        <f t="shared" si="4">IF(ISBLANK('ONR 1'!U11),"",'ONR 1'!U11)</f>
+        <f>IF(ISBLANK('ONR 1'!U11),"",'ONR 1'!U11)</f>
       </c>
       <c r="V9" s="241" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G11),"",'ONR 1'!G11)</f>
+        <f>IF(ISBLANK('ONR 1'!G11),"",'ONR 1'!G11)</f>
       </c>
       <c r="W9" s="241" t="str">
         <f>IF(ISBLANK('ONR 1'!V11),"",'ONR 1'!V11)</f>
@@ -31847,42 +31787,34 @@
         <f>IF(ISBLANK('ONR 1'!W11),"",'ONR 1'!W11)</f>
       </c>
       <c r="Y9" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I11),"",'ONR 1'!I11)</f>
+        <f>IF(ISBLANK('ONR 1'!I11),"",'ONR 1'!I11)</f>
       </c>
       <c r="Z9" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D11),"",'ONR 1'!D11)</f>
+        <f>IF(ISBLANK('ONR 1'!D11),"",'ONR 1'!D11)</f>
       </c>
       <c r="AE9" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T9),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T9),0,1)</f>
       </c>
       <c r="AF9" s="206" t="n">
-        <f t="shared" si="9">IF(L9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L9=TRUE,1,0)</f>
       </c>
       <c r="AG9" s="206" t="n">
-        <f t="shared" si="9">IF(M9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M9=TRUE,1,0)</f>
       </c>
       <c r="AH9" s="206" t="n">
-        <f t="shared" si="9">IF(N9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N9=TRUE,1,0)</f>
       </c>
       <c r="AI9" s="206" t="n">
-        <f t="shared" si="9">IF(O9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O9=TRUE,1,0)</f>
       </c>
       <c r="AJ9" s="206" t="n">
-        <f t="shared" si="9">IF(P9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P9=TRUE,1,0)</f>
       </c>
       <c r="AK9" s="206" t="n">
-        <f t="shared" si="9">IF(Q9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q9=TRUE,1,0)</f>
       </c>
       <c r="AL9" s="206" t="n">
-        <f t="shared" si="9">IF(R9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R9=TRUE,1,0)</f>
       </c>
       <c r="AM9" t="n">
         <f>IF(LEN(TRIM(W9))&gt;0,1,0)</f>
@@ -31918,50 +31850,43 @@
         <f>IF(ISBLANK('ONR 1'!I12),"",'ONR 1'!I12)</f>
       </c>
       <c r="J10" s="232" t="str">
-        <f t="shared" ref="J10:J11" si="18">IF(ISBLANK('ONR 1'!J12),"",'ONR 1'!J12)</f>
+        <f>IF(ISBLANK('ONR 1'!J12),"",'ONR 1'!J12)</f>
       </c>
       <c r="K10" s="233" t="str">
-        <f t="shared" ref="K10:K11" si="19">IF(ISBLANK('ONR 1'!K12),"",'ONR 1'!K12)</f>
+        <f>IF(ISBLANK('ONR 1'!K12),"",'ONR 1'!K12)</f>
       </c>
       <c r="L10" s="233" t="b">
-        <f t="shared" ref="L10:L11" si="20">IF(ISBLANK('ONR 1'!L12),"",'ONR 1'!L12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L12),"",'ONR 1'!L12)</f>
       </c>
       <c r="M10" s="233" t="b">
-        <f t="shared" ref="M10:M11" si="21">IF(ISBLANK('ONR 1'!M12),"",'ONR 1'!M12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M12),"",'ONR 1'!M12)</f>
       </c>
       <c r="N10" s="233" t="b">
-        <f t="shared" ref="N10:N11" si="22">IF(ISBLANK('ONR 1'!N12),"",'ONR 1'!N12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N12),"",'ONR 1'!N12)</f>
       </c>
       <c r="O10" s="233" t="b">
-        <f t="shared" ref="O10:O11" si="23">IF(ISBLANK('ONR 1'!O12),"",'ONR 1'!O12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O12),"",'ONR 1'!O12)</f>
       </c>
       <c r="P10" s="233" t="b">
-        <f t="shared" ref="P10:P11" si="24">IF(ISBLANK('ONR 1'!P12),"",'ONR 1'!P12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P12),"",'ONR 1'!P12)</f>
       </c>
       <c r="Q10" s="233" t="b">
-        <f t="shared" ref="Q10:Q11" si="25">IF(ISBLANK('ONR 1'!Q12),"",'ONR 1'!Q12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q12),"",'ONR 1'!Q12)</f>
       </c>
       <c r="R10" s="233" t="b">
-        <f t="shared" ref="R10:R11" si="26">IF(ISBLANK('ONR 1'!R12),"",'ONR 1'!R12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R12),"",'ONR 1'!R12)</f>
       </c>
       <c r="S10" s="234" t="str">
-        <f t="shared" ref="S10:S11" si="27">IF(ISBLANK('ONR 1'!S12),"",'ONR 1'!S12)</f>
+        <f>IF(ISBLANK('ONR 1'!S12),"",'ONR 1'!S12)</f>
       </c>
       <c r="T10" s="232" t="str">
-        <f t="shared" ref="T10:T11" si="28">IF(ISBLANK('ONR 1'!T12),"",'ONR 1'!T12)</f>
+        <f>IF(ISBLANK('ONR 1'!T12),"",'ONR 1'!T12)</f>
       </c>
       <c r="U10" s="233" t="str">
-        <f t="shared" ref="U10:U11" si="29">IF(ISBLANK('ONR 1'!U12),"",'ONR 1'!U12)</f>
+        <f>IF(ISBLANK('ONR 1'!U12),"",'ONR 1'!U12)</f>
       </c>
       <c r="V10" s="241" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G12),"",'ONR 1'!G12)</f>
+        <f>IF(ISBLANK('ONR 1'!G12),"",'ONR 1'!G12)</f>
       </c>
       <c r="W10" s="241" t="str">
         <f>IF(ISBLANK('ONR 1'!V12),"",'ONR 1'!V12)</f>
@@ -31970,42 +31895,34 @@
         <f>IF(ISBLANK('ONR 1'!W12),"",'ONR 1'!W12)</f>
       </c>
       <c r="Y10" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I12),"",'ONR 1'!I12)</f>
+        <f>IF(ISBLANK('ONR 1'!I12),"",'ONR 1'!I12)</f>
       </c>
       <c r="Z10" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D12),"",'ONR 1'!D12)</f>
+        <f>IF(ISBLANK('ONR 1'!D12),"",'ONR 1'!D12)</f>
       </c>
       <c r="AE10" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T10),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T10),0,1)</f>
       </c>
       <c r="AF10" s="206" t="n">
-        <f t="shared" si="9">IF(L10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L10=TRUE,1,0)</f>
       </c>
       <c r="AG10" s="206" t="n">
-        <f t="shared" si="9">IF(M10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M10=TRUE,1,0)</f>
       </c>
       <c r="AH10" s="206" t="n">
-        <f t="shared" si="9">IF(N10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N10=TRUE,1,0)</f>
       </c>
       <c r="AI10" s="206" t="n">
-        <f t="shared" si="9">IF(O10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O10=TRUE,1,0)</f>
       </c>
       <c r="AJ10" s="206" t="n">
-        <f t="shared" si="9">IF(P10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P10=TRUE,1,0)</f>
       </c>
       <c r="AK10" s="206" t="n">
-        <f t="shared" si="9">IF(Q10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q10=TRUE,1,0)</f>
       </c>
       <c r="AL10" s="206" t="n">
-        <f t="shared" si="9">IF(R10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R10=TRUE,1,0)</f>
       </c>
       <c r="AM10" t="n">
         <f>IF(LEN(TRIM(W10))&gt;0,1,0)</f>
@@ -32041,50 +31958,43 @@
         <f>IF(ISBLANK('ONR 1'!I13),"",'ONR 1'!I13)</f>
       </c>
       <c r="J11" s="232" t="str">
-        <f t="shared" si="18">IF(ISBLANK('ONR 1'!J13),"",'ONR 1'!J13)</f>
+        <f>IF(ISBLANK('ONR 1'!J13),"",'ONR 1'!J13)</f>
       </c>
       <c r="K11" s="233" t="str">
-        <f t="shared" si="19">IF(ISBLANK('ONR 1'!K13),"",'ONR 1'!K13)</f>
+        <f>IF(ISBLANK('ONR 1'!K13),"",'ONR 1'!K13)</f>
       </c>
       <c r="L11" s="233" t="b">
-        <f t="shared" si="20">IF(ISBLANK('ONR 1'!L13),"",'ONR 1'!L13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L13),"",'ONR 1'!L13)</f>
       </c>
       <c r="M11" s="233" t="b">
-        <f t="shared" si="21">IF(ISBLANK('ONR 1'!M13),"",'ONR 1'!M13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M13),"",'ONR 1'!M13)</f>
       </c>
       <c r="N11" s="233" t="b">
-        <f t="shared" si="22">IF(ISBLANK('ONR 1'!N13),"",'ONR 1'!N13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N13),"",'ONR 1'!N13)</f>
       </c>
       <c r="O11" s="233" t="b">
-        <f t="shared" si="23">IF(ISBLANK('ONR 1'!O13),"",'ONR 1'!O13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O13),"",'ONR 1'!O13)</f>
       </c>
       <c r="P11" s="233" t="b">
-        <f t="shared" si="24">IF(ISBLANK('ONR 1'!P13),"",'ONR 1'!P13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P13),"",'ONR 1'!P13)</f>
       </c>
       <c r="Q11" s="233" t="b">
-        <f t="shared" si="25">IF(ISBLANK('ONR 1'!Q13),"",'ONR 1'!Q13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q13),"",'ONR 1'!Q13)</f>
       </c>
       <c r="R11" s="233" t="b">
-        <f t="shared" si="26">IF(ISBLANK('ONR 1'!R13),"",'ONR 1'!R13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R13),"",'ONR 1'!R13)</f>
       </c>
       <c r="S11" s="234" t="str">
-        <f t="shared" si="27">IF(ISBLANK('ONR 1'!S13),"",'ONR 1'!S13)</f>
+        <f>IF(ISBLANK('ONR 1'!S13),"",'ONR 1'!S13)</f>
       </c>
       <c r="T11" s="232" t="str">
-        <f t="shared" si="28">IF(ISBLANK('ONR 1'!T13),"",'ONR 1'!T13)</f>
+        <f>IF(ISBLANK('ONR 1'!T13),"",'ONR 1'!T13)</f>
       </c>
       <c r="U11" s="233" t="str">
-        <f t="shared" si="29">IF(ISBLANK('ONR 1'!U13),"",'ONR 1'!U13)</f>
+        <f>IF(ISBLANK('ONR 1'!U13),"",'ONR 1'!U13)</f>
       </c>
       <c r="V11" s="241" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G13),"",'ONR 1'!G13)</f>
+        <f>IF(ISBLANK('ONR 1'!G13),"",'ONR 1'!G13)</f>
       </c>
       <c r="W11" s="241" t="str">
         <f>IF(ISBLANK('ONR 1'!V13),"",'ONR 1'!V13)</f>
@@ -32093,42 +32003,34 @@
         <f>IF(ISBLANK('ONR 1'!W13),"",'ONR 1'!W13)</f>
       </c>
       <c r="Y11" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I13),"",'ONR 1'!I13)</f>
+        <f>IF(ISBLANK('ONR 1'!I13),"",'ONR 1'!I13)</f>
       </c>
       <c r="Z11" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D13),"",'ONR 1'!D13)</f>
+        <f>IF(ISBLANK('ONR 1'!D13),"",'ONR 1'!D13)</f>
       </c>
       <c r="AE11" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T11),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T11),0,1)</f>
       </c>
       <c r="AF11" s="206" t="n">
-        <f t="shared" si="9">IF(L11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L11=TRUE,1,0)</f>
       </c>
       <c r="AG11" s="206" t="n">
-        <f t="shared" si="9">IF(M11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M11=TRUE,1,0)</f>
       </c>
       <c r="AH11" s="206" t="n">
-        <f t="shared" si="9">IF(N11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N11=TRUE,1,0)</f>
       </c>
       <c r="AI11" s="206" t="n">
-        <f t="shared" si="9">IF(O11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O11=TRUE,1,0)</f>
       </c>
       <c r="AJ11" s="206" t="n">
-        <f t="shared" si="9">IF(P11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P11=TRUE,1,0)</f>
       </c>
       <c r="AK11" s="206" t="n">
-        <f t="shared" si="9">IF(Q11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q11=TRUE,1,0)</f>
       </c>
       <c r="AL11" s="206" t="n">
-        <f t="shared" si="9">IF(R11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R11=TRUE,1,0)</f>
       </c>
       <c r="AM11" t="n">
         <f>IF(LEN(TRIM(W11))&gt;0,1,0)</f>
@@ -32366,7 +32268,7 @@
         <f>IF(ISBLANK('ONR 2'!J7),"",'ONR 2'!J7)</f>
       </c>
       <c r="K14" s="227" t="str">
-        <f t="shared" ref="K14" si="31">IF(ISBLANK('ONR 2'!K7),"",'ONR 2'!K7)</f>
+        <f>IF(ISBLANK('ONR 2'!K7),"",'ONR 2'!K7)</f>
       </c>
       <c r="L14" s="227" t="b">
         <f>IF(ISBLANK('ONR 2'!L7),"",'ONR 2'!L7)</f>
@@ -32397,13 +32299,13 @@
         <v>0</v>
       </c>
       <c r="S14" s="228" t="str">
-        <f t="shared" ref="S14" si="32">IF(ISBLANK('ONR 2'!S7),"",'ONR 2'!S7)</f>
+        <f>IF(ISBLANK('ONR 2'!S7),"",'ONR 2'!S7)</f>
       </c>
       <c r="T14" s="226" t="str">
-        <f t="shared" ref="T14" si="33">IF(ISBLANK('ONR 2'!T7),"",'ONR 2'!T7)</f>
+        <f>IF(ISBLANK('ONR 2'!T7),"",'ONR 2'!T7)</f>
       </c>
       <c r="U14" s="242" t="str">
-        <f t="shared" ref="U14" si="34">IF(ISBLANK('ONR 2'!U7),"",'ONR 2'!U7)</f>
+        <f>IF(ISBLANK('ONR 2'!U7),"",'ONR 2'!U7)</f>
       </c>
       <c r="V14" s="229" t="str">
         <f>IF(ISBLANK('ONR 2'!G7),"",'ONR 2'!G7)</f>
@@ -32425,32 +32327,25 @@
         <v>1</v>
       </c>
       <c r="AF14" s="206" t="n">
-        <f t="shared" ref="AF14:AL17" si="35">IF(L14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L14=TRUE,1,0)</f>
       </c>
       <c r="AG14" s="206" t="n">
-        <f t="shared" si="35">IF(M14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M14=TRUE,1,0)</f>
       </c>
       <c r="AH14" s="206" t="n">
-        <f t="shared" si="35">IF(N14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N14=TRUE,1,0)</f>
       </c>
       <c r="AI14" s="206" t="n">
-        <f t="shared" si="35">IF(O14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O14=TRUE,1,0)</f>
       </c>
       <c r="AJ14" s="206" t="n">
-        <f t="shared" si="35">IF(P14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P14=TRUE,1,0)</f>
       </c>
       <c r="AK14" s="206" t="n">
-        <f t="shared" si="35">IF(Q14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q14=TRUE,1,0)</f>
       </c>
       <c r="AL14" s="206" t="n">
-        <f t="shared" si="35">IF(R14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R14=TRUE,1,0)</f>
       </c>
       <c r="AM14" t="n">
         <f>IF(LEN(TRIM(W14))&gt;0,1,0)</f>
@@ -32486,47 +32381,40 @@
         <f>IF(ISBLANK('ONR 2'!I8),"",'ONR 2'!I8)</f>
       </c>
       <c r="J15" s="218" t="str">
-        <f t="shared" ref="J15:J17" si="36">IF(ISBLANK('ONR 2'!J8),"",'ONR 2'!J8)</f>
+        <f>IF(ISBLANK('ONR 2'!J8),"",'ONR 2'!J8)</f>
       </c>
       <c r="K15" s="227" t="str">
-        <f t="shared" ref="K15:K17" si="37">IF(ISBLANK('ONR 2'!K8),"",'ONR 2'!K8)</f>
+        <f>IF(ISBLANK('ONR 2'!K8),"",'ONR 2'!K8)</f>
       </c>
       <c r="L15" s="227" t="b">
-        <f t="shared" ref="L15:L17" si="38">IF(ISBLANK('ONR 2'!L8),"",'ONR 2'!L8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!L8),"",'ONR 2'!L8)</f>
       </c>
       <c r="M15" s="227" t="b">
-        <f t="shared" ref="M15:M17" si="39">IF(ISBLANK('ONR 2'!M8),"",'ONR 2'!M8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!M8),"",'ONR 2'!M8)</f>
       </c>
       <c r="N15" s="227" t="b">
-        <f t="shared" ref="N15:N17" si="40">IF(ISBLANK('ONR 2'!N8),"",'ONR 2'!N8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!N8),"",'ONR 2'!N8)</f>
       </c>
       <c r="O15" s="227" t="b">
-        <f t="shared" ref="O15:O17" si="41">IF(ISBLANK('ONR 2'!O8),"",'ONR 2'!O8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!O8),"",'ONR 2'!O8)</f>
       </c>
       <c r="P15" s="227" t="b">
-        <f t="shared" ref="P15:P17" si="42">IF(ISBLANK('ONR 2'!P8),"",'ONR 2'!P8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!P8),"",'ONR 2'!P8)</f>
       </c>
       <c r="Q15" s="227" t="b">
-        <f t="shared" ref="Q15:Q17" si="43">IF(ISBLANK('ONR 2'!Q8),"",'ONR 2'!Q8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!Q8),"",'ONR 2'!Q8)</f>
       </c>
       <c r="R15" s="227" t="b">
-        <f t="shared" ref="R15:R17" si="44">IF(ISBLANK('ONR 2'!R8),"",'ONR 2'!R8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!R8),"",'ONR 2'!R8)</f>
       </c>
       <c r="S15" s="228" t="str">
-        <f t="shared" ref="S15:S17" si="45">IF(ISBLANK('ONR 2'!S8),"",'ONR 2'!S8)</f>
+        <f>IF(ISBLANK('ONR 2'!S8),"",'ONR 2'!S8)</f>
       </c>
       <c r="T15" s="226" t="str">
-        <f t="shared" ref="T15:T17" si="46">IF(ISBLANK('ONR 2'!T8),"",'ONR 2'!T8)</f>
+        <f>IF(ISBLANK('ONR 2'!T8),"",'ONR 2'!T8)</f>
       </c>
       <c r="U15" s="242" t="str">
-        <f t="shared" ref="U15:U17" si="47">IF(ISBLANK('ONR 2'!U8),"",'ONR 2'!U8)</f>
+        <f>IF(ISBLANK('ONR 2'!U8),"",'ONR 2'!U8)</f>
       </c>
       <c r="V15" s="229" t="str">
         <f>IF(ISBLANK('ONR 2'!G8),"",'ONR 2'!G8)</f>
@@ -32548,32 +32436,25 @@
         <v>1</v>
       </c>
       <c r="AF15" s="206" t="n">
-        <f t="shared" si="35">IF(L15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L15=TRUE,1,0)</f>
       </c>
       <c r="AG15" s="206" t="n">
-        <f t="shared" si="35">IF(M15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M15=TRUE,1,0)</f>
       </c>
       <c r="AH15" s="206" t="n">
-        <f t="shared" si="35">IF(N15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N15=TRUE,1,0)</f>
       </c>
       <c r="AI15" s="206" t="n">
-        <f t="shared" si="35">IF(O15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O15=TRUE,1,0)</f>
       </c>
       <c r="AJ15" s="206" t="n">
-        <f t="shared" si="35">IF(P15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P15=TRUE,1,0)</f>
       </c>
       <c r="AK15" s="206" t="n">
-        <f t="shared" si="35">IF(Q15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q15=TRUE,1,0)</f>
       </c>
       <c r="AL15" s="206" t="n">
-        <f t="shared" si="35">IF(R15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R15=TRUE,1,0)</f>
       </c>
       <c r="AM15" t="n">
         <f>IF(LEN(TRIM(W15))&gt;0,1,0)</f>
@@ -32609,90 +32490,47 @@
         <f>IF(ISBLANK('ONR 2'!I9),"",'ONR 2'!I9)</f>
       </c>
       <c r="J16" s="218" t="str">
-        <f t="shared" si="36">IF(ISBLANK('ONR 2'!J9),"",'ONR 2'!J9)</f>
-      </c>
-      <c r="K17" s="227" t="str">
-        <f t="shared" si="37">IF(ISBLANK('ONR 2'!K10),"",'ONR 2'!K10)</f>
+        <f>IF(ISBLANK('ONR 2'!J9),"",'ONR 2'!J9)</f>
       </c>
       <c r="K16" t="str" s="227">
         <f>IF(ISBLANK('ONR 2'!K9),"",'ONR 2'!K9)</f>
-      </c>
-      <c r="L17" s="227" t="b">
-        <f t="shared" si="38">IF(ISBLANK('ONR 2'!L10),"",'ONR 2'!L10)</f>
-        <v>0</v>
       </c>
       <c r="L16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!L9),"",'ONR 2'!L9)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="227" t="b">
-        <f t="shared" si="39">IF(ISBLANK('ONR 2'!M10),"",'ONR 2'!M10)</f>
-        <v>0</v>
-      </c>
       <c r="M16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!M9),"",'ONR 2'!M9)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="227" t="b">
-        <f t="shared" si="40">IF(ISBLANK('ONR 2'!N10),"",'ONR 2'!N10)</f>
-        <v>0</v>
-      </c>
       <c r="N16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!N9),"",'ONR 2'!N9)</f>
         <v>0</v>
       </c>
-      <c r="O17" s="227" t="b">
-        <f t="shared" si="41">IF(ISBLANK('ONR 2'!O10),"",'ONR 2'!O10)</f>
-        <v>0</v>
-      </c>
       <c r="O16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!O9),"",'ONR 2'!O9)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="227" t="b">
-        <f t="shared" si="42">IF(ISBLANK('ONR 2'!P10),"",'ONR 2'!P10)</f>
-        <v>0</v>
-      </c>
       <c r="P16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!P9),"",'ONR 2'!P9)</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="227" t="b">
-        <f t="shared" si="43">IF(ISBLANK('ONR 2'!Q10),"",'ONR 2'!Q10)</f>
-        <v>0</v>
-      </c>
       <c r="Q16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!Q9),"",'ONR 2'!Q9)</f>
         <v>0</v>
       </c>
-      <c r="R17" s="227" t="b">
-        <f t="shared" si="44">IF(ISBLANK('ONR 2'!R10),"",'ONR 2'!R10)</f>
-        <v>0</v>
-      </c>
       <c r="R16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!R9),"",'ONR 2'!R9)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="228" t="str">
-        <f t="shared" si="45">IF(ISBLANK('ONR 2'!S10),"",'ONR 2'!S10)</f>
-      </c>
       <c r="S16" t="str" s="228">
         <f>IF(ISBLANK('ONR 2'!S9),"",'ONR 2'!S9)</f>
       </c>
-      <c r="T17" s="226" t="str">
-        <f t="shared" si="46">IF(ISBLANK('ONR 2'!T10),"",'ONR 2'!T10)</f>
-      </c>
       <c r="T16" t="str" s="226">
         <f>IF(ISBLANK('ONR 2'!T9),"",'ONR 2'!T9)</f>
       </c>
-      <c r="U17" s="242" t="str">
-        <f t="shared" si="47">IF(ISBLANK('ONR 2'!U10),"",'ONR 2'!U10)</f>
-      </c>
       <c r="U16" t="str" s="242">
         <f>IF(ISBLANK('ONR 2'!U9),"",'ONR 2'!U9)</f>
-      </c>
-      <c r="V17" s="229" t="str">
-        <f>IF(ISBLANK('ONR 2'!G10),"",'ONR 2'!G10)</f>
       </c>
       <c r="V16" t="str" s="229">
         <f>IF(ISBLANK('ONR 2'!G9),"",'ONR 2'!G9)</f>
@@ -32714,32 +32552,25 @@
         <v>1</v>
       </c>
       <c r="AF16" s="206" t="n">
-        <f t="shared" si="35">IF(L16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L16=TRUE,1,0)</f>
       </c>
       <c r="AG16" s="206" t="n">
-        <f t="shared" si="35">IF(M16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M16=TRUE,1,0)</f>
       </c>
       <c r="AH16" s="206" t="n">
-        <f t="shared" si="35">IF(N16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N16=TRUE,1,0)</f>
       </c>
       <c r="AI16" s="206" t="n">
-        <f t="shared" si="35">IF(O16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O16=TRUE,1,0)</f>
       </c>
       <c r="AJ16" s="206" t="n">
-        <f t="shared" si="35">IF(P16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P16=TRUE,1,0)</f>
       </c>
       <c r="AK16" s="206" t="n">
-        <f t="shared" si="35">IF(Q16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q16=TRUE,1,0)</f>
       </c>
       <c r="AL16" s="206" t="n">
-        <f t="shared" si="35">IF(R16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R16=TRUE,1,0)</f>
       </c>
       <c r="AM16" t="n">
         <f>IF(LEN(TRIM(W16))&gt;0,1,0)</f>
@@ -32775,43 +32606,43 @@
         <f>IF(ISBLANK('ONR 2'!I10),"",'ONR 2'!I10)</f>
       </c>
       <c r="J17" s="218" t="str">
-        <f t="shared" si="36">IF(ISBLANK('ONR 2'!J10),"",'ONR 2'!J10)</f>
-      </c>
-      <c r="K19" s="227">
-        <f t="shared" si="37"/>
-      </c>
-      <c r="L19" s="227">
-        <f t="shared" si="38"/>
-      </c>
-      <c r="M19" s="227">
-        <f t="shared" si="39"/>
-      </c>
-      <c r="N19" s="227">
-        <f t="shared" si="40"/>
-      </c>
-      <c r="O19" s="227">
-        <f t="shared" si="41"/>
-      </c>
-      <c r="P19" s="227">
-        <f t="shared" si="42"/>
-      </c>
-      <c r="Q19" s="227">
-        <f t="shared" si="43"/>
-      </c>
-      <c r="R19" s="227">
-        <f t="shared" si="44"/>
-      </c>
-      <c r="S19" s="228">
-        <f t="shared" si="45"/>
-      </c>
-      <c r="T19" s="226">
-        <f t="shared" si="46"/>
-      </c>
-      <c r="U19" s="242">
-        <f t="shared" si="47"/>
-      </c>
-      <c r="V19" s="229">
-        <f>G17</f>
+        <f>IF(ISBLANK('ONR 2'!J10),"",'ONR 2'!J10)</f>
+      </c>
+      <c r="K17" s="227" t="str">
+        <f>IF(ISBLANK('ONR 2'!K10),"",'ONR 2'!K10)</f>
+      </c>
+      <c r="L17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!L10),"",'ONR 2'!L10)</f>
+      </c>
+      <c r="M17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!M10),"",'ONR 2'!M10)</f>
+      </c>
+      <c r="N17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!N10),"",'ONR 2'!N10)</f>
+      </c>
+      <c r="O17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!O10),"",'ONR 2'!O10)</f>
+      </c>
+      <c r="P17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!P10),"",'ONR 2'!P10)</f>
+      </c>
+      <c r="Q17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!Q10),"",'ONR 2'!Q10)</f>
+      </c>
+      <c r="R17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!R10),"",'ONR 2'!R10)</f>
+      </c>
+      <c r="S17" s="228" t="str">
+        <f>IF(ISBLANK('ONR 2'!S10),"",'ONR 2'!S10)</f>
+      </c>
+      <c r="T17" s="226" t="str">
+        <f>IF(ISBLANK('ONR 2'!T10),"",'ONR 2'!T10)</f>
+      </c>
+      <c r="U17" s="242" t="str">
+        <f>IF(ISBLANK('ONR 2'!U10),"",'ONR 2'!U10)</f>
+      </c>
+      <c r="V17" s="229" t="str">
+        <f>IF(ISBLANK('ONR 2'!G10),"",'ONR 2'!G10)</f>
       </c>
       <c r="W17" s="229" t="str">
         <f>IF(ISBLANK('ONR 2'!V10),"",'ONR 2'!V10)</f>
@@ -32830,32 +32661,25 @@
         <v>1</v>
       </c>
       <c r="AF17" s="206" t="n">
-        <f t="shared" si="35">IF(L17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L17=TRUE,1,0)</f>
       </c>
       <c r="AG17" s="206" t="n">
-        <f t="shared" si="35">IF(M17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M17=TRUE,1,0)</f>
       </c>
       <c r="AH17" s="206" t="n">
-        <f t="shared" si="35">IF(N17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N17=TRUE,1,0)</f>
       </c>
       <c r="AI17" s="206" t="n">
-        <f t="shared" si="35">IF(O17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O17=TRUE,1,0)</f>
       </c>
       <c r="AJ17" s="206" t="n">
-        <f t="shared" si="35">IF(P17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P17=TRUE,1,0)</f>
       </c>
       <c r="AK17" s="206" t="n">
-        <f t="shared" si="35">IF(Q17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q17=TRUE,1,0)</f>
       </c>
       <c r="AL17" s="206" t="n">
-        <f t="shared" si="35">IF(R17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R17=TRUE,1,0)</f>
       </c>
       <c r="AM17" t="n">
         <f>IF(LEN(TRIM(W17))&gt;0,1,0)</f>
@@ -33090,50 +32914,43 @@
         <f>IF(ISBLANK('ONR 3'!I7),"",'ONR 3'!I7)</f>
       </c>
       <c r="J20" s="246" t="str">
-        <f t="shared" ref="J20:J25" si="49">IF(ISBLANK('ONR 3'!J7),"",'ONR 3'!J7)</f>
+        <f>IF(ISBLANK('ONR 3'!J7),"",'ONR 3'!J7)</f>
       </c>
       <c r="K20" s="247" t="str">
-        <f t="shared" ref="K20:K25" si="50">IF(ISBLANK('ONR 3'!K7),"",'ONR 3'!K7)</f>
+        <f>IF(ISBLANK('ONR 3'!K7),"",'ONR 3'!K7)</f>
       </c>
       <c r="L20" s="247" t="b">
-        <f t="shared" ref="L20:L25" si="51">IF(ISBLANK('ONR 3'!L7),"",'ONR 3'!L7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!L7),"",'ONR 3'!L7)</f>
       </c>
       <c r="M20" s="247" t="b">
-        <f t="shared" ref="M20:M25" si="52">IF(ISBLANK('ONR 3'!M7),"",'ONR 3'!M7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!M7),"",'ONR 3'!M7)</f>
       </c>
       <c r="N20" s="247" t="b">
-        <f t="shared" ref="N20:N25" si="53">IF(ISBLANK('ONR 3'!N7),"",'ONR 3'!N7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!N7),"",'ONR 3'!N7)</f>
       </c>
       <c r="O20" s="247" t="b">
-        <f t="shared" ref="O20:O25" si="54">IF(ISBLANK('ONR 3'!O7),"",'ONR 3'!O7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!O7),"",'ONR 3'!O7)</f>
       </c>
       <c r="P20" s="247" t="b">
-        <f t="shared" ref="P20:P25" si="55">IF(ISBLANK('ONR 3'!P7),"",'ONR 3'!P7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!P7),"",'ONR 3'!P7)</f>
       </c>
       <c r="Q20" s="247" t="b">
-        <f t="shared" ref="Q20:Q25" si="56">IF(ISBLANK('ONR 3'!Q7),"",'ONR 3'!Q7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!Q7),"",'ONR 3'!Q7)</f>
       </c>
       <c r="R20" s="247" t="b">
-        <f t="shared" ref="R20:R25" si="57">IF(ISBLANK('ONR 3'!R7),"",'ONR 3'!R7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!R7),"",'ONR 3'!R7)</f>
       </c>
       <c r="S20" s="248" t="str">
-        <f t="shared" ref="S20:S25" si="58">IF(ISBLANK('ONR 3'!S7),"",'ONR 3'!S7)</f>
+        <f>IF(ISBLANK('ONR 3'!S7),"",'ONR 3'!S7)</f>
       </c>
       <c r="T20" s="249" t="str">
-        <f t="shared" ref="T20:T25" si="59">IF(ISBLANK('ONR 3'!T7),"",'ONR 3'!T7)</f>
+        <f>IF(ISBLANK('ONR 3'!T7),"",'ONR 3'!T7)</f>
       </c>
       <c r="U20" s="250" t="str">
-        <f t="shared" ref="U20:U25" si="60">IF(ISBLANK('ONR 3'!U7),"",'ONR 3'!U7)</f>
+        <f>IF(ISBLANK('ONR 3'!U7),"",'ONR 3'!U7)</f>
       </c>
       <c r="V20" s="235" t="str">
-        <f t="shared" ref="V20:V26" si="61">IF(ISBLANK('ONR 3'!G7),"",'ONR 3'!G7)</f>
+        <f>IF(ISBLANK('ONR 3'!G7),"",'ONR 3'!G7)</f>
       </c>
       <c r="W20" s="235" t="str">
         <f>IF(ISBLANK('ONR 3'!V7),"",'ONR 3'!V7)</f>
@@ -33142,42 +32959,34 @@
         <f>IF(ISBLANK('ONR 3'!W7),"",'ONR 3'!W7)</f>
       </c>
       <c r="Y20" s="236" t="str">
-        <f t="shared" ref="Y20:Y26" si="62">IF(ISBLANK('ONR 3'!I7),"",'ONR 3'!I7)</f>
+        <f>IF(ISBLANK('ONR 3'!I7),"",'ONR 3'!I7)</f>
       </c>
       <c r="Z20" s="236" t="str">
-        <f t="shared" ref="Z20:Z26" si="63">IF(ISBLANK('ONR 3'!D7),"",'ONR 3'!D7)</f>
+        <f>IF(ISBLANK('ONR 3'!D7),"",'ONR 3'!D7)</f>
       </c>
       <c r="AE20" s="206" t="n">
-        <f t="shared" ref="AE20:AE26" si="64">IF(ISNUMBER(T20),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T20),0,1)</f>
       </c>
       <c r="AF20" s="206" t="n">
-        <f t="shared" ref="AF20:AL26" si="65">IF(L20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L20=TRUE,1,0)</f>
       </c>
       <c r="AG20" s="206" t="n">
-        <f t="shared" si="65">IF(M20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M20=TRUE,1,0)</f>
       </c>
       <c r="AH20" s="206" t="n">
-        <f t="shared" si="65">IF(N20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N20=TRUE,1,0)</f>
       </c>
       <c r="AI20" s="206" t="n">
-        <f t="shared" si="65">IF(O20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O20=TRUE,1,0)</f>
       </c>
       <c r="AJ20" s="206" t="n">
-        <f t="shared" si="65">IF(P20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P20=TRUE,1,0)</f>
       </c>
       <c r="AK20" s="206" t="n">
-        <f t="shared" si="65">IF(Q20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q20=TRUE,1,0)</f>
       </c>
       <c r="AL20" s="206" t="n">
-        <f t="shared" si="65">IF(R20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R20=TRUE,1,0)</f>
       </c>
       <c r="AM20" t="n">
         <f>IF(LEN(TRIM(W20))&gt;0,1,0)</f>
@@ -33213,97 +33022,51 @@
         <f>IF(ISBLANK('ONR 3'!I8),"",'ONR 3'!I8)</f>
       </c>
       <c r="J21" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J8),"",'ONR 3'!J8)</f>
-      </c>
-      <c r="K23" s="247" t="str">
-        <f t="shared" si="50">IF(ISBLANK('ONR 3'!K10),"",'ONR 3'!K10)</f>
+        <f>IF(ISBLANK('ONR 3'!J8),"",'ONR 3'!J8)</f>
       </c>
       <c r="K21" t="str" s="247">
         <f>IF(ISBLANK('ONR 3'!K8),"",'ONR 3'!K8)</f>
-      </c>
-      <c r="L23" s="247" t="b">
-        <f t="shared" si="51">IF(ISBLANK('ONR 3'!L10),"",'ONR 3'!L10)</f>
-        <v>0</v>
       </c>
       <c r="L21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!L8),"",'ONR 3'!L8)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="247" t="b">
-        <f t="shared" si="52">IF(ISBLANK('ONR 3'!M10),"",'ONR 3'!M10)</f>
-        <v>0</v>
-      </c>
       <c r="M21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!M8),"",'ONR 3'!M8)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="247" t="b">
-        <f t="shared" si="53">IF(ISBLANK('ONR 3'!N10),"",'ONR 3'!N10)</f>
-        <v>0</v>
-      </c>
       <c r="N21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!N8),"",'ONR 3'!N8)</f>
         <v>0</v>
       </c>
-      <c r="O23" s="247" t="b">
-        <f t="shared" si="54">IF(ISBLANK('ONR 3'!O10),"",'ONR 3'!O10)</f>
-        <v>0</v>
-      </c>
       <c r="O21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!O8),"",'ONR 3'!O8)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="247" t="b">
-        <f t="shared" si="55">IF(ISBLANK('ONR 3'!P10),"",'ONR 3'!P10)</f>
-        <v>0</v>
-      </c>
       <c r="P21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!P8),"",'ONR 3'!P8)</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="247" t="b">
-        <f t="shared" si="56">IF(ISBLANK('ONR 3'!Q10),"",'ONR 3'!Q10)</f>
-        <v>0</v>
-      </c>
       <c r="Q21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!Q8),"",'ONR 3'!Q8)</f>
         <v>0</v>
       </c>
-      <c r="R23" s="247" t="b">
-        <f t="shared" si="57">IF(ISBLANK('ONR 3'!R10),"",'ONR 3'!R10)</f>
-        <v>0</v>
-      </c>
       <c r="R21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!R8),"",'ONR 3'!R8)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="248" t="str">
-        <f t="shared" si="58">IF(ISBLANK('ONR 3'!S10),"",'ONR 3'!S10)</f>
-      </c>
       <c r="S21" t="str" s="248">
         <f>IF(ISBLANK('ONR 3'!S8),"",'ONR 3'!S8)</f>
       </c>
-      <c r="T23" s="249" t="str">
-        <f t="shared" si="59">IF(ISBLANK('ONR 3'!T10),"",'ONR 3'!T10)</f>
-      </c>
       <c r="T21" t="str" s="249">
         <f>IF(ISBLANK('ONR 3'!T8),"",'ONR 3'!T8)</f>
       </c>
-      <c r="U23" s="250" t="str">
-        <f t="shared" si="60">IF(ISBLANK('ONR 3'!U10),"",'ONR 3'!U10)</f>
-      </c>
       <c r="U21" t="str" s="250">
         <f>IF(ISBLANK('ONR 3'!U8),"",'ONR 3'!U8)</f>
       </c>
-      <c r="V23" s="235" t="str">
-        <f t="shared" si="61">IF(ISBLANK('ONR 3'!G10),"",'ONR 3'!G10)</f>
-      </c>
       <c r="V21" t="str" s="235">
         <f>IF(ISBLANK('ONR 3'!G8),"",'ONR 3'!G8)</f>
       </c>
-      <c r="W23" s="235" t="str">
-        <f>IF(ISBLANK('ONR 3'!V10),"",'ONR 3'!V10)</f>
-      </c>
       <c r="W21" t="str" s="235">
         <f>IF(ISBLANK('ONR 3'!V8),"",'ONR 3'!V8)</f>
       </c>
@@ -33311,42 +33074,34 @@
         <f>IF(ISBLANK('ONR 3'!W8),"",'ONR 3'!W8)</f>
       </c>
       <c r="Y21" s="236" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I8),"",'ONR 3'!I8)</f>
+        <f>IF(ISBLANK('ONR 3'!I8),"",'ONR 3'!I8)</f>
       </c>
       <c r="Z21" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D8),"",'ONR 3'!D8)</f>
+        <f>IF(ISBLANK('ONR 3'!D8),"",'ONR 3'!D8)</f>
       </c>
       <c r="AE21" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T21),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T21),0,1)</f>
       </c>
       <c r="AF21" s="206" t="n">
-        <f t="shared" si="65">IF(L21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L21=TRUE,1,0)</f>
       </c>
       <c r="AG21" s="206" t="n">
-        <f t="shared" si="65">IF(M21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M21=TRUE,1,0)</f>
       </c>
       <c r="AH21" s="206" t="n">
-        <f t="shared" si="65">IF(N21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N21=TRUE,1,0)</f>
       </c>
       <c r="AI21" s="206" t="n">
-        <f t="shared" si="65">IF(O21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O21=TRUE,1,0)</f>
       </c>
       <c r="AJ21" s="206" t="n">
-        <f t="shared" si="65">IF(P21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P21=TRUE,1,0)</f>
       </c>
       <c r="AK21" s="206" t="n">
-        <f t="shared" si="65">IF(Q21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q21=TRUE,1,0)</f>
       </c>
       <c r="AL21" s="206" t="n">
-        <f t="shared" si="65">IF(R21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R21=TRUE,1,0)</f>
       </c>
       <c r="AM21" t="n">
         <f>IF(LEN(TRIM(W21))&gt;0,1,0)</f>
@@ -33382,97 +33137,51 @@
         <f>IF(ISBLANK('ONR 3'!I9),"",'ONR 3'!I9)</f>
       </c>
       <c r="J22" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J9),"",'ONR 3'!J9)</f>
-      </c>
-      <c r="K24" s="247" t="str">
-        <f t="shared" si="50">IF(ISBLANK('ONR 3'!K11),"",'ONR 3'!K11)</f>
+        <f>IF(ISBLANK('ONR 3'!J9),"",'ONR 3'!J9)</f>
       </c>
       <c r="K22" t="str" s="247">
         <f>IF(ISBLANK('ONR 3'!K9),"",'ONR 3'!K9)</f>
-      </c>
-      <c r="L24" s="247" t="b">
-        <f t="shared" si="51">IF(ISBLANK('ONR 3'!L11),"",'ONR 3'!L11)</f>
-        <v>0</v>
       </c>
       <c r="L22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!L9),"",'ONR 3'!L9)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="247" t="b">
-        <f t="shared" si="52">IF(ISBLANK('ONR 3'!M11),"",'ONR 3'!M11)</f>
-        <v>0</v>
-      </c>
       <c r="M22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!M9),"",'ONR 3'!M9)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="247" t="b">
-        <f t="shared" si="53">IF(ISBLANK('ONR 3'!N11),"",'ONR 3'!N11)</f>
-        <v>0</v>
-      </c>
       <c r="N22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!N9),"",'ONR 3'!N9)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="247" t="b">
-        <f t="shared" si="54">IF(ISBLANK('ONR 3'!O11),"",'ONR 3'!O11)</f>
-        <v>0</v>
-      </c>
       <c r="O22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!O9),"",'ONR 3'!O9)</f>
         <v>0</v>
       </c>
-      <c r="P24" s="247" t="b">
-        <f t="shared" si="55">IF(ISBLANK('ONR 3'!P11),"",'ONR 3'!P11)</f>
-        <v>0</v>
-      </c>
       <c r="P22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!P9),"",'ONR 3'!P9)</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="247" t="b">
-        <f t="shared" si="56">IF(ISBLANK('ONR 3'!Q11),"",'ONR 3'!Q11)</f>
-        <v>0</v>
-      </c>
       <c r="Q22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!Q9),"",'ONR 3'!Q9)</f>
         <v>0</v>
       </c>
-      <c r="R24" s="247" t="b">
-        <f t="shared" si="57">IF(ISBLANK('ONR 3'!R11),"",'ONR 3'!R11)</f>
-        <v>0</v>
-      </c>
       <c r="R22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!R9),"",'ONR 3'!R9)</f>
         <v>0</v>
       </c>
-      <c r="S24" s="248" t="str">
-        <f t="shared" si="58">IF(ISBLANK('ONR 3'!S11),"",'ONR 3'!S11)</f>
-      </c>
       <c r="S22" t="str" s="248">
         <f>IF(ISBLANK('ONR 3'!S9),"",'ONR 3'!S9)</f>
       </c>
-      <c r="T24" s="249" t="str">
-        <f t="shared" si="59">IF(ISBLANK('ONR 3'!T11),"",'ONR 3'!T11)</f>
-      </c>
       <c r="T22" t="str" s="249">
         <f>IF(ISBLANK('ONR 3'!T9),"",'ONR 3'!T9)</f>
       </c>
-      <c r="U24" s="250" t="str">
-        <f t="shared" si="60">IF(ISBLANK('ONR 3'!U11),"",'ONR 3'!U11)</f>
-      </c>
       <c r="U22" t="str" s="250">
         <f>IF(ISBLANK('ONR 3'!U9),"",'ONR 3'!U9)</f>
       </c>
-      <c r="V24" s="235" t="str">
-        <f t="shared" si="61">IF(ISBLANK('ONR 3'!G11),"",'ONR 3'!G11)</f>
-      </c>
       <c r="V22" t="str" s="235">
         <f>IF(ISBLANK('ONR 3'!G9),"",'ONR 3'!G9)</f>
       </c>
-      <c r="W24" s="235" t="str">
-        <f>IF(ISBLANK('ONR 3'!V11),"",'ONR 3'!V11)</f>
-      </c>
       <c r="W22" t="str" s="235">
         <f>IF(ISBLANK('ONR 3'!V9),"",'ONR 3'!V9)</f>
       </c>
@@ -33480,42 +33189,34 @@
         <f>IF(ISBLANK('ONR 3'!W9),"",'ONR 3'!W9)</f>
       </c>
       <c r="Y22" s="236" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I9),"",'ONR 3'!I9)</f>
+        <f>IF(ISBLANK('ONR 3'!I9),"",'ONR 3'!I9)</f>
       </c>
       <c r="Z22" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D9),"",'ONR 3'!D9)</f>
+        <f>IF(ISBLANK('ONR 3'!D9),"",'ONR 3'!D9)</f>
       </c>
       <c r="AE22" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T22),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T22),0,1)</f>
       </c>
       <c r="AF22" s="206" t="n">
-        <f t="shared" si="65">IF(L22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L22=TRUE,1,0)</f>
       </c>
       <c r="AG22" s="206" t="n">
-        <f t="shared" si="65">IF(M22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M22=TRUE,1,0)</f>
       </c>
       <c r="AH22" s="206" t="n">
-        <f t="shared" si="65">IF(N22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N22=TRUE,1,0)</f>
       </c>
       <c r="AI22" s="206" t="n">
-        <f t="shared" si="65">IF(O22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O22=TRUE,1,0)</f>
       </c>
       <c r="AJ22" s="206" t="n">
-        <f t="shared" si="65">IF(P22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P22=TRUE,1,0)</f>
       </c>
       <c r="AK22" s="206" t="n">
-        <f t="shared" si="65">IF(Q22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q22=TRUE,1,0)</f>
       </c>
       <c r="AL22" s="206" t="n">
-        <f t="shared" si="65">IF(R22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R22=TRUE,1,0)</f>
       </c>
       <c r="AM22" t="n">
         <f>IF(LEN(TRIM(W22))&gt;0,1,0)</f>
@@ -33551,94 +33252,79 @@
         <f>IF(ISBLANK('ONR 3'!I10),"",'ONR 3'!I10)</f>
       </c>
       <c r="J23" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J10),"",'ONR 3'!J10)</f>
-      </c>
-      <c r="K25" s="247" t="str">
-        <f t="shared" si="50">IF(ISBLANK('ONR 3'!K12),"",'ONR 3'!K12)</f>
-      </c>
-      <c r="L25" s="247" t="b">
-        <f t="shared" si="51">IF(ISBLANK('ONR 3'!L12),"",'ONR 3'!L12)</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="247" t="b">
-        <f t="shared" si="52">IF(ISBLANK('ONR 3'!M12),"",'ONR 3'!M12)</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="247" t="b">
-        <f t="shared" si="53">IF(ISBLANK('ONR 3'!N12),"",'ONR 3'!N12)</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="247" t="b">
-        <f t="shared" si="54">IF(ISBLANK('ONR 3'!O12),"",'ONR 3'!O12)</f>
-        <v>0</v>
-      </c>
-      <c r="P25" s="247" t="b">
-        <f t="shared" si="55">IF(ISBLANK('ONR 3'!P12),"",'ONR 3'!P12)</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="247" t="b">
-        <f t="shared" si="56">IF(ISBLANK('ONR 3'!Q12),"",'ONR 3'!Q12)</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="247" t="b">
-        <f t="shared" si="57">IF(ISBLANK('ONR 3'!R12),"",'ONR 3'!R12)</f>
-        <v>0</v>
-      </c>
-      <c r="S25" s="248" t="str">
-        <f t="shared" si="58">IF(ISBLANK('ONR 3'!S12),"",'ONR 3'!S12)</f>
-      </c>
-      <c r="T25" s="249" t="str">
-        <f t="shared" si="59">IF(ISBLANK('ONR 3'!T12),"",'ONR 3'!T12)</f>
-      </c>
-      <c r="U25" s="250" t="str">
-        <f t="shared" si="60">IF(ISBLANK('ONR 3'!U12),"",'ONR 3'!U12)</f>
-      </c>
-      <c r="V25" s="252" t="str">
-        <f t="shared" si="61">IF(ISBLANK('ONR 3'!G12),"",'ONR 3'!G12)</f>
-      </c>
-      <c r="W25" s="252" t="str">
-        <f>IF(ISBLANK('ONR 3'!V12),"",'ONR 3'!V12)</f>
+        <f>IF(ISBLANK('ONR 3'!J10),"",'ONR 3'!J10)</f>
+      </c>
+      <c r="K23" s="247" t="str">
+        <f>IF(ISBLANK('ONR 3'!K10),"",'ONR 3'!K10)</f>
+      </c>
+      <c r="L23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!L10),"",'ONR 3'!L10)</f>
+      </c>
+      <c r="M23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!M10),"",'ONR 3'!M10)</f>
+      </c>
+      <c r="N23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!N10),"",'ONR 3'!N10)</f>
+      </c>
+      <c r="O23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!O10),"",'ONR 3'!O10)</f>
+      </c>
+      <c r="P23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!P10),"",'ONR 3'!P10)</f>
+      </c>
+      <c r="Q23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!Q10),"",'ONR 3'!Q10)</f>
+      </c>
+      <c r="R23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!R10),"",'ONR 3'!R10)</f>
+      </c>
+      <c r="S23" s="248" t="str">
+        <f>IF(ISBLANK('ONR 3'!S10),"",'ONR 3'!S10)</f>
+      </c>
+      <c r="T23" s="249" t="str">
+        <f>IF(ISBLANK('ONR 3'!T10),"",'ONR 3'!T10)</f>
+      </c>
+      <c r="U23" s="250" t="str">
+        <f>IF(ISBLANK('ONR 3'!U10),"",'ONR 3'!U10)</f>
+      </c>
+      <c r="V23" s="235" t="str">
+        <f>IF(ISBLANK('ONR 3'!G10),"",'ONR 3'!G10)</f>
+      </c>
+      <c r="W23" s="235" t="str">
+        <f>IF(ISBLANK('ONR 3'!V10),"",'ONR 3'!V10)</f>
       </c>
       <c r="X23" s="183" t="str">
         <f>IF(ISBLANK('ONR 3'!W10),"",'ONR 3'!W10)</f>
       </c>
       <c r="Y23" s="253" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I10),"",'ONR 3'!I10)</f>
+        <f>IF(ISBLANK('ONR 3'!I10),"",'ONR 3'!I10)</f>
       </c>
       <c r="Z23" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D10),"",'ONR 3'!D10)</f>
+        <f>IF(ISBLANK('ONR 3'!D10),"",'ONR 3'!D10)</f>
       </c>
       <c r="AE23" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T23),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T23),0,1)</f>
       </c>
       <c r="AF23" s="206" t="n">
-        <f t="shared" si="65">IF(L23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L23=TRUE,1,0)</f>
       </c>
       <c r="AG23" s="206" t="n">
-        <f t="shared" si="65">IF(M23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M23=TRUE,1,0)</f>
       </c>
       <c r="AH23" s="206" t="n">
-        <f t="shared" si="65">IF(N23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N23=TRUE,1,0)</f>
       </c>
       <c r="AI23" s="206" t="n">
-        <f t="shared" si="65">IF(O23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O23=TRUE,1,0)</f>
       </c>
       <c r="AJ23" s="206" t="n">
-        <f t="shared" si="65">IF(P23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P23=TRUE,1,0)</f>
       </c>
       <c r="AK23" s="206" t="n">
-        <f t="shared" si="65">IF(Q23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q23=TRUE,1,0)</f>
       </c>
       <c r="AL23" s="206" t="n">
-        <f t="shared" si="65">IF(R23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R23=TRUE,1,0)</f>
       </c>
       <c r="AM23" t="n">
         <f>IF(LEN(TRIM(W23))&gt;0,1,0)</f>
@@ -33674,94 +33360,79 @@
         <f>IF(ISBLANK('ONR 3'!I11),"",'ONR 3'!I11)</f>
       </c>
       <c r="J24" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J11),"",'ONR 3'!J11)</f>
-      </c>
-      <c r="K26" s="247" t="str">
-        <f t="shared" si="50"/>
-      </c>
-      <c r="L26" s="247" t="b">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="247" t="b">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="247" t="b">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="247" t="b">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="247" t="b">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="247" t="b">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="247" t="b">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="248" t="str">
-        <f t="shared" si="58"/>
-      </c>
-      <c r="T26" s="249" t="str">
-        <f t="shared" si="59"/>
-      </c>
-      <c r="U26" s="250" t="str">
-        <f t="shared" si="60"/>
-      </c>
-      <c r="V26" s="252" t="str">
-        <f t="shared" si="61"/>
-      </c>
-      <c r="W26" s="145" t="str">
-        <f>IF(ISBLANK('ONR 3'!V13),"",'ONR 3'!V13)</f>
+        <f>IF(ISBLANK('ONR 3'!J11),"",'ONR 3'!J11)</f>
+      </c>
+      <c r="K24" s="247" t="str">
+        <f>IF(ISBLANK('ONR 3'!K11),"",'ONR 3'!K11)</f>
+      </c>
+      <c r="L24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!L11),"",'ONR 3'!L11)</f>
+      </c>
+      <c r="M24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!M11),"",'ONR 3'!M11)</f>
+      </c>
+      <c r="N24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!N11),"",'ONR 3'!N11)</f>
+      </c>
+      <c r="O24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!O11),"",'ONR 3'!O11)</f>
+      </c>
+      <c r="P24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!P11),"",'ONR 3'!P11)</f>
+      </c>
+      <c r="Q24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!Q11),"",'ONR 3'!Q11)</f>
+      </c>
+      <c r="R24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!R11),"",'ONR 3'!R11)</f>
+      </c>
+      <c r="S24" s="248" t="str">
+        <f>IF(ISBLANK('ONR 3'!S11),"",'ONR 3'!S11)</f>
+      </c>
+      <c r="T24" s="249" t="str">
+        <f>IF(ISBLANK('ONR 3'!T11),"",'ONR 3'!T11)</f>
+      </c>
+      <c r="U24" s="250" t="str">
+        <f>IF(ISBLANK('ONR 3'!U11),"",'ONR 3'!U11)</f>
+      </c>
+      <c r="V24" s="235" t="str">
+        <f>IF(ISBLANK('ONR 3'!G11),"",'ONR 3'!G11)</f>
+      </c>
+      <c r="W24" s="235" t="str">
+        <f>IF(ISBLANK('ONR 3'!V11),"",'ONR 3'!V11)</f>
       </c>
       <c r="X24" s="183" t="str">
         <f>IF(ISBLANK('ONR 3'!W11),"",'ONR 3'!W11)</f>
       </c>
       <c r="Y24" s="253" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I11),"",'ONR 3'!I11)</f>
+        <f>IF(ISBLANK('ONR 3'!I11),"",'ONR 3'!I11)</f>
       </c>
       <c r="Z24" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D11),"",'ONR 3'!D11)</f>
+        <f>IF(ISBLANK('ONR 3'!D11),"",'ONR 3'!D11)</f>
       </c>
       <c r="AE24" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T24),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T24),0,1)</f>
       </c>
       <c r="AF24" s="206" t="n">
-        <f t="shared" si="65">IF(L24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L24=TRUE,1,0)</f>
       </c>
       <c r="AG24" s="206" t="n">
-        <f t="shared" si="65">IF(M24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M24=TRUE,1,0)</f>
       </c>
       <c r="AH24" s="206" t="n">
-        <f t="shared" si="65">IF(N24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N24=TRUE,1,0)</f>
       </c>
       <c r="AI24" s="206" t="n">
-        <f t="shared" si="65">IF(O24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O24=TRUE,1,0)</f>
       </c>
       <c r="AJ24" s="206" t="n">
-        <f t="shared" si="65">IF(P24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P24=TRUE,1,0)</f>
       </c>
       <c r="AK24" s="206" t="n">
-        <f t="shared" si="65">IF(Q24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q24=TRUE,1,0)</f>
       </c>
       <c r="AL24" s="206" t="n">
-        <f t="shared" si="65">IF(R24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R24=TRUE,1,0)</f>
       </c>
       <c r="AM24" t="n">
         <f>IF(LEN(TRIM(W24))&gt;0,1,0)</f>
@@ -33797,87 +33468,79 @@
         <f>IF(ISBLANK('ONR 3'!I12),"",'ONR 3'!I12)</f>
       </c>
       <c r="J25" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J12),"",'ONR 3'!J12)</f>
-      </c>
-      <c r="K28" s="247">
-        <f t="shared" si="50"/>
-      </c>
-      <c r="L28" s="247">
-        <f t="shared" si="51"/>
-      </c>
-      <c r="M28" s="247">
-        <f t="shared" si="52"/>
-      </c>
-      <c r="N28" s="247">
-        <f t="shared" si="53"/>
-      </c>
-      <c r="O28" s="247">
-        <f t="shared" si="54"/>
-      </c>
-      <c r="P28" s="247">
-        <f t="shared" si="55"/>
-      </c>
-      <c r="Q28" s="247">
-        <f t="shared" si="56"/>
-      </c>
-      <c r="R28" s="247">
-        <f t="shared" si="57"/>
-      </c>
-      <c r="S28" s="248">
-        <f t="shared" si="58"/>
-      </c>
-      <c r="T28" s="249">
-        <f t="shared" si="59"/>
-      </c>
-      <c r="U28" s="250">
-        <f t="shared" si="60"/>
-      </c>
-      <c r="V28" s="241">
-        <f t="shared" si="61"/>
-      </c>
-      <c r="W28" s="148">
-        <f>'ONR 3'!V12</f>
+        <f>IF(ISBLANK('ONR 3'!J12),"",'ONR 3'!J12)</f>
+      </c>
+      <c r="K25" s="247" t="str">
+        <f>IF(ISBLANK('ONR 3'!K12),"",'ONR 3'!K12)</f>
+      </c>
+      <c r="L25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!L12),"",'ONR 3'!L12)</f>
+      </c>
+      <c r="M25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!M12),"",'ONR 3'!M12)</f>
+      </c>
+      <c r="N25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!N12),"",'ONR 3'!N12)</f>
+      </c>
+      <c r="O25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!O12),"",'ONR 3'!O12)</f>
+      </c>
+      <c r="P25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!P12),"",'ONR 3'!P12)</f>
+      </c>
+      <c r="Q25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!Q12),"",'ONR 3'!Q12)</f>
+      </c>
+      <c r="R25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!R12),"",'ONR 3'!R12)</f>
+      </c>
+      <c r="S25" s="248" t="str">
+        <f>IF(ISBLANK('ONR 3'!S12),"",'ONR 3'!S12)</f>
+      </c>
+      <c r="T25" s="249" t="str">
+        <f>IF(ISBLANK('ONR 3'!T12),"",'ONR 3'!T12)</f>
+      </c>
+      <c r="U25" s="250" t="str">
+        <f>IF(ISBLANK('ONR 3'!U12),"",'ONR 3'!U12)</f>
+      </c>
+      <c r="V25" s="252" t="str">
+        <f>IF(ISBLANK('ONR 3'!G12),"",'ONR 3'!G12)</f>
+      </c>
+      <c r="W25" s="252" t="str">
+        <f>IF(ISBLANK('ONR 3'!V12),"",'ONR 3'!V12)</f>
       </c>
       <c r="X25" s="183" t="str">
         <f>IF(ISBLANK('ONR 3'!W12),"",'ONR 3'!W12)</f>
       </c>
       <c r="Y25" s="254" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I12),"",'ONR 3'!I12)</f>
+        <f>IF(ISBLANK('ONR 3'!I12),"",'ONR 3'!I12)</f>
       </c>
       <c r="Z25" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D12),"",'ONR 3'!D12)</f>
+        <f>IF(ISBLANK('ONR 3'!D12),"",'ONR 3'!D12)</f>
       </c>
       <c r="AE25" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T25),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T25),0,1)</f>
       </c>
       <c r="AF25" s="206" t="n">
-        <f t="shared" si="65">IF(L25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L25=TRUE,1,0)</f>
       </c>
       <c r="AG25" s="206" t="n">
-        <f t="shared" si="65">IF(M25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M25=TRUE,1,0)</f>
       </c>
       <c r="AH25" s="206" t="n">
-        <f t="shared" si="65">IF(N25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N25=TRUE,1,0)</f>
       </c>
       <c r="AI25" s="206" t="n">
-        <f t="shared" si="65">IF(O25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O25=TRUE,1,0)</f>
       </c>
       <c r="AJ25" s="206" t="n">
-        <f t="shared" si="65">IF(P25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P25=TRUE,1,0)</f>
       </c>
       <c r="AK25" s="206" t="n">
-        <f t="shared" si="65">IF(Q25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q25=TRUE,1,0)</f>
       </c>
       <c r="AL25" s="206" t="n">
-        <f t="shared" si="65">IF(R25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R25=TRUE,1,0)</f>
       </c>
       <c r="AM25" t="n">
         <f>IF(LEN(TRIM(W25))&gt;0,1,0)</f>
@@ -33913,94 +33576,79 @@
         <f>IF(ISBLANK('ONR 3'!I13),"",'ONR 3'!I13)</f>
       </c>
       <c r="J26" s="246" t="str">
-        <f t="shared" ref="J26" si="66">IF(ISBLANK('ONR 3'!J13),"",'ONR 3'!J13)</f>
+        <f>IF(ISBLANK('ONR 3'!J13),"",'ONR 3'!J13)</f>
       </c>
       <c r="K26" s="247" t="str">
-        <f t="shared" ref="K26" si="67">IF(ISBLANK('ONR 3'!K13),"",'ONR 3'!K13)</f>
+        <f>IF(ISBLANK('ONR 3'!K13),"",'ONR 3'!K13)</f>
       </c>
       <c r="L26" s="247" t="b">
-        <f t="shared" ref="L26" si="68">IF(ISBLANK('ONR 3'!L13),"",'ONR 3'!L13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!L13),"",'ONR 3'!L13)</f>
       </c>
       <c r="M26" s="247" t="b">
-        <f t="shared" ref="M26" si="69">IF(ISBLANK('ONR 3'!M13),"",'ONR 3'!M13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!M13),"",'ONR 3'!M13)</f>
       </c>
       <c r="N26" s="247" t="b">
-        <f t="shared" ref="N26" si="70">IF(ISBLANK('ONR 3'!N13),"",'ONR 3'!N13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!N13),"",'ONR 3'!N13)</f>
       </c>
       <c r="O26" s="247" t="b">
-        <f t="shared" ref="O26" si="71">IF(ISBLANK('ONR 3'!O13),"",'ONR 3'!O13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!O13),"",'ONR 3'!O13)</f>
       </c>
       <c r="P26" s="247" t="b">
-        <f t="shared" ref="P26" si="72">IF(ISBLANK('ONR 3'!P13),"",'ONR 3'!P13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!P13),"",'ONR 3'!P13)</f>
       </c>
       <c r="Q26" s="247" t="b">
-        <f t="shared" ref="Q26" si="73">IF(ISBLANK('ONR 3'!Q13),"",'ONR 3'!Q13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!Q13),"",'ONR 3'!Q13)</f>
       </c>
       <c r="R26" s="247" t="b">
-        <f t="shared" ref="R26" si="74">IF(ISBLANK('ONR 3'!R13),"",'ONR 3'!R13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!R13),"",'ONR 3'!R13)</f>
       </c>
       <c r="S26" s="248" t="str">
-        <f t="shared" ref="S26" si="75">IF(ISBLANK('ONR 3'!S13),"",'ONR 3'!S13)</f>
+        <f>IF(ISBLANK('ONR 3'!S13),"",'ONR 3'!S13)</f>
       </c>
       <c r="T26" s="249" t="str">
-        <f t="shared" ref="T26" si="76">IF(ISBLANK('ONR 3'!T13),"",'ONR 3'!T13)</f>
+        <f>IF(ISBLANK('ONR 3'!T13),"",'ONR 3'!T13)</f>
       </c>
       <c r="U26" s="250" t="str">
-        <f t="shared" ref="U26" si="77">IF(ISBLANK('ONR 3'!U13),"",'ONR 3'!U13)</f>
+        <f>IF(ISBLANK('ONR 3'!U13),"",'ONR 3'!U13)</f>
       </c>
       <c r="V26" s="255" t="str">
-        <f t="shared" si="61">IF(ISBLANK('ONR 3'!G13),"",'ONR 3'!G13)</f>
-      </c>
-      <c r="W29" s="215" t="str">
-        <f>'ONR 3'!V13</f>
+        <f>IF(ISBLANK('ONR 3'!G13),"",'ONR 3'!G13)</f>
+      </c>
+      <c r="W26" s="145" t="str">
+        <f>IF(ISBLANK('ONR 3'!V13),"",'ONR 3'!V13)</f>
       </c>
       <c r="X26" s="183" t="str">
         <f>IF(ISBLANK('ONR 3'!W13),"",'ONR 3'!W13)</f>
       </c>
       <c r="Y26" s="251" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I13),"",'ONR 3'!I13)</f>
+        <f>IF(ISBLANK('ONR 3'!I13),"",'ONR 3'!I13)</f>
       </c>
       <c r="Z26" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D13),"",'ONR 3'!D13)</f>
+        <f>IF(ISBLANK('ONR 3'!D13),"",'ONR 3'!D13)</f>
       </c>
       <c r="AE26" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T26),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T26),0,1)</f>
       </c>
       <c r="AF26" s="206" t="n">
-        <f t="shared" si="65">IF(L26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L26=TRUE,1,0)</f>
       </c>
       <c r="AG26" s="206" t="n">
-        <f t="shared" si="65">IF(M26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M26=TRUE,1,0)</f>
       </c>
       <c r="AH26" s="206" t="n">
-        <f t="shared" si="65">IF(N26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N26=TRUE,1,0)</f>
       </c>
       <c r="AI26" s="206" t="n">
-        <f t="shared" si="65">IF(O26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O26=TRUE,1,0)</f>
       </c>
       <c r="AJ26" s="206" t="n">
-        <f t="shared" si="65">IF(P26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P26=TRUE,1,0)</f>
       </c>
       <c r="AK26" s="206" t="n">
-        <f t="shared" si="65">IF(Q26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q26=TRUE,1,0)</f>
       </c>
       <c r="AL26" s="206" t="n">
-        <f t="shared" si="65">IF(R26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R26=TRUE,1,0)</f>
       </c>
       <c r="AM26" t="n">
         <f>IF(LEN(TRIM(W26))&gt;0,1,0)</f>
@@ -34238,7 +33886,7 @@
         <f>IF(ISBLANK('ONR 4'!J7),"",'ONR 4'!J7)</f>
       </c>
       <c r="K29" s="227" t="str">
-        <f t="shared" ref="K29:K30" si="79">IF(ISBLANK('ONR 4'!K7),"",'ONR 4'!K7)</f>
+        <f>IF(ISBLANK('ONR 4'!K7),"",'ONR 4'!K7)</f>
       </c>
       <c r="L29" s="227" t="b">
         <f>IF(ISBLANK('ONR 4'!L7),"",'ONR 4'!L7)</f>
@@ -34269,13 +33917,13 @@
         <v>0</v>
       </c>
       <c r="S29" s="228" t="str">
-        <f t="shared" ref="S29:S30" si="80">IF(ISBLANK('ONR 4'!S7),"",'ONR 4'!S7)</f>
+        <f>IF(ISBLANK('ONR 4'!S7),"",'ONR 4'!S7)</f>
       </c>
       <c r="T29" s="226" t="str">
-        <f t="shared" ref="T29" si="81">IF(ISBLANK('ONR 4'!T7),"",'ONR 4'!T7)</f>
+        <f>IF(ISBLANK('ONR 4'!T7),"",'ONR 4'!T7)</f>
       </c>
       <c r="U29" s="242" t="str">
-        <f t="shared" ref="U29" si="82">IF(ISBLANK('ONR 4'!U7),"",'ONR 4'!U7)</f>
+        <f>IF(ISBLANK('ONR 4'!U7),"",'ONR 4'!U7)</f>
       </c>
       <c r="V29" s="229" t="str">
         <f>IF(ISBLANK('ONR 4'!G7),"",'ONR 4'!G7)</f>
@@ -34297,32 +33945,25 @@
         <v>1</v>
       </c>
       <c r="AF29" s="206" t="n">
-        <f t="shared" ref="AF29:AL32" si="83">IF(L29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L29=TRUE,1,0)</f>
       </c>
       <c r="AG29" s="206" t="n">
-        <f t="shared" si="83">IF(M29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M29=TRUE,1,0)</f>
       </c>
       <c r="AH29" s="206" t="n">
-        <f t="shared" si="83">IF(N29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N29=TRUE,1,0)</f>
       </c>
       <c r="AI29" s="206" t="n">
-        <f t="shared" si="83">IF(O29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O29=TRUE,1,0)</f>
       </c>
       <c r="AJ29" s="206" t="n">
-        <f t="shared" si="83">IF(P29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P29=TRUE,1,0)</f>
       </c>
       <c r="AK29" s="206" t="n">
-        <f t="shared" si="83">IF(Q29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q29=TRUE,1,0)</f>
       </c>
       <c r="AL29" s="206" t="n">
-        <f t="shared" si="83">IF(R29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R29=TRUE,1,0)</f>
       </c>
       <c r="AM29" t="n">
         <f>IF(LEN(TRIM(W29))&gt;0,1,0)</f>
@@ -34358,59 +33999,41 @@
         <f>IF(ISBLANK('ONR 4'!I8),"",'ONR 4'!I8)</f>
       </c>
       <c r="J30" s="219" t="str">
-        <f t="shared" ref="J30:J38" si="84">IF(ISBLANK('ONR 4'!J8),"",'ONR 4'!J8)</f>
+        <f>IF(ISBLANK('ONR 4'!J8),"",'ONR 4'!J8)</f>
       </c>
       <c r="K30" s="233" t="str">
-        <f t="shared" si="79">IF(ISBLANK('ONR 4'!K8),"",'ONR 4'!K8)</f>
-      </c>
-      <c r="L33" s="233">
-        <f t="shared" ref="L33" si="85">OR(K30=31)</f>
+        <f>IF(ISBLANK('ONR 4'!K8),"",'ONR 4'!K8)</f>
       </c>
       <c r="L30" t="b" s="227">
         <f>IF(ISBLANK('ONR 4'!L8),"",'ONR 4'!L8)</f>
         <v>0</v>
       </c>
       <c r="M30" s="233" t="b">
-        <f t="shared" ref="M30" si="86">IF(ISBLANK('ONR 4'!M8),"",'ONR 4'!M8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!M8),"",'ONR 4'!M8)</f>
       </c>
       <c r="N30" s="233" t="b">
-        <f t="shared" ref="N30" si="87">IF(ISBLANK('ONR 4'!N8),"",'ONR 4'!N8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!N8),"",'ONR 4'!N8)</f>
       </c>
       <c r="O30" s="233" t="b">
-        <f t="shared" ref="O30" si="88">IF(ISBLANK('ONR 4'!O8),"",'ONR 4'!O8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!O8),"",'ONR 4'!O8)</f>
       </c>
       <c r="P30" s="233" t="b">
-        <f t="shared" ref="P30" si="89">IF(ISBLANK('ONR 4'!P8),"",'ONR 4'!P8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!P8),"",'ONR 4'!P8)</f>
       </c>
       <c r="Q30" s="233" t="b">
-        <f t="shared" ref="Q30" si="90">IF(ISBLANK('ONR 4'!Q8),"",'ONR 4'!Q8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!Q8),"",'ONR 4'!Q8)</f>
       </c>
       <c r="R30" s="233" t="b">
-        <f t="shared" ref="R30" si="91">IF(ISBLANK('ONR 4'!R8),"",'ONR 4'!R8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!R8),"",'ONR 4'!R8)</f>
       </c>
       <c r="S30" s="234" t="str">
-        <f t="shared" si="80">IF(ISBLANK('ONR 4'!S8),"",'ONR 4'!S8)</f>
-      </c>
-      <c r="T33" s="232">
-        <f t="shared" si="81"/>
+        <f>IF(ISBLANK('ONR 4'!S8),"",'ONR 4'!S8)</f>
       </c>
       <c r="T30" t="str" s="226">
         <f>IF(ISBLANK('ONR 4'!T8),"",'ONR 4'!T8)</f>
       </c>
-      <c r="U33" s="243">
-        <f t="shared" si="82"/>
-      </c>
       <c r="U30" t="str" s="242">
         <f>IF(ISBLANK('ONR 4'!U8),"",'ONR 4'!U8)</f>
-      </c>
-      <c r="V33" s="235">
-        <f>G30</f>
       </c>
       <c r="V30" t="str" s="229">
         <f>IF(ISBLANK('ONR 4'!G8),"",'ONR 4'!G8)</f>
@@ -34432,32 +34055,25 @@
         <v>1</v>
       </c>
       <c r="AF30" s="206" t="n">
-        <f t="shared" si="83">IF(L30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L30=TRUE,1,0)</f>
       </c>
       <c r="AG30" s="206" t="n">
-        <f t="shared" si="83">IF(M30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M30=TRUE,1,0)</f>
       </c>
       <c r="AH30" s="206" t="n">
-        <f t="shared" si="83">IF(N30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N30=TRUE,1,0)</f>
       </c>
       <c r="AI30" s="206" t="n">
-        <f t="shared" si="83">IF(O30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O30=TRUE,1,0)</f>
       </c>
       <c r="AJ30" s="206" t="n">
-        <f t="shared" si="83">IF(P30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P30=TRUE,1,0)</f>
       </c>
       <c r="AK30" s="206" t="n">
-        <f t="shared" si="83">IF(Q30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q30=TRUE,1,0)</f>
       </c>
       <c r="AL30" s="206" t="n">
-        <f t="shared" si="83">IF(R30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R30=TRUE,1,0)</f>
       </c>
       <c r="AM30" t="n">
         <f>IF(LEN(TRIM(W30))&gt;0,1,0)</f>
@@ -34493,47 +34109,40 @@
         <f>IF(ISBLANK('ONR 4'!I9),"",'ONR 4'!I9)</f>
       </c>
       <c r="J31" s="219" t="str">
-        <f t="shared" ref="J31:J32" si="92">IF(ISBLANK('ONR 4'!J9),"",'ONR 4'!J9)</f>
+        <f>IF(ISBLANK('ONR 4'!J9),"",'ONR 4'!J9)</f>
       </c>
       <c r="K31" s="233" t="str">
-        <f t="shared" ref="K31:K35" si="93">IF(ISBLANK('ONR 4'!K9),"",'ONR 4'!K9)</f>
+        <f>IF(ISBLANK('ONR 4'!K9),"",'ONR 4'!K9)</f>
       </c>
       <c r="L31" s="233" t="b">
-        <f t="shared" ref="L31:L35" si="94">IF(ISBLANK('ONR 4'!L9),"",'ONR 4'!L9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!L9),"",'ONR 4'!L9)</f>
       </c>
       <c r="M31" s="233" t="b">
-        <f t="shared" ref="M31" si="95">IF(ISBLANK('ONR 4'!M9),"",'ONR 4'!M9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!M9),"",'ONR 4'!M9)</f>
       </c>
       <c r="N31" s="233" t="b">
-        <f t="shared" ref="N31" si="96">IF(ISBLANK('ONR 4'!N9),"",'ONR 4'!N9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!N9),"",'ONR 4'!N9)</f>
       </c>
       <c r="O31" s="233" t="b">
-        <f t="shared" ref="O31" si="97">IF(ISBLANK('ONR 4'!O9),"",'ONR 4'!O9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!O9),"",'ONR 4'!O9)</f>
       </c>
       <c r="P31" s="233" t="b">
-        <f t="shared" ref="P31" si="98">IF(ISBLANK('ONR 4'!P9),"",'ONR 4'!P9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!P9),"",'ONR 4'!P9)</f>
       </c>
       <c r="Q31" s="233" t="b">
-        <f t="shared" ref="Q31" si="99">IF(ISBLANK('ONR 4'!Q9),"",'ONR 4'!Q9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!Q9),"",'ONR 4'!Q9)</f>
       </c>
       <c r="R31" s="233" t="b">
-        <f t="shared" ref="R31" si="100">IF(ISBLANK('ONR 4'!R9),"",'ONR 4'!R9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!R9),"",'ONR 4'!R9)</f>
       </c>
       <c r="S31" s="234" t="str">
-        <f t="shared" ref="S31" si="101">IF(ISBLANK('ONR 4'!S9),"",'ONR 4'!S9)</f>
+        <f>IF(ISBLANK('ONR 4'!S9),"",'ONR 4'!S9)</f>
       </c>
       <c r="T31" s="232" t="str">
-        <f t="shared" ref="T31:T35" si="102">IF(ISBLANK('ONR 4'!T9),"",'ONR 4'!T9)</f>
+        <f>IF(ISBLANK('ONR 4'!T9),"",'ONR 4'!T9)</f>
       </c>
       <c r="U31" s="243" t="str">
-        <f t="shared" ref="U31:U35" si="103">IF(ISBLANK('ONR 4'!U9),"",'ONR 4'!U9)</f>
+        <f>IF(ISBLANK('ONR 4'!U9),"",'ONR 4'!U9)</f>
       </c>
       <c r="V31" s="235" t="str">
         <f>IF(ISBLANK('ONR 4'!G9),"",'ONR 4'!G9)</f>
@@ -34555,32 +34164,25 @@
         <v>1</v>
       </c>
       <c r="AF31" s="206" t="n">
-        <f t="shared" si="83">IF(L31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L31=TRUE,1,0)</f>
       </c>
       <c r="AG31" s="206" t="n">
-        <f t="shared" si="83">IF(M31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M31=TRUE,1,0)</f>
       </c>
       <c r="AH31" s="206" t="n">
-        <f t="shared" si="83">IF(N31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N31=TRUE,1,0)</f>
       </c>
       <c r="AI31" s="206" t="n">
-        <f t="shared" si="83">IF(O31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O31=TRUE,1,0)</f>
       </c>
       <c r="AJ31" s="206" t="n">
-        <f t="shared" si="83">IF(P31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P31=TRUE,1,0)</f>
       </c>
       <c r="AK31" s="206" t="n">
-        <f t="shared" si="83">IF(Q31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q31=TRUE,1,0)</f>
       </c>
       <c r="AL31" s="206" t="n">
-        <f t="shared" si="83">IF(R31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R31=TRUE,1,0)</f>
       </c>
       <c r="AM31" t="n">
         <f>IF(LEN(TRIM(W31))&gt;0,1,0)</f>
@@ -34616,91 +34218,47 @@
         <f>IF(ISBLANK('ONR 4'!I10),"",'ONR 4'!I10)</f>
       </c>
       <c r="J32" s="219" t="n">
-        <f t="shared" si="92">IF(ISBLANK('ONR 4'!J10),"",'ONR 4'!J10)</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="233" t="str">
-        <f t="shared" si="93">IF(ISBLANK('ONR 5'!K8),"",'ONR 5'!K8)</f>
+        <f>IF(ISBLANK('ONR 4'!J10),"",'ONR 4'!J10)</f>
       </c>
       <c r="K32" t="str" s="233">
         <f>IF(ISBLANK('ONR 4'!K10),"",'ONR 4'!K10)</f>
-      </c>
-      <c r="L35" s="233" t="b">
-        <f t="shared" si="94">IF(ISBLANK('ONR 5'!L8),"",'ONR 5'!L8)</f>
-        <v>0</v>
       </c>
       <c r="L32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!L10),"",'ONR 4'!L10)</f>
         <v>0</v>
       </c>
-      <c r="M35" s="233" t="b">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
       <c r="M32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!M10),"",'ONR 4'!M10)</f>
         <v>0</v>
       </c>
-      <c r="N35" s="233" t="b">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
       <c r="N32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!N10),"",'ONR 4'!N10)</f>
         <v>0</v>
       </c>
-      <c r="O35" s="233" t="b">
-        <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
       <c r="O32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!O10),"",'ONR 4'!O10)</f>
         <v>0</v>
       </c>
-      <c r="P35" s="233" t="b">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
       <c r="P32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!P10),"",'ONR 4'!P10)</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="233" t="b">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="Q32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!Q10),"",'ONR 4'!Q10)</f>
         <v>0</v>
       </c>
-      <c r="R35" s="233" t="b">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
       <c r="R32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!R10),"",'ONR 4'!R10)</f>
         <v>0</v>
       </c>
-      <c r="S35" s="234" t="str">
-        <f t="shared" si="101"/>
-      </c>
       <c r="S32" t="str" s="234">
         <f>IF(ISBLANK('ONR 4'!S10),"",'ONR 4'!S10)</f>
       </c>
-      <c r="T35" s="232" t="str">
-        <f t="shared" si="102">IF(ISBLANK('ONR 5'!T8),"",'ONR 5'!T8)</f>
-      </c>
       <c r="T32" t="str" s="232">
         <f>IF(ISBLANK('ONR 4'!T10),"",'ONR 4'!T10)</f>
       </c>
-      <c r="U35" s="243" t="str">
-        <f t="shared" si="103">IF(ISBLANK('ONR 5'!U8),"",'ONR 5'!U8)</f>
-      </c>
       <c r="U32" t="str" s="243">
         <f>IF(ISBLANK('ONR 4'!U10),"",'ONR 4'!U10)</f>
-      </c>
-      <c r="V35" s="235" t="str">
-        <f>IF(ISBLANK('ONR 5'!G8),"",'ONR 5'!G8)</f>
       </c>
       <c r="V32" t="str" s="235">
         <f>IF(ISBLANK('ONR 4'!G10),"",'ONR 4'!G10)</f>
@@ -34722,32 +34280,25 @@
         <v>1</v>
       </c>
       <c r="AF32" s="206" t="n">
-        <f t="shared" si="83">IF(L32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L32=TRUE,1,0)</f>
       </c>
       <c r="AG32" s="206" t="n">
-        <f t="shared" si="83">IF(M32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M32=TRUE,1,0)</f>
       </c>
       <c r="AH32" s="206" t="n">
-        <f t="shared" si="83">IF(N32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N32=TRUE,1,0)</f>
       </c>
       <c r="AI32" s="206" t="n">
-        <f t="shared" si="83">IF(O32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O32=TRUE,1,0)</f>
       </c>
       <c r="AJ32" s="206" t="n">
-        <f t="shared" si="83">IF(P32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P32=TRUE,1,0)</f>
       </c>
       <c r="AK32" s="206" t="n">
-        <f t="shared" si="83">IF(Q32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q32=TRUE,1,0)</f>
       </c>
       <c r="AL32" s="206" t="n">
-        <f t="shared" si="83">IF(R32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R32=TRUE,1,0)</f>
       </c>
       <c r="AM32" t="n">
         <f>IF(LEN(TRIM(W32))&gt;0,1,0)</f>
@@ -34858,10 +34409,7 @@
         <f>IF(ISBLANK('ONR 5'!I7),"",'ONR 5'!I7)</f>
       </c>
       <c r="J34" s="220" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J7),"",'ONR 5'!J7)</f>
-      </c>
-      <c r="K37" s="227" t="str">
-        <f t="shared" ref="K37:K38" si="105">E34*10+F34</f>
+        <f>IF(ISBLANK('ONR 5'!J7),"",'ONR 5'!J7)</f>
       </c>
       <c r="K34" t="str" s="363">
         <f>IF(ISBLANK('ONR 5'!K7),"",'ONR 5'!K7)</f>
@@ -34895,16 +34443,16 @@
         <v>0</v>
       </c>
       <c r="S34" s="228" t="str">
-        <f t="shared" ref="S34:S38" si="106">IF(ISBLANK('ONR 5'!S7),"",'ONR 5'!S7)</f>
+        <f>IF(ISBLANK('ONR 5'!S7),"",'ONR 5'!S7)</f>
       </c>
       <c r="T34" s="226" t="str">
-        <f t="shared" ref="T34:T38" si="107">IF(ISBLANK('ONR 5'!T7),"",'ONR 5'!T7)</f>
+        <f>IF(ISBLANK('ONR 5'!T7),"",'ONR 5'!T7)</f>
       </c>
       <c r="U34" s="242" t="str">
-        <f t="shared" ref="U34:U38" si="108">IF(ISBLANK('ONR 5'!U7),"",'ONR 5'!U7)</f>
+        <f>IF(ISBLANK('ONR 5'!U7),"",'ONR 5'!U7)</f>
       </c>
       <c r="V34" s="229" t="str">
-        <f t="shared" ref="V34:V38" si="109">IF(ISBLANK('ONR 5'!G7),"",'ONR 5'!G7)</f>
+        <f>IF(ISBLANK('ONR 5'!G7),"",'ONR 5'!G7)</f>
       </c>
       <c r="W34" s="203" t="str">
         <f>IF(ISBLANK('ONR 5'!V7),"",'ONR 5'!V7)</f>
@@ -34913,42 +34461,34 @@
         <f>IF(ISBLANK('ONR 5'!W7),"",'ONR 5'!W7)</f>
       </c>
       <c r="Y34" s="257" t="str">
-        <f t="shared" ref="Y34:Y38" si="110">IF(ISBLANK('ONR 5'!I7),"",'ONR 5'!I7)</f>
+        <f>IF(ISBLANK('ONR 5'!I7),"",'ONR 5'!I7)</f>
       </c>
       <c r="Z34" s="256" t="str">
         <f>IF(ISBLANK('ONR 5'!D7),"",'ONR 5'!D7)</f>
       </c>
       <c r="AE34" s="206" t="n">
-        <f t="shared" ref="AE34:AE38" si="111">IF(ISNUMBER(T34),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T34),0,1)</f>
       </c>
       <c r="AF34" s="206" t="n">
-        <f t="shared" ref="AF34:AF38" si="112">IF(L34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L34=TRUE,1,0)</f>
       </c>
       <c r="AG34" s="206" t="n">
-        <f t="shared" ref="AG34:AG38" si="113">IF(M34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M34=TRUE,1,0)</f>
       </c>
       <c r="AH34" s="206" t="n">
-        <f t="shared" ref="AH34:AH38" si="114">IF(N34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N34=TRUE,1,0)</f>
       </c>
       <c r="AI34" s="206" t="n">
-        <f t="shared" ref="AI34:AI38" si="115">IF(O34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O34=TRUE,1,0)</f>
       </c>
       <c r="AJ34" s="206" t="n">
-        <f t="shared" ref="AJ34:AJ38" si="116">IF(P34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P34=TRUE,1,0)</f>
       </c>
       <c r="AK34" s="206" t="n">
-        <f t="shared" ref="AK34:AK38" si="117">IF(Q34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q34=TRUE,1,0)</f>
       </c>
       <c r="AL34" s="206" t="n">
-        <f t="shared" ref="AL34:AL38" si="118">IF(R34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R34=TRUE,1,0)</f>
       </c>
       <c r="AM34" t="n">
         <f>IF(LEN(TRIM(W34))&gt;0,1,0)</f>
@@ -34984,53 +34524,43 @@
         <f>IF(ISBLANK('ONR 5'!I8),"",'ONR 5'!I8)</f>
       </c>
       <c r="J35" s="220" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J8),"",'ONR 5'!J8)</f>
-      </c>
-      <c r="K38" s="233" t="str">
-        <f t="shared" si="105"/>
-      </c>
-      <c r="L38" s="233" t="b">
-        <f t="shared" ref="L38:L38" si="119">OR(K35=31)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!J8),"",'ONR 5'!J8)</f>
+      </c>
+      <c r="K35" s="233" t="str">
+        <f>IF(ISBLANK('ONR 5'!K8),"",'ONR 5'!K8)</f>
+      </c>
+      <c r="L35" s="233" t="b">
+        <f>IF(ISBLANK('ONR 5'!L8),"",'ONR 5'!L8)</f>
       </c>
       <c r="M35" s="233" t="b">
-        <f t="shared" ref="M35:M38" si="120">IF(ISBLANK('ONR 5'!M8),"",'ONR 5'!M8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!M8),"",'ONR 5'!M8)</f>
       </c>
       <c r="N35" s="233" t="b">
-        <f t="shared" ref="N35:N38" si="121">IF(ISBLANK('ONR 5'!N8),"",'ONR 5'!N8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!N8),"",'ONR 5'!N8)</f>
       </c>
       <c r="O35" s="233" t="b">
-        <f t="shared" ref="O35:O38" si="122">IF(ISBLANK('ONR 5'!O8),"",'ONR 5'!O8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!O8),"",'ONR 5'!O8)</f>
       </c>
       <c r="P35" s="233" t="b">
-        <f t="shared" ref="P35:P38" si="123">IF(ISBLANK('ONR 5'!P8),"",'ONR 5'!P8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!P8),"",'ONR 5'!P8)</f>
       </c>
       <c r="Q35" s="233" t="b">
-        <f t="shared" ref="Q35:Q38" si="124">IF(ISBLANK('ONR 5'!Q8),"",'ONR 5'!Q8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!Q8),"",'ONR 5'!Q8)</f>
       </c>
       <c r="R35" s="233" t="b">
-        <f t="shared" ref="R35:R38" si="125">IF(ISBLANK('ONR 5'!R8),"",'ONR 5'!R8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!R8),"",'ONR 5'!R8)</f>
       </c>
       <c r="S35" s="234" t="str">
-        <f t="shared" si="106">IF(ISBLANK('ONR 5'!S8),"",'ONR 5'!S8)</f>
-      </c>
-      <c r="T38" s="232" t="str">
-        <f t="shared" si="107"/>
-      </c>
-      <c r="U38" s="243" t="str">
-        <f t="shared" si="108"/>
-      </c>
-      <c r="V38" s="235" t="str">
-        <f t="shared" si="109"/>
-      </c>
-      <c r="W38" s="142" t="str">
-        <f>'ONR 5'!V8</f>
+        <f>IF(ISBLANK('ONR 5'!S8),"",'ONR 5'!S8)</f>
+      </c>
+      <c r="T35" s="232" t="str">
+        <f>IF(ISBLANK('ONR 5'!T8),"",'ONR 5'!T8)</f>
+      </c>
+      <c r="U35" s="243" t="str">
+        <f>IF(ISBLANK('ONR 5'!U8),"",'ONR 5'!U8)</f>
+      </c>
+      <c r="V35" s="235" t="str">
+        <f>IF(ISBLANK('ONR 5'!G8),"",'ONR 5'!G8)</f>
       </c>
       <c r="W35" t="str" s="203">
         <f>IF(ISBLANK('ONR 5'!V8),"",'ONR 5'!V8)</f>
@@ -35039,45 +34569,34 @@
         <f>IF(ISBLANK('ONR 5'!W8),"",'ONR 5'!W8)</f>
       </c>
       <c r="Y35" s="258" t="str">
-        <f t="shared" si="110">IF(ISBLANK('ONR 5'!I8),"",'ONR 5'!I8)</f>
-      </c>
-      <c r="Z38" s="256" t="str">
-        <f t="shared" ref="Z38:Z38" si="126">D35</f>
+        <f>IF(ISBLANK('ONR 5'!I8),"",'ONR 5'!I8)</f>
       </c>
       <c r="Z35" t="str" s="256">
         <f>IF(ISBLANK('ONR 5'!D8),"",'ONR 5'!D8)</f>
       </c>
       <c r="AE35" s="206" t="n">
-        <f t="shared" si="111">IF(ISNUMBER(T35),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T35),0,1)</f>
       </c>
       <c r="AF35" s="206" t="n">
-        <f t="shared" si="112">IF(L35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L35=TRUE,1,0)</f>
       </c>
       <c r="AG35" s="206" t="n">
-        <f t="shared" si="113">IF(M35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M35=TRUE,1,0)</f>
       </c>
       <c r="AH35" s="206" t="n">
-        <f t="shared" si="114">IF(N35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N35=TRUE,1,0)</f>
       </c>
       <c r="AI35" s="206" t="n">
-        <f t="shared" si="115">IF(O35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O35=TRUE,1,0)</f>
       </c>
       <c r="AJ35" s="206" t="n">
-        <f t="shared" si="116">IF(P35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P35=TRUE,1,0)</f>
       </c>
       <c r="AK35" s="206" t="n">
-        <f t="shared" si="117">IF(Q35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q35=TRUE,1,0)</f>
       </c>
       <c r="AL35" s="206" t="n">
-        <f t="shared" si="118">IF(R35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R35=TRUE,1,0)</f>
       </c>
       <c r="AM35" t="n">
         <f>IF(LEN(TRIM(W35))&gt;0,1,0)</f>
@@ -35113,97 +34632,51 @@
         <f>IF(ISBLANK('ONR 5'!I9),"",'ONR 5'!I9)</f>
       </c>
       <c r="J36" s="220" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J9),"",'ONR 5'!J9)</f>
-      </c>
-      <c r="K39" s="233" t="str">
-        <f t="shared" si="105"/>
+        <f>IF(ISBLANK('ONR 5'!J9),"",'ONR 5'!J9)</f>
       </c>
       <c r="K36" t="str" s="233">
         <f>IF(ISBLANK('ONR 5'!K9),"",'ONR 5'!K9)</f>
-      </c>
-      <c r="L39" s="233" t="b">
-        <f t="shared" si="119"/>
-        <v>0</v>
       </c>
       <c r="L36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!L9),"",'ONR 5'!L9)</f>
         <v>0</v>
       </c>
-      <c r="M39" s="233" t="b">
-        <f t="shared" si="120"/>
-        <v>0</v>
-      </c>
       <c r="M36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!M9),"",'ONR 5'!M9)</f>
         <v>0</v>
       </c>
-      <c r="N39" s="233" t="b">
-        <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
       <c r="N36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!N9),"",'ONR 5'!N9)</f>
         <v>0</v>
       </c>
-      <c r="O39" s="233" t="b">
-        <f t="shared" si="122"/>
-        <v>0</v>
-      </c>
       <c r="O36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!O9),"",'ONR 5'!O9)</f>
         <v>0</v>
       </c>
-      <c r="P39" s="233" t="b">
-        <f t="shared" si="123"/>
-        <v>0</v>
-      </c>
       <c r="P36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!P9),"",'ONR 5'!P9)</f>
         <v>0</v>
       </c>
-      <c r="Q39" s="233" t="b">
-        <f t="shared" si="124"/>
-        <v>0</v>
-      </c>
       <c r="Q36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!Q9),"",'ONR 5'!Q9)</f>
         <v>0</v>
       </c>
-      <c r="R39" s="233" t="b">
-        <f t="shared" si="125"/>
-        <v>0</v>
-      </c>
       <c r="R36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!R9),"",'ONR 5'!R9)</f>
         <v>0</v>
       </c>
-      <c r="S39" s="234" t="str">
-        <f t="shared" si="106"/>
-      </c>
       <c r="S36" t="str" s="234">
         <f>IF(ISBLANK('ONR 5'!S9),"",'ONR 5'!S9)</f>
       </c>
-      <c r="T39" s="232" t="str">
-        <f t="shared" si="107"/>
-      </c>
       <c r="T36" t="str" s="232">
         <f>IF(ISBLANK('ONR 5'!T9),"",'ONR 5'!T9)</f>
       </c>
-      <c r="U39" s="243" t="str">
-        <f t="shared" si="108"/>
-      </c>
       <c r="U36" t="str" s="243">
         <f>IF(ISBLANK('ONR 5'!U9),"",'ONR 5'!U9)</f>
       </c>
-      <c r="V39" s="235" t="str">
-        <f t="shared" si="109"/>
-      </c>
       <c r="V36" t="str" s="235">
         <f>IF(ISBLANK('ONR 5'!G9),"",'ONR 5'!G9)</f>
       </c>
-      <c r="W39" s="142" t="str">
-        <f>'ONR 5'!V9</f>
-      </c>
       <c r="W36" t="str" s="142">
         <f>IF(ISBLANK('ONR 5'!V9),"",'ONR 5'!V9)</f>
       </c>
@@ -35211,42 +34684,34 @@
         <f>IF(ISBLANK('ONR 5'!W9),"",'ONR 5'!W9)</f>
       </c>
       <c r="Y36" s="258" t="str">
-        <f t="shared" si="110">IF(ISBLANK('ONR 5'!I9),"",'ONR 5'!I9)</f>
+        <f>IF(ISBLANK('ONR 5'!I9),"",'ONR 5'!I9)</f>
       </c>
       <c r="Z36" s="256" t="str">
-        <f t="shared" si="126">IF(ISBLANK('ONR 5'!D9),"",'ONR 5'!D9)</f>
+        <f>IF(ISBLANK('ONR 5'!D9),"",'ONR 5'!D9)</f>
       </c>
       <c r="AE36" s="206" t="n">
-        <f t="shared" si="111">IF(ISNUMBER(T36),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T36),0,1)</f>
       </c>
       <c r="AF36" s="206" t="n">
-        <f t="shared" si="112">IF(L36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L36=TRUE,1,0)</f>
       </c>
       <c r="AG36" s="206" t="n">
-        <f t="shared" si="113">IF(M36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M36=TRUE,1,0)</f>
       </c>
       <c r="AH36" s="206" t="n">
-        <f t="shared" si="114">IF(N36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N36=TRUE,1,0)</f>
       </c>
       <c r="AI36" s="206" t="n">
-        <f t="shared" si="115">IF(O36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O36=TRUE,1,0)</f>
       </c>
       <c r="AJ36" s="206" t="n">
-        <f t="shared" si="116">IF(P36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P36=TRUE,1,0)</f>
       </c>
       <c r="AK36" s="206" t="n">
-        <f t="shared" si="117">IF(Q36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q36=TRUE,1,0)</f>
       </c>
       <c r="AL36" s="206" t="n">
-        <f t="shared" si="118">IF(R36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R36=TRUE,1,0)</f>
       </c>
       <c r="AM36" t="n">
         <f>IF(LEN(TRIM(W36))&gt;0,1,0)</f>
@@ -35282,50 +34747,43 @@
         <f>IF(ISBLANK('ONR 5'!I10),"",'ONR 5'!I10)</f>
       </c>
       <c r="J37" s="220" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J10),"",'ONR 5'!J10)</f>
+        <f>IF(ISBLANK('ONR 5'!J10),"",'ONR 5'!J10)</f>
       </c>
       <c r="K37" s="233" t="str">
-        <f t="shared" ref="K37:K38" si="105">IF(ISBLANK('ONR 5'!K10),"",'ONR 5'!K10)</f>
+        <f>IF(ISBLANK('ONR 5'!K10),"",'ONR 5'!K10)</f>
       </c>
       <c r="L37" s="233" t="b">
-        <f t="shared" si="119">IF(ISBLANK('ONR 5'!L10),"",'ONR 5'!L10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!L10),"",'ONR 5'!L10)</f>
       </c>
       <c r="M37" s="233" t="b">
-        <f t="shared" si="120">IF(ISBLANK('ONR 5'!M10),"",'ONR 5'!M10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!M10),"",'ONR 5'!M10)</f>
       </c>
       <c r="N37" s="233" t="b">
-        <f t="shared" si="121">IF(ISBLANK('ONR 5'!N10),"",'ONR 5'!N10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!N10),"",'ONR 5'!N10)</f>
       </c>
       <c r="O37" s="233" t="b">
-        <f t="shared" si="122">IF(ISBLANK('ONR 5'!O10),"",'ONR 5'!O10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!O10),"",'ONR 5'!O10)</f>
       </c>
       <c r="P37" s="233" t="b">
-        <f t="shared" si="123">IF(ISBLANK('ONR 5'!P10),"",'ONR 5'!P10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!P10),"",'ONR 5'!P10)</f>
       </c>
       <c r="Q37" s="233" t="b">
-        <f t="shared" si="124">IF(ISBLANK('ONR 5'!Q10),"",'ONR 5'!Q10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!Q10),"",'ONR 5'!Q10)</f>
       </c>
       <c r="R37" s="233" t="b">
-        <f t="shared" si="125">IF(ISBLANK('ONR 5'!R10),"",'ONR 5'!R10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!R10),"",'ONR 5'!R10)</f>
       </c>
       <c r="S37" s="234" t="str">
-        <f t="shared" si="106">IF(ISBLANK('ONR 5'!S10),"",'ONR 5'!S10)</f>
+        <f>IF(ISBLANK('ONR 5'!S10),"",'ONR 5'!S10)</f>
       </c>
       <c r="T37" s="232" t="str">
-        <f t="shared" si="107">IF(ISBLANK('ONR 5'!T10),"",'ONR 5'!T10)</f>
+        <f>IF(ISBLANK('ONR 5'!T10),"",'ONR 5'!T10)</f>
       </c>
       <c r="U37" s="243" t="str">
-        <f t="shared" si="108">IF(ISBLANK('ONR 5'!U10),"",'ONR 5'!U10)</f>
+        <f>IF(ISBLANK('ONR 5'!U10),"",'ONR 5'!U10)</f>
       </c>
       <c r="V37" s="235" t="str">
-        <f t="shared" si="109">IF(ISBLANK('ONR 5'!G10),"",'ONR 5'!G10)</f>
+        <f>IF(ISBLANK('ONR 5'!G10),"",'ONR 5'!G10)</f>
       </c>
       <c r="W37" s="142" t="str">
         <f>IF(ISBLANK('ONR 5'!V10),"",'ONR 5'!V10)</f>
@@ -35334,42 +34792,34 @@
         <f>IF(ISBLANK('ONR 5'!W10),"",'ONR 5'!W10)</f>
       </c>
       <c r="Y37" s="258" t="str">
-        <f t="shared" si="110">IF(ISBLANK('ONR 5'!I10),"",'ONR 5'!I10)</f>
+        <f>IF(ISBLANK('ONR 5'!I10),"",'ONR 5'!I10)</f>
       </c>
       <c r="Z37" s="256" t="str">
-        <f t="shared" si="126">IF(ISBLANK('ONR 5'!D10),"",'ONR 5'!D10)</f>
+        <f>IF(ISBLANK('ONR 5'!D10),"",'ONR 5'!D10)</f>
       </c>
       <c r="AE37" s="206" t="n">
-        <f t="shared" si="111">IF(ISNUMBER(T37),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T37),0,1)</f>
       </c>
       <c r="AF37" s="206" t="n">
-        <f t="shared" si="112">IF(L37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L37=TRUE,1,0)</f>
       </c>
       <c r="AG37" s="206" t="n">
-        <f t="shared" si="113">IF(M37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M37=TRUE,1,0)</f>
       </c>
       <c r="AH37" s="206" t="n">
-        <f t="shared" si="114">IF(N37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N37=TRUE,1,0)</f>
       </c>
       <c r="AI37" s="206" t="n">
-        <f t="shared" si="115">IF(O37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O37=TRUE,1,0)</f>
       </c>
       <c r="AJ37" s="206" t="n">
-        <f t="shared" si="116">IF(P37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P37=TRUE,1,0)</f>
       </c>
       <c r="AK37" s="206" t="n">
-        <f t="shared" si="117">IF(Q37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q37=TRUE,1,0)</f>
       </c>
       <c r="AL37" s="206" t="n">
-        <f t="shared" si="118">IF(R37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R37=TRUE,1,0)</f>
       </c>
       <c r="AM37" t="n">
         <f>IF(LEN(TRIM(W37))&gt;0,1,0)</f>
@@ -35405,50 +34855,43 @@
         <f>IF(ISBLANK('ONR 5'!I11),"",'ONR 5'!I11)</f>
       </c>
       <c r="J38" s="219" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J11),"",'ONR 5'!J11)</f>
+        <f>IF(ISBLANK('ONR 5'!J11),"",'ONR 5'!J11)</f>
       </c>
       <c r="K38" s="233" t="str">
-        <f t="shared" si="105">IF(ISBLANK('ONR 5'!K11),"",'ONR 5'!K11)</f>
+        <f>IF(ISBLANK('ONR 5'!K11),"",'ONR 5'!K11)</f>
       </c>
       <c r="L38" s="233" t="b">
-        <f t="shared" ref="L37:L38" si="119">IF(ISBLANK('ONR 5'!L11),"",'ONR 5'!L11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!L11),"",'ONR 5'!L11)</f>
       </c>
       <c r="M38" s="233" t="b">
-        <f t="shared" si="120">IF(ISBLANK('ONR 5'!M11),"",'ONR 5'!M11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!M11),"",'ONR 5'!M11)</f>
       </c>
       <c r="N38" s="233" t="b">
-        <f t="shared" si="121">IF(ISBLANK('ONR 5'!N11),"",'ONR 5'!N11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!N11),"",'ONR 5'!N11)</f>
       </c>
       <c r="O38" s="233" t="b">
-        <f t="shared" si="122">IF(ISBLANK('ONR 5'!O11),"",'ONR 5'!O11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!O11),"",'ONR 5'!O11)</f>
       </c>
       <c r="P38" s="233" t="b">
-        <f t="shared" si="123">IF(ISBLANK('ONR 5'!P11),"",'ONR 5'!P11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!P11),"",'ONR 5'!P11)</f>
       </c>
       <c r="Q38" s="233" t="b">
-        <f t="shared" si="124">IF(ISBLANK('ONR 5'!Q11),"",'ONR 5'!Q11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!Q11),"",'ONR 5'!Q11)</f>
       </c>
       <c r="R38" s="233" t="b">
-        <f t="shared" si="125">IF(ISBLANK('ONR 5'!R11),"",'ONR 5'!R11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!R11),"",'ONR 5'!R11)</f>
       </c>
       <c r="S38" s="234" t="str">
-        <f t="shared" si="106">IF(ISBLANK('ONR 5'!S11),"",'ONR 5'!S11)</f>
+        <f>IF(ISBLANK('ONR 5'!S11),"",'ONR 5'!S11)</f>
       </c>
       <c r="T38" s="232" t="str">
-        <f t="shared" si="107">IF(ISBLANK('ONR 5'!T11),"",'ONR 5'!T11)</f>
+        <f>IF(ISBLANK('ONR 5'!T11),"",'ONR 5'!T11)</f>
       </c>
       <c r="U38" s="243" t="str">
-        <f t="shared" si="108">IF(ISBLANK('ONR 5'!U11),"",'ONR 5'!U11)</f>
+        <f>IF(ISBLANK('ONR 5'!U11),"",'ONR 5'!U11)</f>
       </c>
       <c r="V38" s="235" t="str">
-        <f t="shared" si="109">IF(ISBLANK('ONR 5'!G11),"",'ONR 5'!G11)</f>
+        <f>IF(ISBLANK('ONR 5'!G11),"",'ONR 5'!G11)</f>
       </c>
       <c r="W38" s="142" t="str">
         <f>IF(ISBLANK('ONR 5'!V11),"",'ONR 5'!V11)</f>
@@ -35457,42 +34900,34 @@
         <f>IF(ISBLANK('ONR 5'!W11),"",'ONR 5'!W11)</f>
       </c>
       <c r="Y38" s="258" t="str">
-        <f t="shared" si="110">IF(ISBLANK('ONR 5'!I11),"",'ONR 5'!I11)</f>
+        <f>IF(ISBLANK('ONR 5'!I11),"",'ONR 5'!I11)</f>
       </c>
       <c r="Z38" s="236" t="str">
-        <f t="shared" ref="Z36:Z38" si="126">IF(ISBLANK('ONR 5'!D11),"",'ONR 5'!D11)</f>
+        <f>IF(ISBLANK('ONR 5'!D11),"",'ONR 5'!D11)</f>
       </c>
       <c r="AE38" s="206" t="n">
-        <f t="shared" si="111">IF(ISNUMBER(T38),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T38),0,1)</f>
       </c>
       <c r="AF38" s="206" t="n">
-        <f t="shared" si="112">IF(L38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L38=TRUE,1,0)</f>
       </c>
       <c r="AG38" s="206" t="n">
-        <f t="shared" si="113">IF(M38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M38=TRUE,1,0)</f>
       </c>
       <c r="AH38" s="206" t="n">
-        <f t="shared" si="114">IF(N38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N38=TRUE,1,0)</f>
       </c>
       <c r="AI38" s="206" t="n">
-        <f t="shared" si="115">IF(O38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O38=TRUE,1,0)</f>
       </c>
       <c r="AJ38" s="206" t="n">
-        <f t="shared" si="116">IF(P38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P38=TRUE,1,0)</f>
       </c>
       <c r="AK38" s="206" t="n">
-        <f t="shared" si="117">IF(Q38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q38=TRUE,1,0)</f>
       </c>
       <c r="AL38" s="206" t="n">
-        <f t="shared" si="118">IF(R38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R38=TRUE,1,0)</f>
       </c>
       <c r="AM38" t="n">
         <f>IF(LEN(TRIM(W38))&gt;0,1,0)</f>
@@ -35527,50 +34962,43 @@
         <f>IF(ISBLANK('ONR 5'!I12),"",'ONR 5'!I12)</f>
       </c>
       <c r="J39" s="219" t="str">
-        <f t="shared" ref="J39" si="127">IF(ISBLANK('ONR 5'!J12),"",'ONR 5'!J12)</f>
+        <f>IF(ISBLANK('ONR 5'!J12),"",'ONR 5'!J12)</f>
       </c>
       <c r="K39" s="233" t="str">
-        <f t="shared" ref="K39" si="128">IF(ISBLANK('ONR 5'!K12),"",'ONR 5'!K12)</f>
+        <f>IF(ISBLANK('ONR 5'!K12),"",'ONR 5'!K12)</f>
       </c>
       <c r="L39" s="233" t="b">
-        <f t="shared" ref="L39" si="129">IF(ISBLANK('ONR 5'!L12),"",'ONR 5'!L12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!L12),"",'ONR 5'!L12)</f>
       </c>
       <c r="M39" s="233" t="b">
-        <f t="shared" ref="M39" si="130">IF(ISBLANK('ONR 5'!M12),"",'ONR 5'!M12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!M12),"",'ONR 5'!M12)</f>
       </c>
       <c r="N39" s="233" t="b">
-        <f t="shared" ref="N39" si="131">IF(ISBLANK('ONR 5'!N12),"",'ONR 5'!N12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!N12),"",'ONR 5'!N12)</f>
       </c>
       <c r="O39" s="233" t="b">
-        <f t="shared" ref="O39" si="132">IF(ISBLANK('ONR 5'!O12),"",'ONR 5'!O12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!O12),"",'ONR 5'!O12)</f>
       </c>
       <c r="P39" s="233" t="b">
-        <f t="shared" ref="P39" si="133">IF(ISBLANK('ONR 5'!P12),"",'ONR 5'!P12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!P12),"",'ONR 5'!P12)</f>
       </c>
       <c r="Q39" s="233" t="b">
-        <f t="shared" ref="Q39" si="134">IF(ISBLANK('ONR 5'!Q12),"",'ONR 5'!Q12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!Q12),"",'ONR 5'!Q12)</f>
       </c>
       <c r="R39" s="233" t="b">
-        <f t="shared" ref="R39" si="135">IF(ISBLANK('ONR 5'!R12),"",'ONR 5'!R12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!R12),"",'ONR 5'!R12)</f>
       </c>
       <c r="S39" s="234" t="str">
-        <f t="shared" ref="S39" si="136">IF(ISBLANK('ONR 5'!S12),"",'ONR 5'!S12)</f>
+        <f>IF(ISBLANK('ONR 5'!S12),"",'ONR 5'!S12)</f>
       </c>
       <c r="T39" s="232" t="str">
-        <f t="shared" ref="T39" si="137">IF(ISBLANK('ONR 5'!T12),"",'ONR 5'!T12)</f>
+        <f>IF(ISBLANK('ONR 5'!T12),"",'ONR 5'!T12)</f>
       </c>
       <c r="U39" s="243" t="str">
-        <f t="shared" ref="U39" si="138">IF(ISBLANK('ONR 5'!U12),"",'ONR 5'!U12)</f>
+        <f>IF(ISBLANK('ONR 5'!U12),"",'ONR 5'!U12)</f>
       </c>
       <c r="V39" s="235" t="str">
-        <f t="shared" ref="V39" si="139">IF(ISBLANK('ONR 5'!G12),"",'ONR 5'!G12)</f>
+        <f>IF(ISBLANK('ONR 5'!G12),"",'ONR 5'!G12)</f>
       </c>
       <c r="W39" s="142" t="str">
         <f>IF(ISBLANK('ONR 5'!V12),"",'ONR 5'!V12)</f>
@@ -35579,42 +35007,34 @@
         <f>IF(ISBLANK('ONR 5'!W12),"",'ONR 5'!W12)</f>
       </c>
       <c r="Y39" s="258" t="str">
-        <f t="shared" ref="Y39" si="140">IF(ISBLANK('ONR 5'!I12),"",'ONR 5'!I12)</f>
+        <f>IF(ISBLANK('ONR 5'!I12),"",'ONR 5'!I12)</f>
       </c>
       <c r="Z39" s="236" t="str">
-        <f t="shared" ref="Z39" si="141">IF(ISBLANK('ONR 5'!D12),"",'ONR 5'!D12)</f>
+        <f>IF(ISBLANK('ONR 5'!D12),"",'ONR 5'!D12)</f>
       </c>
       <c r="AE39" s="206" t="n">
-        <f t="shared" ref="AE39" si="142">IF(ISNUMBER(T39),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T39),0,1)</f>
       </c>
       <c r="AF39" s="206" t="n">
-        <f t="shared" ref="AF39" si="143">IF(L39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L39=TRUE,1,0)</f>
       </c>
       <c r="AG39" s="206" t="n">
-        <f t="shared" ref="AG39" si="144">IF(M39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M39=TRUE,1,0)</f>
       </c>
       <c r="AH39" s="206" t="n">
-        <f t="shared" ref="AH39" si="145">IF(N39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N39=TRUE,1,0)</f>
       </c>
       <c r="AI39" s="206" t="n">
-        <f t="shared" ref="AI39" si="146">IF(O39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O39=TRUE,1,0)</f>
       </c>
       <c r="AJ39" s="206" t="n">
-        <f t="shared" ref="AJ39" si="147">IF(P39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P39=TRUE,1,0)</f>
       </c>
       <c r="AK39" s="206" t="n">
-        <f t="shared" ref="AK39" si="148">IF(Q39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q39=TRUE,1,0)</f>
       </c>
       <c r="AL39" s="206" t="n">
-        <f t="shared" ref="AL39" si="149">IF(R39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R39=TRUE,1,0)</f>
       </c>
       <c r="AM39" t="n">
         <f>IF(LEN(TRIM(W39))&gt;0,1,0)</f>

--- a/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
+++ b/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
@@ -27567,10 +27567,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
@@ -30038,10 +30038,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>123824</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
@@ -30365,10 +30365,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>498475</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>650874</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>266699</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
@@ -30397,10 +30397,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>66674</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>

--- a/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
+++ b/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
@@ -27567,10 +27567,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
@@ -30038,10 +30038,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>123824</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
@@ -30365,10 +30365,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>498475</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>650874</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>266699</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
@@ -30397,10 +30397,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>66674</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
@@ -31306,7 +31306,7 @@
         <f>IF(ISBLANK('ONR 1'!J7),"",'ONR 1'!J7)</f>
       </c>
       <c r="K5" s="227" t="str">
-        <f t="shared" ref="K5:K9" si="1">IF(ISBLANK('ONR 1'!K7),"",'ONR 1'!K7)</f>
+        <f>IF(ISBLANK('ONR 1'!K7),"",'ONR 1'!K7)</f>
       </c>
       <c r="L5" s="227" t="b">
         <f>IF(ISBLANK('ONR 1'!L7),"",'ONR 1'!L7)</f>
@@ -31337,16 +31337,16 @@
         <v>0</v>
       </c>
       <c r="S5" s="228" t="str">
-        <f t="shared" ref="S5:S9" si="2">IF(ISBLANK('ONR 1'!S7),"",'ONR 1'!S7)</f>
+        <f>IF(ISBLANK('ONR 1'!S7),"",'ONR 1'!S7)</f>
       </c>
       <c r="T5" s="226" t="str">
-        <f t="shared" ref="T5:T9" si="3">IF(ISBLANK('ONR 1'!T7),"",'ONR 1'!T7)</f>
+        <f>IF(ISBLANK('ONR 1'!T7),"",'ONR 1'!T7)</f>
       </c>
       <c r="U5" s="227" t="str">
-        <f t="shared" ref="U5:U9" si="4">IF(ISBLANK('ONR 1'!U7),"",'ONR 1'!U7)</f>
+        <f>IF(ISBLANK('ONR 1'!U7),"",'ONR 1'!U7)</f>
       </c>
       <c r="V5" s="229" t="str">
-        <f t="shared" ref="V5:V11" si="5">IF(ISBLANK('ONR 1'!G7),"",'ONR 1'!G7)</f>
+        <f>IF(ISBLANK('ONR 1'!G7),"",'ONR 1'!G7)</f>
       </c>
       <c r="W5" s="203" t="str">
         <f>IF(ISBLANK('ONR 1'!V7),"",'ONR 1'!V7)</f>
@@ -31355,42 +31355,34 @@
         <f>IF(ISBLANK('ONR 1'!W7),"",'ONR 1'!W7)</f>
       </c>
       <c r="Y5" s="230" t="str">
-        <f t="shared" ref="Y5:Y11" si="6">IF(ISBLANK('ONR 1'!I7),"",'ONR 1'!I7)</f>
+        <f>IF(ISBLANK('ONR 1'!I7),"",'ONR 1'!I7)</f>
       </c>
       <c r="Z5" s="230" t="str">
-        <f t="shared" ref="Z5:Z11" si="7">IF(ISBLANK('ONR 1'!D7),"",'ONR 1'!D7)</f>
+        <f>IF(ISBLANK('ONR 1'!D7),"",'ONR 1'!D7)</f>
       </c>
       <c r="AE5" s="206" t="n">
-        <f t="shared" ref="AE5:AE11" si="8">IF(ISNUMBER(T5),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T5),0,1)</f>
       </c>
       <c r="AF5" s="206" t="n">
-        <f t="shared" ref="AF5:AL11" si="9">IF(L5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L5=TRUE,1,0)</f>
       </c>
       <c r="AG5" s="206" t="n">
-        <f t="shared" si="9">IF(M5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M5=TRUE,1,0)</f>
       </c>
       <c r="AH5" s="206" t="n">
-        <f t="shared" si="9">IF(N5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N5=TRUE,1,0)</f>
       </c>
       <c r="AI5" s="206" t="n">
-        <f t="shared" si="9">IF(O5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O5=TRUE,1,0)</f>
       </c>
       <c r="AJ5" s="206" t="n">
-        <f t="shared" si="9">IF(P5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P5=TRUE,1,0)</f>
       </c>
       <c r="AK5" s="206" t="n">
-        <f t="shared" si="9">IF(Q5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q5=TRUE,1,0)</f>
       </c>
       <c r="AL5" s="206" t="n">
-        <f t="shared" si="9">IF(R5=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R5=TRUE,1,0)</f>
       </c>
       <c r="AM5" t="n">
         <f>IF(LEN(TRIM(W5))&gt;0,1,0)</f>
@@ -31426,50 +31418,43 @@
         <f>IF(ISBLANK('ONR 1'!I8),"",'ONR 1'!I8)</f>
       </c>
       <c r="J6" s="232" t="str">
-        <f t="shared" ref="J6:J9" si="10">IF(ISBLANK('ONR 1'!J8),"",'ONR 1'!J8)</f>
+        <f>IF(ISBLANK('ONR 1'!J8),"",'ONR 1'!J8)</f>
       </c>
       <c r="K6" s="233" t="str">
-        <f t="shared" si="1">IF(ISBLANK('ONR 1'!K8),"",'ONR 1'!K8)</f>
+        <f>IF(ISBLANK('ONR 1'!K8),"",'ONR 1'!K8)</f>
       </c>
       <c r="L6" s="233" t="b">
-        <f t="shared" ref="L6:L9" si="11">IF(ISBLANK('ONR 1'!L8),"",'ONR 1'!L8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L8),"",'ONR 1'!L8)</f>
       </c>
       <c r="M6" s="233" t="b">
-        <f t="shared" ref="M6:M9" si="12">IF(ISBLANK('ONR 1'!M8),"",'ONR 1'!M8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M8),"",'ONR 1'!M8)</f>
       </c>
       <c r="N6" s="233" t="b">
-        <f t="shared" ref="N6:N9" si="13">IF(ISBLANK('ONR 1'!N8),"",'ONR 1'!N8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N8),"",'ONR 1'!N8)</f>
       </c>
       <c r="O6" s="233" t="b">
-        <f t="shared" ref="O6:O9" si="14">IF(ISBLANK('ONR 1'!O8),"",'ONR 1'!O8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O8),"",'ONR 1'!O8)</f>
       </c>
       <c r="P6" s="233" t="b">
-        <f t="shared" ref="P6:P9" si="15">IF(ISBLANK('ONR 1'!P8),"",'ONR 1'!P8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P8),"",'ONR 1'!P8)</f>
       </c>
       <c r="Q6" s="233" t="b">
-        <f t="shared" ref="Q6:Q9" si="16">IF(ISBLANK('ONR 1'!Q8),"",'ONR 1'!Q8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q8),"",'ONR 1'!Q8)</f>
       </c>
       <c r="R6" s="233" t="b">
-        <f t="shared" ref="R6:R9" si="17">IF(ISBLANK('ONR 1'!R8),"",'ONR 1'!R8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R8),"",'ONR 1'!R8)</f>
       </c>
       <c r="S6" s="234" t="str">
-        <f t="shared" si="2">IF(ISBLANK('ONR 1'!S8),"",'ONR 1'!S8)</f>
+        <f>IF(ISBLANK('ONR 1'!S8),"",'ONR 1'!S8)</f>
       </c>
       <c r="T6" s="232" t="str">
-        <f t="shared" si="3">IF(ISBLANK('ONR 1'!T8),"",'ONR 1'!T8)</f>
+        <f>IF(ISBLANK('ONR 1'!T8),"",'ONR 1'!T8)</f>
       </c>
       <c r="U6" s="233" t="str">
-        <f t="shared" si="4">IF(ISBLANK('ONR 1'!U8),"",'ONR 1'!U8)</f>
+        <f>IF(ISBLANK('ONR 1'!U8),"",'ONR 1'!U8)</f>
       </c>
       <c r="V6" s="235" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G8),"",'ONR 1'!G8)</f>
+        <f>IF(ISBLANK('ONR 1'!G8),"",'ONR 1'!G8)</f>
       </c>
       <c r="W6" s="235" t="str">
         <f>IF(ISBLANK('ONR 1'!V8),"",'ONR 1'!V8)</f>
@@ -31478,42 +31463,34 @@
         <f>IF(ISBLANK('ONR 1'!W8),"",'ONR 1'!W8)</f>
       </c>
       <c r="Y6" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I8),"",'ONR 1'!I8)</f>
+        <f>IF(ISBLANK('ONR 1'!I8),"",'ONR 1'!I8)</f>
       </c>
       <c r="Z6" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D8),"",'ONR 1'!D8)</f>
+        <f>IF(ISBLANK('ONR 1'!D8),"",'ONR 1'!D8)</f>
       </c>
       <c r="AE6" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T6),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T6),0,1)</f>
       </c>
       <c r="AF6" s="206" t="n">
-        <f t="shared" si="9">IF(L6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L6=TRUE,1,0)</f>
       </c>
       <c r="AG6" s="206" t="n">
-        <f t="shared" si="9">IF(M6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M6=TRUE,1,0)</f>
       </c>
       <c r="AH6" s="206" t="n">
-        <f t="shared" si="9">IF(N6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N6=TRUE,1,0)</f>
       </c>
       <c r="AI6" s="206" t="n">
-        <f t="shared" si="9">IF(O6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O6=TRUE,1,0)</f>
       </c>
       <c r="AJ6" s="206" t="n">
-        <f t="shared" si="9">IF(P6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P6=TRUE,1,0)</f>
       </c>
       <c r="AK6" s="206" t="n">
-        <f t="shared" si="9">IF(Q6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q6=TRUE,1,0)</f>
       </c>
       <c r="AL6" s="206" t="n">
-        <f t="shared" si="9">IF(R6=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R6=TRUE,1,0)</f>
       </c>
       <c r="AM6" t="n">
         <f>IF(LEN(TRIM(W6))&gt;0,1,0)</f>
@@ -31549,50 +31526,43 @@
         <f>IF(ISBLANK('ONR 1'!I9),"",'ONR 1'!I9)</f>
       </c>
       <c r="J7" s="232" t="str">
-        <f t="shared" si="10">IF(ISBLANK('ONR 1'!J9),"",'ONR 1'!J9)</f>
+        <f>IF(ISBLANK('ONR 1'!J9),"",'ONR 1'!J9)</f>
       </c>
       <c r="K7" s="233" t="str">
-        <f t="shared" si="1">IF(ISBLANK('ONR 1'!K9),"",'ONR 1'!K9)</f>
+        <f>IF(ISBLANK('ONR 1'!K9),"",'ONR 1'!K9)</f>
       </c>
       <c r="L7" s="233" t="b">
-        <f t="shared" si="11">IF(ISBLANK('ONR 1'!L9),"",'ONR 1'!L9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L9),"",'ONR 1'!L9)</f>
       </c>
       <c r="M7" s="233" t="b">
-        <f t="shared" si="12">IF(ISBLANK('ONR 1'!M9),"",'ONR 1'!M9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M9),"",'ONR 1'!M9)</f>
       </c>
       <c r="N7" s="233" t="b">
-        <f t="shared" si="13">IF(ISBLANK('ONR 1'!N9),"",'ONR 1'!N9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N9),"",'ONR 1'!N9)</f>
       </c>
       <c r="O7" s="233" t="b">
-        <f t="shared" si="14">IF(ISBLANK('ONR 1'!O9),"",'ONR 1'!O9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O9),"",'ONR 1'!O9)</f>
       </c>
       <c r="P7" s="233" t="b">
-        <f t="shared" si="15">IF(ISBLANK('ONR 1'!P9),"",'ONR 1'!P9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P9),"",'ONR 1'!P9)</f>
       </c>
       <c r="Q7" s="233" t="b">
-        <f t="shared" si="16">IF(ISBLANK('ONR 1'!Q9),"",'ONR 1'!Q9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q9),"",'ONR 1'!Q9)</f>
       </c>
       <c r="R7" s="233" t="b">
-        <f t="shared" si="17">IF(ISBLANK('ONR 1'!R9),"",'ONR 1'!R9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R9),"",'ONR 1'!R9)</f>
       </c>
       <c r="S7" s="234" t="str">
-        <f t="shared" si="2">IF(ISBLANK('ONR 1'!S9),"",'ONR 1'!S9)</f>
+        <f>IF(ISBLANK('ONR 1'!S9),"",'ONR 1'!S9)</f>
       </c>
       <c r="T7" s="232" t="str">
-        <f t="shared" si="3">IF(ISBLANK('ONR 1'!T9),"",'ONR 1'!T9)</f>
+        <f>IF(ISBLANK('ONR 1'!T9),"",'ONR 1'!T9)</f>
       </c>
       <c r="U7" s="233" t="str">
-        <f t="shared" si="4">IF(ISBLANK('ONR 1'!U9),"",'ONR 1'!U9)</f>
+        <f>IF(ISBLANK('ONR 1'!U9),"",'ONR 1'!U9)</f>
       </c>
       <c r="V7" s="235" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G9),"",'ONR 1'!G9)</f>
+        <f>IF(ISBLANK('ONR 1'!G9),"",'ONR 1'!G9)</f>
       </c>
       <c r="W7" s="142" t="str">
         <f>IF(ISBLANK('ONR 1'!V9),"",'ONR 1'!V9)</f>
@@ -31601,42 +31571,34 @@
         <f>IF(ISBLANK('ONR 1'!W9),"",'ONR 1'!W9)</f>
       </c>
       <c r="Y7" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I9),"",'ONR 1'!I9)</f>
+        <f>IF(ISBLANK('ONR 1'!I9),"",'ONR 1'!I9)</f>
       </c>
       <c r="Z7" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D9),"",'ONR 1'!D9)</f>
+        <f>IF(ISBLANK('ONR 1'!D9),"",'ONR 1'!D9)</f>
       </c>
       <c r="AE7" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T7),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T7),0,1)</f>
       </c>
       <c r="AF7" s="206" t="n">
-        <f t="shared" si="9">IF(L7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L7=TRUE,1,0)</f>
       </c>
       <c r="AG7" s="206" t="n">
-        <f t="shared" si="9">IF(M7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M7=TRUE,1,0)</f>
       </c>
       <c r="AH7" s="206" t="n">
-        <f t="shared" si="9">IF(N7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N7=TRUE,1,0)</f>
       </c>
       <c r="AI7" s="206" t="n">
-        <f t="shared" si="9">IF(O7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O7=TRUE,1,0)</f>
       </c>
       <c r="AJ7" s="206" t="n">
-        <f t="shared" si="9">IF(P7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P7=TRUE,1,0)</f>
       </c>
       <c r="AK7" s="206" t="n">
-        <f t="shared" si="9">IF(Q7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q7=TRUE,1,0)</f>
       </c>
       <c r="AL7" s="206" t="n">
-        <f t="shared" si="9">IF(R7=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R7=TRUE,1,0)</f>
       </c>
       <c r="AM7" t="n">
         <f>IF(LEN(TRIM(W7))&gt;0,1,0)</f>
@@ -31672,50 +31634,43 @@
         <f>IF(ISBLANK('ONR 1'!I10),"",'ONR 1'!I10)</f>
       </c>
       <c r="J8" s="232" t="str">
-        <f t="shared" si="10">IF(ISBLANK('ONR 1'!J10),"",'ONR 1'!J10)</f>
+        <f>IF(ISBLANK('ONR 1'!J10),"",'ONR 1'!J10)</f>
       </c>
       <c r="K8" s="233" t="str">
-        <f t="shared" si="1">IF(ISBLANK('ONR 1'!K10),"",'ONR 1'!K10)</f>
+        <f>IF(ISBLANK('ONR 1'!K10),"",'ONR 1'!K10)</f>
       </c>
       <c r="L8" s="233" t="b">
-        <f t="shared" si="11">IF(ISBLANK('ONR 1'!L10),"",'ONR 1'!L10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L10),"",'ONR 1'!L10)</f>
       </c>
       <c r="M8" s="233" t="b">
-        <f t="shared" si="12">IF(ISBLANK('ONR 1'!M10),"",'ONR 1'!M10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M10),"",'ONR 1'!M10)</f>
       </c>
       <c r="N8" s="233" t="b">
-        <f t="shared" si="13">IF(ISBLANK('ONR 1'!N10),"",'ONR 1'!N10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N10),"",'ONR 1'!N10)</f>
       </c>
       <c r="O8" s="233" t="b">
-        <f t="shared" si="14">IF(ISBLANK('ONR 1'!O10),"",'ONR 1'!O10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O10),"",'ONR 1'!O10)</f>
       </c>
       <c r="P8" s="233" t="b">
-        <f t="shared" si="15">IF(ISBLANK('ONR 1'!P10),"",'ONR 1'!P10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P10),"",'ONR 1'!P10)</f>
       </c>
       <c r="Q8" s="233" t="b">
-        <f t="shared" si="16">IF(ISBLANK('ONR 1'!Q10),"",'ONR 1'!Q10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q10),"",'ONR 1'!Q10)</f>
       </c>
       <c r="R8" s="233" t="b">
-        <f t="shared" si="17">IF(ISBLANK('ONR 1'!R10),"",'ONR 1'!R10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R10),"",'ONR 1'!R10)</f>
       </c>
       <c r="S8" s="234" t="str">
-        <f t="shared" si="2">IF(ISBLANK('ONR 1'!S10),"",'ONR 1'!S10)</f>
+        <f>IF(ISBLANK('ONR 1'!S10),"",'ONR 1'!S10)</f>
       </c>
       <c r="T8" s="232" t="str">
-        <f t="shared" si="3">IF(ISBLANK('ONR 1'!T10),"",'ONR 1'!T10)</f>
+        <f>IF(ISBLANK('ONR 1'!T10),"",'ONR 1'!T10)</f>
       </c>
       <c r="U8" s="233" t="str">
-        <f t="shared" si="4">IF(ISBLANK('ONR 1'!U10),"",'ONR 1'!U10)</f>
+        <f>IF(ISBLANK('ONR 1'!U10),"",'ONR 1'!U10)</f>
       </c>
       <c r="V8" s="239" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G10),"",'ONR 1'!G10)</f>
+        <f>IF(ISBLANK('ONR 1'!G10),"",'ONR 1'!G10)</f>
       </c>
       <c r="W8" s="210" t="str">
         <f>IF(ISBLANK('ONR 1'!V10),"",'ONR 1'!V10)</f>
@@ -31724,42 +31679,34 @@
         <f>IF(ISBLANK('ONR 1'!W10),"",'ONR 1'!W10)</f>
       </c>
       <c r="Y8" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I10),"",'ONR 1'!I10)</f>
+        <f>IF(ISBLANK('ONR 1'!I10),"",'ONR 1'!I10)</f>
       </c>
       <c r="Z8" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D10),"",'ONR 1'!D10)</f>
+        <f>IF(ISBLANK('ONR 1'!D10),"",'ONR 1'!D10)</f>
       </c>
       <c r="AE8" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T8),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T8),0,1)</f>
       </c>
       <c r="AF8" s="206" t="n">
-        <f t="shared" si="9">IF(L8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L8=TRUE,1,0)</f>
       </c>
       <c r="AG8" s="206" t="n">
-        <f t="shared" si="9">IF(M8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M8=TRUE,1,0)</f>
       </c>
       <c r="AH8" s="206" t="n">
-        <f t="shared" si="9">IF(N8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N8=TRUE,1,0)</f>
       </c>
       <c r="AI8" s="206" t="n">
-        <f t="shared" si="9">IF(O8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O8=TRUE,1,0)</f>
       </c>
       <c r="AJ8" s="206" t="n">
-        <f t="shared" si="9">IF(P8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P8=TRUE,1,0)</f>
       </c>
       <c r="AK8" s="206" t="n">
-        <f t="shared" si="9">IF(Q8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q8=TRUE,1,0)</f>
       </c>
       <c r="AL8" s="206" t="n">
-        <f t="shared" si="9">IF(R8=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R8=TRUE,1,0)</f>
       </c>
       <c r="AM8" t="n">
         <f>IF(LEN(TRIM(W8))&gt;0,1,0)</f>
@@ -31795,50 +31742,43 @@
         <f>IF(ISBLANK('ONR 1'!I11),"",'ONR 1'!I11)</f>
       </c>
       <c r="J9" s="232" t="str">
-        <f t="shared" si="10">IF(ISBLANK('ONR 1'!J11),"",'ONR 1'!J11)</f>
+        <f>IF(ISBLANK('ONR 1'!J11),"",'ONR 1'!J11)</f>
       </c>
       <c r="K9" s="233" t="str">
-        <f t="shared" si="1">IF(ISBLANK('ONR 1'!K11),"",'ONR 1'!K11)</f>
+        <f>IF(ISBLANK('ONR 1'!K11),"",'ONR 1'!K11)</f>
       </c>
       <c r="L9" s="233" t="b">
-        <f t="shared" si="11">IF(ISBLANK('ONR 1'!L11),"",'ONR 1'!L11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L11),"",'ONR 1'!L11)</f>
       </c>
       <c r="M9" s="233" t="b">
-        <f t="shared" si="12">IF(ISBLANK('ONR 1'!M11),"",'ONR 1'!M11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M11),"",'ONR 1'!M11)</f>
       </c>
       <c r="N9" s="233" t="b">
-        <f t="shared" si="13">IF(ISBLANK('ONR 1'!N11),"",'ONR 1'!N11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N11),"",'ONR 1'!N11)</f>
       </c>
       <c r="O9" s="233" t="b">
-        <f t="shared" si="14">IF(ISBLANK('ONR 1'!O11),"",'ONR 1'!O11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O11),"",'ONR 1'!O11)</f>
       </c>
       <c r="P9" s="233" t="b">
-        <f t="shared" si="15">IF(ISBLANK('ONR 1'!P11),"",'ONR 1'!P11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P11),"",'ONR 1'!P11)</f>
       </c>
       <c r="Q9" s="233" t="b">
-        <f t="shared" si="16">IF(ISBLANK('ONR 1'!Q11),"",'ONR 1'!Q11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q11),"",'ONR 1'!Q11)</f>
       </c>
       <c r="R9" s="233" t="b">
-        <f t="shared" si="17">IF(ISBLANK('ONR 1'!R11),"",'ONR 1'!R11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R11),"",'ONR 1'!R11)</f>
       </c>
       <c r="S9" s="234" t="str">
-        <f t="shared" si="2">IF(ISBLANK('ONR 1'!S11),"",'ONR 1'!S11)</f>
+        <f>IF(ISBLANK('ONR 1'!S11),"",'ONR 1'!S11)</f>
       </c>
       <c r="T9" s="232" t="str">
-        <f t="shared" si="3">IF(ISBLANK('ONR 1'!T11),"",'ONR 1'!T11)</f>
+        <f>IF(ISBLANK('ONR 1'!T11),"",'ONR 1'!T11)</f>
       </c>
       <c r="U9" s="233" t="str">
-        <f t="shared" si="4">IF(ISBLANK('ONR 1'!U11),"",'ONR 1'!U11)</f>
+        <f>IF(ISBLANK('ONR 1'!U11),"",'ONR 1'!U11)</f>
       </c>
       <c r="V9" s="241" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G11),"",'ONR 1'!G11)</f>
+        <f>IF(ISBLANK('ONR 1'!G11),"",'ONR 1'!G11)</f>
       </c>
       <c r="W9" s="241" t="str">
         <f>IF(ISBLANK('ONR 1'!V11),"",'ONR 1'!V11)</f>
@@ -31847,42 +31787,34 @@
         <f>IF(ISBLANK('ONR 1'!W11),"",'ONR 1'!W11)</f>
       </c>
       <c r="Y9" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I11),"",'ONR 1'!I11)</f>
+        <f>IF(ISBLANK('ONR 1'!I11),"",'ONR 1'!I11)</f>
       </c>
       <c r="Z9" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D11),"",'ONR 1'!D11)</f>
+        <f>IF(ISBLANK('ONR 1'!D11),"",'ONR 1'!D11)</f>
       </c>
       <c r="AE9" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T9),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T9),0,1)</f>
       </c>
       <c r="AF9" s="206" t="n">
-        <f t="shared" si="9">IF(L9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L9=TRUE,1,0)</f>
       </c>
       <c r="AG9" s="206" t="n">
-        <f t="shared" si="9">IF(M9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M9=TRUE,1,0)</f>
       </c>
       <c r="AH9" s="206" t="n">
-        <f t="shared" si="9">IF(N9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N9=TRUE,1,0)</f>
       </c>
       <c r="AI9" s="206" t="n">
-        <f t="shared" si="9">IF(O9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O9=TRUE,1,0)</f>
       </c>
       <c r="AJ9" s="206" t="n">
-        <f t="shared" si="9">IF(P9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P9=TRUE,1,0)</f>
       </c>
       <c r="AK9" s="206" t="n">
-        <f t="shared" si="9">IF(Q9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q9=TRUE,1,0)</f>
       </c>
       <c r="AL9" s="206" t="n">
-        <f t="shared" si="9">IF(R9=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R9=TRUE,1,0)</f>
       </c>
       <c r="AM9" t="n">
         <f>IF(LEN(TRIM(W9))&gt;0,1,0)</f>
@@ -31918,50 +31850,43 @@
         <f>IF(ISBLANK('ONR 1'!I12),"",'ONR 1'!I12)</f>
       </c>
       <c r="J10" s="232" t="str">
-        <f t="shared" ref="J10:J11" si="18">IF(ISBLANK('ONR 1'!J12),"",'ONR 1'!J12)</f>
+        <f>IF(ISBLANK('ONR 1'!J12),"",'ONR 1'!J12)</f>
       </c>
       <c r="K10" s="233" t="str">
-        <f t="shared" ref="K10:K11" si="19">IF(ISBLANK('ONR 1'!K12),"",'ONR 1'!K12)</f>
+        <f>IF(ISBLANK('ONR 1'!K12),"",'ONR 1'!K12)</f>
       </c>
       <c r="L10" s="233" t="b">
-        <f t="shared" ref="L10:L11" si="20">IF(ISBLANK('ONR 1'!L12),"",'ONR 1'!L12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L12),"",'ONR 1'!L12)</f>
       </c>
       <c r="M10" s="233" t="b">
-        <f t="shared" ref="M10:M11" si="21">IF(ISBLANK('ONR 1'!M12),"",'ONR 1'!M12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M12),"",'ONR 1'!M12)</f>
       </c>
       <c r="N10" s="233" t="b">
-        <f t="shared" ref="N10:N11" si="22">IF(ISBLANK('ONR 1'!N12),"",'ONR 1'!N12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N12),"",'ONR 1'!N12)</f>
       </c>
       <c r="O10" s="233" t="b">
-        <f t="shared" ref="O10:O11" si="23">IF(ISBLANK('ONR 1'!O12),"",'ONR 1'!O12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O12),"",'ONR 1'!O12)</f>
       </c>
       <c r="P10" s="233" t="b">
-        <f t="shared" ref="P10:P11" si="24">IF(ISBLANK('ONR 1'!P12),"",'ONR 1'!P12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P12),"",'ONR 1'!P12)</f>
       </c>
       <c r="Q10" s="233" t="b">
-        <f t="shared" ref="Q10:Q11" si="25">IF(ISBLANK('ONR 1'!Q12),"",'ONR 1'!Q12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q12),"",'ONR 1'!Q12)</f>
       </c>
       <c r="R10" s="233" t="b">
-        <f t="shared" ref="R10:R11" si="26">IF(ISBLANK('ONR 1'!R12),"",'ONR 1'!R12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R12),"",'ONR 1'!R12)</f>
       </c>
       <c r="S10" s="234" t="str">
-        <f t="shared" ref="S10:S11" si="27">IF(ISBLANK('ONR 1'!S12),"",'ONR 1'!S12)</f>
+        <f>IF(ISBLANK('ONR 1'!S12),"",'ONR 1'!S12)</f>
       </c>
       <c r="T10" s="232" t="str">
-        <f t="shared" ref="T10:T11" si="28">IF(ISBLANK('ONR 1'!T12),"",'ONR 1'!T12)</f>
+        <f>IF(ISBLANK('ONR 1'!T12),"",'ONR 1'!T12)</f>
       </c>
       <c r="U10" s="233" t="str">
-        <f t="shared" ref="U10:U11" si="29">IF(ISBLANK('ONR 1'!U12),"",'ONR 1'!U12)</f>
+        <f>IF(ISBLANK('ONR 1'!U12),"",'ONR 1'!U12)</f>
       </c>
       <c r="V10" s="241" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G12),"",'ONR 1'!G12)</f>
+        <f>IF(ISBLANK('ONR 1'!G12),"",'ONR 1'!G12)</f>
       </c>
       <c r="W10" s="241" t="str">
         <f>IF(ISBLANK('ONR 1'!V12),"",'ONR 1'!V12)</f>
@@ -31970,42 +31895,34 @@
         <f>IF(ISBLANK('ONR 1'!W12),"",'ONR 1'!W12)</f>
       </c>
       <c r="Y10" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I12),"",'ONR 1'!I12)</f>
+        <f>IF(ISBLANK('ONR 1'!I12),"",'ONR 1'!I12)</f>
       </c>
       <c r="Z10" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D12),"",'ONR 1'!D12)</f>
+        <f>IF(ISBLANK('ONR 1'!D12),"",'ONR 1'!D12)</f>
       </c>
       <c r="AE10" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T10),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T10),0,1)</f>
       </c>
       <c r="AF10" s="206" t="n">
-        <f t="shared" si="9">IF(L10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L10=TRUE,1,0)</f>
       </c>
       <c r="AG10" s="206" t="n">
-        <f t="shared" si="9">IF(M10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M10=TRUE,1,0)</f>
       </c>
       <c r="AH10" s="206" t="n">
-        <f t="shared" si="9">IF(N10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N10=TRUE,1,0)</f>
       </c>
       <c r="AI10" s="206" t="n">
-        <f t="shared" si="9">IF(O10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O10=TRUE,1,0)</f>
       </c>
       <c r="AJ10" s="206" t="n">
-        <f t="shared" si="9">IF(P10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P10=TRUE,1,0)</f>
       </c>
       <c r="AK10" s="206" t="n">
-        <f t="shared" si="9">IF(Q10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q10=TRUE,1,0)</f>
       </c>
       <c r="AL10" s="206" t="n">
-        <f t="shared" si="9">IF(R10=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R10=TRUE,1,0)</f>
       </c>
       <c r="AM10" t="n">
         <f>IF(LEN(TRIM(W10))&gt;0,1,0)</f>
@@ -32041,50 +31958,43 @@
         <f>IF(ISBLANK('ONR 1'!I13),"",'ONR 1'!I13)</f>
       </c>
       <c r="J11" s="232" t="str">
-        <f t="shared" si="18">IF(ISBLANK('ONR 1'!J13),"",'ONR 1'!J13)</f>
+        <f>IF(ISBLANK('ONR 1'!J13),"",'ONR 1'!J13)</f>
       </c>
       <c r="K11" s="233" t="str">
-        <f t="shared" si="19">IF(ISBLANK('ONR 1'!K13),"",'ONR 1'!K13)</f>
+        <f>IF(ISBLANK('ONR 1'!K13),"",'ONR 1'!K13)</f>
       </c>
       <c r="L11" s="233" t="b">
-        <f t="shared" si="20">IF(ISBLANK('ONR 1'!L13),"",'ONR 1'!L13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!L13),"",'ONR 1'!L13)</f>
       </c>
       <c r="M11" s="233" t="b">
-        <f t="shared" si="21">IF(ISBLANK('ONR 1'!M13),"",'ONR 1'!M13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!M13),"",'ONR 1'!M13)</f>
       </c>
       <c r="N11" s="233" t="b">
-        <f t="shared" si="22">IF(ISBLANK('ONR 1'!N13),"",'ONR 1'!N13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!N13),"",'ONR 1'!N13)</f>
       </c>
       <c r="O11" s="233" t="b">
-        <f t="shared" si="23">IF(ISBLANK('ONR 1'!O13),"",'ONR 1'!O13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!O13),"",'ONR 1'!O13)</f>
       </c>
       <c r="P11" s="233" t="b">
-        <f t="shared" si="24">IF(ISBLANK('ONR 1'!P13),"",'ONR 1'!P13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!P13),"",'ONR 1'!P13)</f>
       </c>
       <c r="Q11" s="233" t="b">
-        <f t="shared" si="25">IF(ISBLANK('ONR 1'!Q13),"",'ONR 1'!Q13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!Q13),"",'ONR 1'!Q13)</f>
       </c>
       <c r="R11" s="233" t="b">
-        <f t="shared" si="26">IF(ISBLANK('ONR 1'!R13),"",'ONR 1'!R13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 1'!R13),"",'ONR 1'!R13)</f>
       </c>
       <c r="S11" s="234" t="str">
-        <f t="shared" si="27">IF(ISBLANK('ONR 1'!S13),"",'ONR 1'!S13)</f>
+        <f>IF(ISBLANK('ONR 1'!S13),"",'ONR 1'!S13)</f>
       </c>
       <c r="T11" s="232" t="str">
-        <f t="shared" si="28">IF(ISBLANK('ONR 1'!T13),"",'ONR 1'!T13)</f>
+        <f>IF(ISBLANK('ONR 1'!T13),"",'ONR 1'!T13)</f>
       </c>
       <c r="U11" s="233" t="str">
-        <f t="shared" si="29">IF(ISBLANK('ONR 1'!U13),"",'ONR 1'!U13)</f>
+        <f>IF(ISBLANK('ONR 1'!U13),"",'ONR 1'!U13)</f>
       </c>
       <c r="V11" s="241" t="str">
-        <f t="shared" si="5">IF(ISBLANK('ONR 1'!G13),"",'ONR 1'!G13)</f>
+        <f>IF(ISBLANK('ONR 1'!G13),"",'ONR 1'!G13)</f>
       </c>
       <c r="W11" s="241" t="str">
         <f>IF(ISBLANK('ONR 1'!V13),"",'ONR 1'!V13)</f>
@@ -32093,42 +32003,34 @@
         <f>IF(ISBLANK('ONR 1'!W13),"",'ONR 1'!W13)</f>
       </c>
       <c r="Y11" s="236" t="str">
-        <f t="shared" si="6">IF(ISBLANK('ONR 1'!I13),"",'ONR 1'!I13)</f>
+        <f>IF(ISBLANK('ONR 1'!I13),"",'ONR 1'!I13)</f>
       </c>
       <c r="Z11" s="236" t="str">
-        <f t="shared" si="7">IF(ISBLANK('ONR 1'!D13),"",'ONR 1'!D13)</f>
+        <f>IF(ISBLANK('ONR 1'!D13),"",'ONR 1'!D13)</f>
       </c>
       <c r="AE11" s="206" t="n">
-        <f t="shared" si="8">IF(ISNUMBER(T11),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T11),0,1)</f>
       </c>
       <c r="AF11" s="206" t="n">
-        <f t="shared" si="9">IF(L11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L11=TRUE,1,0)</f>
       </c>
       <c r="AG11" s="206" t="n">
-        <f t="shared" si="9">IF(M11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M11=TRUE,1,0)</f>
       </c>
       <c r="AH11" s="206" t="n">
-        <f t="shared" si="9">IF(N11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N11=TRUE,1,0)</f>
       </c>
       <c r="AI11" s="206" t="n">
-        <f t="shared" si="9">IF(O11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O11=TRUE,1,0)</f>
       </c>
       <c r="AJ11" s="206" t="n">
-        <f t="shared" si="9">IF(P11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P11=TRUE,1,0)</f>
       </c>
       <c r="AK11" s="206" t="n">
-        <f t="shared" si="9">IF(Q11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q11=TRUE,1,0)</f>
       </c>
       <c r="AL11" s="206" t="n">
-        <f t="shared" si="9">IF(R11=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R11=TRUE,1,0)</f>
       </c>
       <c r="AM11" t="n">
         <f>IF(LEN(TRIM(W11))&gt;0,1,0)</f>
@@ -32366,7 +32268,7 @@
         <f>IF(ISBLANK('ONR 2'!J7),"",'ONR 2'!J7)</f>
       </c>
       <c r="K14" s="227" t="str">
-        <f t="shared" ref="K14" si="31">IF(ISBLANK('ONR 2'!K7),"",'ONR 2'!K7)</f>
+        <f>IF(ISBLANK('ONR 2'!K7),"",'ONR 2'!K7)</f>
       </c>
       <c r="L14" s="227" t="b">
         <f>IF(ISBLANK('ONR 2'!L7),"",'ONR 2'!L7)</f>
@@ -32397,13 +32299,13 @@
         <v>0</v>
       </c>
       <c r="S14" s="228" t="str">
-        <f t="shared" ref="S14" si="32">IF(ISBLANK('ONR 2'!S7),"",'ONR 2'!S7)</f>
+        <f>IF(ISBLANK('ONR 2'!S7),"",'ONR 2'!S7)</f>
       </c>
       <c r="T14" s="226" t="str">
-        <f t="shared" ref="T14" si="33">IF(ISBLANK('ONR 2'!T7),"",'ONR 2'!T7)</f>
+        <f>IF(ISBLANK('ONR 2'!T7),"",'ONR 2'!T7)</f>
       </c>
       <c r="U14" s="242" t="str">
-        <f t="shared" ref="U14" si="34">IF(ISBLANK('ONR 2'!U7),"",'ONR 2'!U7)</f>
+        <f>IF(ISBLANK('ONR 2'!U7),"",'ONR 2'!U7)</f>
       </c>
       <c r="V14" s="229" t="str">
         <f>IF(ISBLANK('ONR 2'!G7),"",'ONR 2'!G7)</f>
@@ -32425,32 +32327,25 @@
         <v>1</v>
       </c>
       <c r="AF14" s="206" t="n">
-        <f t="shared" ref="AF14:AL17" si="35">IF(L14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L14=TRUE,1,0)</f>
       </c>
       <c r="AG14" s="206" t="n">
-        <f t="shared" si="35">IF(M14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M14=TRUE,1,0)</f>
       </c>
       <c r="AH14" s="206" t="n">
-        <f t="shared" si="35">IF(N14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N14=TRUE,1,0)</f>
       </c>
       <c r="AI14" s="206" t="n">
-        <f t="shared" si="35">IF(O14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O14=TRUE,1,0)</f>
       </c>
       <c r="AJ14" s="206" t="n">
-        <f t="shared" si="35">IF(P14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P14=TRUE,1,0)</f>
       </c>
       <c r="AK14" s="206" t="n">
-        <f t="shared" si="35">IF(Q14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q14=TRUE,1,0)</f>
       </c>
       <c r="AL14" s="206" t="n">
-        <f t="shared" si="35">IF(R14=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R14=TRUE,1,0)</f>
       </c>
       <c r="AM14" t="n">
         <f>IF(LEN(TRIM(W14))&gt;0,1,0)</f>
@@ -32486,47 +32381,40 @@
         <f>IF(ISBLANK('ONR 2'!I8),"",'ONR 2'!I8)</f>
       </c>
       <c r="J15" s="218" t="str">
-        <f t="shared" ref="J15:J17" si="36">IF(ISBLANK('ONR 2'!J8),"",'ONR 2'!J8)</f>
+        <f>IF(ISBLANK('ONR 2'!J8),"",'ONR 2'!J8)</f>
       </c>
       <c r="K15" s="227" t="str">
-        <f t="shared" ref="K15:K17" si="37">IF(ISBLANK('ONR 2'!K8),"",'ONR 2'!K8)</f>
+        <f>IF(ISBLANK('ONR 2'!K8),"",'ONR 2'!K8)</f>
       </c>
       <c r="L15" s="227" t="b">
-        <f t="shared" ref="L15:L17" si="38">IF(ISBLANK('ONR 2'!L8),"",'ONR 2'!L8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!L8),"",'ONR 2'!L8)</f>
       </c>
       <c r="M15" s="227" t="b">
-        <f t="shared" ref="M15:M17" si="39">IF(ISBLANK('ONR 2'!M8),"",'ONR 2'!M8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!M8),"",'ONR 2'!M8)</f>
       </c>
       <c r="N15" s="227" t="b">
-        <f t="shared" ref="N15:N17" si="40">IF(ISBLANK('ONR 2'!N8),"",'ONR 2'!N8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!N8),"",'ONR 2'!N8)</f>
       </c>
       <c r="O15" s="227" t="b">
-        <f t="shared" ref="O15:O17" si="41">IF(ISBLANK('ONR 2'!O8),"",'ONR 2'!O8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!O8),"",'ONR 2'!O8)</f>
       </c>
       <c r="P15" s="227" t="b">
-        <f t="shared" ref="P15:P17" si="42">IF(ISBLANK('ONR 2'!P8),"",'ONR 2'!P8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!P8),"",'ONR 2'!P8)</f>
       </c>
       <c r="Q15" s="227" t="b">
-        <f t="shared" ref="Q15:Q17" si="43">IF(ISBLANK('ONR 2'!Q8),"",'ONR 2'!Q8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!Q8),"",'ONR 2'!Q8)</f>
       </c>
       <c r="R15" s="227" t="b">
-        <f t="shared" ref="R15:R17" si="44">IF(ISBLANK('ONR 2'!R8),"",'ONR 2'!R8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 2'!R8),"",'ONR 2'!R8)</f>
       </c>
       <c r="S15" s="228" t="str">
-        <f t="shared" ref="S15:S17" si="45">IF(ISBLANK('ONR 2'!S8),"",'ONR 2'!S8)</f>
+        <f>IF(ISBLANK('ONR 2'!S8),"",'ONR 2'!S8)</f>
       </c>
       <c r="T15" s="226" t="str">
-        <f t="shared" ref="T15:T17" si="46">IF(ISBLANK('ONR 2'!T8),"",'ONR 2'!T8)</f>
+        <f>IF(ISBLANK('ONR 2'!T8),"",'ONR 2'!T8)</f>
       </c>
       <c r="U15" s="242" t="str">
-        <f t="shared" ref="U15:U17" si="47">IF(ISBLANK('ONR 2'!U8),"",'ONR 2'!U8)</f>
+        <f>IF(ISBLANK('ONR 2'!U8),"",'ONR 2'!U8)</f>
       </c>
       <c r="V15" s="229" t="str">
         <f>IF(ISBLANK('ONR 2'!G8),"",'ONR 2'!G8)</f>
@@ -32548,32 +32436,25 @@
         <v>1</v>
       </c>
       <c r="AF15" s="206" t="n">
-        <f t="shared" si="35">IF(L15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L15=TRUE,1,0)</f>
       </c>
       <c r="AG15" s="206" t="n">
-        <f t="shared" si="35">IF(M15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M15=TRUE,1,0)</f>
       </c>
       <c r="AH15" s="206" t="n">
-        <f t="shared" si="35">IF(N15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N15=TRUE,1,0)</f>
       </c>
       <c r="AI15" s="206" t="n">
-        <f t="shared" si="35">IF(O15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O15=TRUE,1,0)</f>
       </c>
       <c r="AJ15" s="206" t="n">
-        <f t="shared" si="35">IF(P15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P15=TRUE,1,0)</f>
       </c>
       <c r="AK15" s="206" t="n">
-        <f t="shared" si="35">IF(Q15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q15=TRUE,1,0)</f>
       </c>
       <c r="AL15" s="206" t="n">
-        <f t="shared" si="35">IF(R15=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R15=TRUE,1,0)</f>
       </c>
       <c r="AM15" t="n">
         <f>IF(LEN(TRIM(W15))&gt;0,1,0)</f>
@@ -32609,90 +32490,47 @@
         <f>IF(ISBLANK('ONR 2'!I9),"",'ONR 2'!I9)</f>
       </c>
       <c r="J16" s="218" t="str">
-        <f t="shared" si="36">IF(ISBLANK('ONR 2'!J9),"",'ONR 2'!J9)</f>
-      </c>
-      <c r="K17" s="227" t="str">
-        <f t="shared" si="37">IF(ISBLANK('ONR 2'!K10),"",'ONR 2'!K10)</f>
+        <f>IF(ISBLANK('ONR 2'!J9),"",'ONR 2'!J9)</f>
       </c>
       <c r="K16" t="str" s="227">
         <f>IF(ISBLANK('ONR 2'!K9),"",'ONR 2'!K9)</f>
-      </c>
-      <c r="L17" s="227" t="b">
-        <f t="shared" si="38">IF(ISBLANK('ONR 2'!L10),"",'ONR 2'!L10)</f>
-        <v>0</v>
       </c>
       <c r="L16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!L9),"",'ONR 2'!L9)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="227" t="b">
-        <f t="shared" si="39">IF(ISBLANK('ONR 2'!M10),"",'ONR 2'!M10)</f>
-        <v>0</v>
-      </c>
       <c r="M16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!M9),"",'ONR 2'!M9)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="227" t="b">
-        <f t="shared" si="40">IF(ISBLANK('ONR 2'!N10),"",'ONR 2'!N10)</f>
-        <v>0</v>
-      </c>
       <c r="N16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!N9),"",'ONR 2'!N9)</f>
         <v>0</v>
       </c>
-      <c r="O17" s="227" t="b">
-        <f t="shared" si="41">IF(ISBLANK('ONR 2'!O10),"",'ONR 2'!O10)</f>
-        <v>0</v>
-      </c>
       <c r="O16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!O9),"",'ONR 2'!O9)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="227" t="b">
-        <f t="shared" si="42">IF(ISBLANK('ONR 2'!P10),"",'ONR 2'!P10)</f>
-        <v>0</v>
-      </c>
       <c r="P16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!P9),"",'ONR 2'!P9)</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="227" t="b">
-        <f t="shared" si="43">IF(ISBLANK('ONR 2'!Q10),"",'ONR 2'!Q10)</f>
-        <v>0</v>
-      </c>
       <c r="Q16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!Q9),"",'ONR 2'!Q9)</f>
         <v>0</v>
       </c>
-      <c r="R17" s="227" t="b">
-        <f t="shared" si="44">IF(ISBLANK('ONR 2'!R10),"",'ONR 2'!R10)</f>
-        <v>0</v>
-      </c>
       <c r="R16" t="b" s="227">
         <f>IF(ISBLANK('ONR 2'!R9),"",'ONR 2'!R9)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="228" t="str">
-        <f t="shared" si="45">IF(ISBLANK('ONR 2'!S10),"",'ONR 2'!S10)</f>
-      </c>
       <c r="S16" t="str" s="228">
         <f>IF(ISBLANK('ONR 2'!S9),"",'ONR 2'!S9)</f>
       </c>
-      <c r="T17" s="226" t="str">
-        <f t="shared" si="46">IF(ISBLANK('ONR 2'!T10),"",'ONR 2'!T10)</f>
-      </c>
       <c r="T16" t="str" s="226">
         <f>IF(ISBLANK('ONR 2'!T9),"",'ONR 2'!T9)</f>
       </c>
-      <c r="U17" s="242" t="str">
-        <f t="shared" si="47">IF(ISBLANK('ONR 2'!U10),"",'ONR 2'!U10)</f>
-      </c>
       <c r="U16" t="str" s="242">
         <f>IF(ISBLANK('ONR 2'!U9),"",'ONR 2'!U9)</f>
-      </c>
-      <c r="V17" s="229" t="str">
-        <f>IF(ISBLANK('ONR 2'!G10),"",'ONR 2'!G10)</f>
       </c>
       <c r="V16" t="str" s="229">
         <f>IF(ISBLANK('ONR 2'!G9),"",'ONR 2'!G9)</f>
@@ -32714,32 +32552,25 @@
         <v>1</v>
       </c>
       <c r="AF16" s="206" t="n">
-        <f t="shared" si="35">IF(L16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L16=TRUE,1,0)</f>
       </c>
       <c r="AG16" s="206" t="n">
-        <f t="shared" si="35">IF(M16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M16=TRUE,1,0)</f>
       </c>
       <c r="AH16" s="206" t="n">
-        <f t="shared" si="35">IF(N16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N16=TRUE,1,0)</f>
       </c>
       <c r="AI16" s="206" t="n">
-        <f t="shared" si="35">IF(O16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O16=TRUE,1,0)</f>
       </c>
       <c r="AJ16" s="206" t="n">
-        <f t="shared" si="35">IF(P16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P16=TRUE,1,0)</f>
       </c>
       <c r="AK16" s="206" t="n">
-        <f t="shared" si="35">IF(Q16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q16=TRUE,1,0)</f>
       </c>
       <c r="AL16" s="206" t="n">
-        <f t="shared" si="35">IF(R16=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R16=TRUE,1,0)</f>
       </c>
       <c r="AM16" t="n">
         <f>IF(LEN(TRIM(W16))&gt;0,1,0)</f>
@@ -32775,43 +32606,43 @@
         <f>IF(ISBLANK('ONR 2'!I10),"",'ONR 2'!I10)</f>
       </c>
       <c r="J17" s="218" t="str">
-        <f t="shared" si="36">IF(ISBLANK('ONR 2'!J10),"",'ONR 2'!J10)</f>
-      </c>
-      <c r="K19" s="227">
-        <f t="shared" si="37"/>
-      </c>
-      <c r="L19" s="227">
-        <f t="shared" si="38"/>
-      </c>
-      <c r="M19" s="227">
-        <f t="shared" si="39"/>
-      </c>
-      <c r="N19" s="227">
-        <f t="shared" si="40"/>
-      </c>
-      <c r="O19" s="227">
-        <f t="shared" si="41"/>
-      </c>
-      <c r="P19" s="227">
-        <f t="shared" si="42"/>
-      </c>
-      <c r="Q19" s="227">
-        <f t="shared" si="43"/>
-      </c>
-      <c r="R19" s="227">
-        <f t="shared" si="44"/>
-      </c>
-      <c r="S19" s="228">
-        <f t="shared" si="45"/>
-      </c>
-      <c r="T19" s="226">
-        <f t="shared" si="46"/>
-      </c>
-      <c r="U19" s="242">
-        <f t="shared" si="47"/>
-      </c>
-      <c r="V19" s="229">
-        <f>G17</f>
+        <f>IF(ISBLANK('ONR 2'!J10),"",'ONR 2'!J10)</f>
+      </c>
+      <c r="K17" s="227" t="str">
+        <f>IF(ISBLANK('ONR 2'!K10),"",'ONR 2'!K10)</f>
+      </c>
+      <c r="L17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!L10),"",'ONR 2'!L10)</f>
+      </c>
+      <c r="M17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!M10),"",'ONR 2'!M10)</f>
+      </c>
+      <c r="N17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!N10),"",'ONR 2'!N10)</f>
+      </c>
+      <c r="O17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!O10),"",'ONR 2'!O10)</f>
+      </c>
+      <c r="P17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!P10),"",'ONR 2'!P10)</f>
+      </c>
+      <c r="Q17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!Q10),"",'ONR 2'!Q10)</f>
+      </c>
+      <c r="R17" s="227" t="b">
+        <f>IF(ISBLANK('ONR 2'!R10),"",'ONR 2'!R10)</f>
+      </c>
+      <c r="S17" s="228" t="str">
+        <f>IF(ISBLANK('ONR 2'!S10),"",'ONR 2'!S10)</f>
+      </c>
+      <c r="T17" s="226" t="str">
+        <f>IF(ISBLANK('ONR 2'!T10),"",'ONR 2'!T10)</f>
+      </c>
+      <c r="U17" s="242" t="str">
+        <f>IF(ISBLANK('ONR 2'!U10),"",'ONR 2'!U10)</f>
+      </c>
+      <c r="V17" s="229" t="str">
+        <f>IF(ISBLANK('ONR 2'!G10),"",'ONR 2'!G10)</f>
       </c>
       <c r="W17" s="229" t="str">
         <f>IF(ISBLANK('ONR 2'!V10),"",'ONR 2'!V10)</f>
@@ -32830,32 +32661,25 @@
         <v>1</v>
       </c>
       <c r="AF17" s="206" t="n">
-        <f t="shared" si="35">IF(L17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L17=TRUE,1,0)</f>
       </c>
       <c r="AG17" s="206" t="n">
-        <f t="shared" si="35">IF(M17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M17=TRUE,1,0)</f>
       </c>
       <c r="AH17" s="206" t="n">
-        <f t="shared" si="35">IF(N17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N17=TRUE,1,0)</f>
       </c>
       <c r="AI17" s="206" t="n">
-        <f t="shared" si="35">IF(O17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O17=TRUE,1,0)</f>
       </c>
       <c r="AJ17" s="206" t="n">
-        <f t="shared" si="35">IF(P17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P17=TRUE,1,0)</f>
       </c>
       <c r="AK17" s="206" t="n">
-        <f t="shared" si="35">IF(Q17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q17=TRUE,1,0)</f>
       </c>
       <c r="AL17" s="206" t="n">
-        <f t="shared" si="35">IF(R17=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R17=TRUE,1,0)</f>
       </c>
       <c r="AM17" t="n">
         <f>IF(LEN(TRIM(W17))&gt;0,1,0)</f>
@@ -33090,50 +32914,43 @@
         <f>IF(ISBLANK('ONR 3'!I7),"",'ONR 3'!I7)</f>
       </c>
       <c r="J20" s="246" t="str">
-        <f t="shared" ref="J20:J25" si="49">IF(ISBLANK('ONR 3'!J7),"",'ONR 3'!J7)</f>
+        <f>IF(ISBLANK('ONR 3'!J7),"",'ONR 3'!J7)</f>
       </c>
       <c r="K20" s="247" t="str">
-        <f t="shared" ref="K20:K25" si="50">IF(ISBLANK('ONR 3'!K7),"",'ONR 3'!K7)</f>
+        <f>IF(ISBLANK('ONR 3'!K7),"",'ONR 3'!K7)</f>
       </c>
       <c r="L20" s="247" t="b">
-        <f t="shared" ref="L20:L25" si="51">IF(ISBLANK('ONR 3'!L7),"",'ONR 3'!L7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!L7),"",'ONR 3'!L7)</f>
       </c>
       <c r="M20" s="247" t="b">
-        <f t="shared" ref="M20:M25" si="52">IF(ISBLANK('ONR 3'!M7),"",'ONR 3'!M7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!M7),"",'ONR 3'!M7)</f>
       </c>
       <c r="N20" s="247" t="b">
-        <f t="shared" ref="N20:N25" si="53">IF(ISBLANK('ONR 3'!N7),"",'ONR 3'!N7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!N7),"",'ONR 3'!N7)</f>
       </c>
       <c r="O20" s="247" t="b">
-        <f t="shared" ref="O20:O25" si="54">IF(ISBLANK('ONR 3'!O7),"",'ONR 3'!O7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!O7),"",'ONR 3'!O7)</f>
       </c>
       <c r="P20" s="247" t="b">
-        <f t="shared" ref="P20:P25" si="55">IF(ISBLANK('ONR 3'!P7),"",'ONR 3'!P7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!P7),"",'ONR 3'!P7)</f>
       </c>
       <c r="Q20" s="247" t="b">
-        <f t="shared" ref="Q20:Q25" si="56">IF(ISBLANK('ONR 3'!Q7),"",'ONR 3'!Q7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!Q7),"",'ONR 3'!Q7)</f>
       </c>
       <c r="R20" s="247" t="b">
-        <f t="shared" ref="R20:R25" si="57">IF(ISBLANK('ONR 3'!R7),"",'ONR 3'!R7)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!R7),"",'ONR 3'!R7)</f>
       </c>
       <c r="S20" s="248" t="str">
-        <f t="shared" ref="S20:S25" si="58">IF(ISBLANK('ONR 3'!S7),"",'ONR 3'!S7)</f>
+        <f>IF(ISBLANK('ONR 3'!S7),"",'ONR 3'!S7)</f>
       </c>
       <c r="T20" s="249" t="str">
-        <f t="shared" ref="T20:T25" si="59">IF(ISBLANK('ONR 3'!T7),"",'ONR 3'!T7)</f>
+        <f>IF(ISBLANK('ONR 3'!T7),"",'ONR 3'!T7)</f>
       </c>
       <c r="U20" s="250" t="str">
-        <f t="shared" ref="U20:U25" si="60">IF(ISBLANK('ONR 3'!U7),"",'ONR 3'!U7)</f>
+        <f>IF(ISBLANK('ONR 3'!U7),"",'ONR 3'!U7)</f>
       </c>
       <c r="V20" s="235" t="str">
-        <f t="shared" ref="V20:V26" si="61">IF(ISBLANK('ONR 3'!G7),"",'ONR 3'!G7)</f>
+        <f>IF(ISBLANK('ONR 3'!G7),"",'ONR 3'!G7)</f>
       </c>
       <c r="W20" s="235" t="str">
         <f>IF(ISBLANK('ONR 3'!V7),"",'ONR 3'!V7)</f>
@@ -33142,42 +32959,34 @@
         <f>IF(ISBLANK('ONR 3'!W7),"",'ONR 3'!W7)</f>
       </c>
       <c r="Y20" s="236" t="str">
-        <f t="shared" ref="Y20:Y26" si="62">IF(ISBLANK('ONR 3'!I7),"",'ONR 3'!I7)</f>
+        <f>IF(ISBLANK('ONR 3'!I7),"",'ONR 3'!I7)</f>
       </c>
       <c r="Z20" s="236" t="str">
-        <f t="shared" ref="Z20:Z26" si="63">IF(ISBLANK('ONR 3'!D7),"",'ONR 3'!D7)</f>
+        <f>IF(ISBLANK('ONR 3'!D7),"",'ONR 3'!D7)</f>
       </c>
       <c r="AE20" s="206" t="n">
-        <f t="shared" ref="AE20:AE26" si="64">IF(ISNUMBER(T20),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T20),0,1)</f>
       </c>
       <c r="AF20" s="206" t="n">
-        <f t="shared" ref="AF20:AL26" si="65">IF(L20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L20=TRUE,1,0)</f>
       </c>
       <c r="AG20" s="206" t="n">
-        <f t="shared" si="65">IF(M20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M20=TRUE,1,0)</f>
       </c>
       <c r="AH20" s="206" t="n">
-        <f t="shared" si="65">IF(N20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N20=TRUE,1,0)</f>
       </c>
       <c r="AI20" s="206" t="n">
-        <f t="shared" si="65">IF(O20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O20=TRUE,1,0)</f>
       </c>
       <c r="AJ20" s="206" t="n">
-        <f t="shared" si="65">IF(P20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P20=TRUE,1,0)</f>
       </c>
       <c r="AK20" s="206" t="n">
-        <f t="shared" si="65">IF(Q20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q20=TRUE,1,0)</f>
       </c>
       <c r="AL20" s="206" t="n">
-        <f t="shared" si="65">IF(R20=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R20=TRUE,1,0)</f>
       </c>
       <c r="AM20" t="n">
         <f>IF(LEN(TRIM(W20))&gt;0,1,0)</f>
@@ -33213,97 +33022,51 @@
         <f>IF(ISBLANK('ONR 3'!I8),"",'ONR 3'!I8)</f>
       </c>
       <c r="J21" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J8),"",'ONR 3'!J8)</f>
-      </c>
-      <c r="K23" s="247" t="str">
-        <f t="shared" si="50">IF(ISBLANK('ONR 3'!K10),"",'ONR 3'!K10)</f>
+        <f>IF(ISBLANK('ONR 3'!J8),"",'ONR 3'!J8)</f>
       </c>
       <c r="K21" t="str" s="247">
         <f>IF(ISBLANK('ONR 3'!K8),"",'ONR 3'!K8)</f>
-      </c>
-      <c r="L23" s="247" t="b">
-        <f t="shared" si="51">IF(ISBLANK('ONR 3'!L10),"",'ONR 3'!L10)</f>
-        <v>0</v>
       </c>
       <c r="L21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!L8),"",'ONR 3'!L8)</f>
         <v>0</v>
       </c>
-      <c r="M23" s="247" t="b">
-        <f t="shared" si="52">IF(ISBLANK('ONR 3'!M10),"",'ONR 3'!M10)</f>
-        <v>0</v>
-      </c>
       <c r="M21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!M8),"",'ONR 3'!M8)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="247" t="b">
-        <f t="shared" si="53">IF(ISBLANK('ONR 3'!N10),"",'ONR 3'!N10)</f>
-        <v>0</v>
-      </c>
       <c r="N21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!N8),"",'ONR 3'!N8)</f>
         <v>0</v>
       </c>
-      <c r="O23" s="247" t="b">
-        <f t="shared" si="54">IF(ISBLANK('ONR 3'!O10),"",'ONR 3'!O10)</f>
-        <v>0</v>
-      </c>
       <c r="O21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!O8),"",'ONR 3'!O8)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="247" t="b">
-        <f t="shared" si="55">IF(ISBLANK('ONR 3'!P10),"",'ONR 3'!P10)</f>
-        <v>0</v>
-      </c>
       <c r="P21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!P8),"",'ONR 3'!P8)</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="247" t="b">
-        <f t="shared" si="56">IF(ISBLANK('ONR 3'!Q10),"",'ONR 3'!Q10)</f>
-        <v>0</v>
-      </c>
       <c r="Q21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!Q8),"",'ONR 3'!Q8)</f>
         <v>0</v>
       </c>
-      <c r="R23" s="247" t="b">
-        <f t="shared" si="57">IF(ISBLANK('ONR 3'!R10),"",'ONR 3'!R10)</f>
-        <v>0</v>
-      </c>
       <c r="R21" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!R8),"",'ONR 3'!R8)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="248" t="str">
-        <f t="shared" si="58">IF(ISBLANK('ONR 3'!S10),"",'ONR 3'!S10)</f>
-      </c>
       <c r="S21" t="str" s="248">
         <f>IF(ISBLANK('ONR 3'!S8),"",'ONR 3'!S8)</f>
       </c>
-      <c r="T23" s="249" t="str">
-        <f t="shared" si="59">IF(ISBLANK('ONR 3'!T10),"",'ONR 3'!T10)</f>
-      </c>
       <c r="T21" t="str" s="249">
         <f>IF(ISBLANK('ONR 3'!T8),"",'ONR 3'!T8)</f>
       </c>
-      <c r="U23" s="250" t="str">
-        <f t="shared" si="60">IF(ISBLANK('ONR 3'!U10),"",'ONR 3'!U10)</f>
-      </c>
       <c r="U21" t="str" s="250">
         <f>IF(ISBLANK('ONR 3'!U8),"",'ONR 3'!U8)</f>
       </c>
-      <c r="V23" s="235" t="str">
-        <f t="shared" si="61">IF(ISBLANK('ONR 3'!G10),"",'ONR 3'!G10)</f>
-      </c>
       <c r="V21" t="str" s="235">
         <f>IF(ISBLANK('ONR 3'!G8),"",'ONR 3'!G8)</f>
       </c>
-      <c r="W23" s="235" t="str">
-        <f>IF(ISBLANK('ONR 3'!V10),"",'ONR 3'!V10)</f>
-      </c>
       <c r="W21" t="str" s="235">
         <f>IF(ISBLANK('ONR 3'!V8),"",'ONR 3'!V8)</f>
       </c>
@@ -33311,42 +33074,34 @@
         <f>IF(ISBLANK('ONR 3'!W8),"",'ONR 3'!W8)</f>
       </c>
       <c r="Y21" s="236" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I8),"",'ONR 3'!I8)</f>
+        <f>IF(ISBLANK('ONR 3'!I8),"",'ONR 3'!I8)</f>
       </c>
       <c r="Z21" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D8),"",'ONR 3'!D8)</f>
+        <f>IF(ISBLANK('ONR 3'!D8),"",'ONR 3'!D8)</f>
       </c>
       <c r="AE21" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T21),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T21),0,1)</f>
       </c>
       <c r="AF21" s="206" t="n">
-        <f t="shared" si="65">IF(L21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L21=TRUE,1,0)</f>
       </c>
       <c r="AG21" s="206" t="n">
-        <f t="shared" si="65">IF(M21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M21=TRUE,1,0)</f>
       </c>
       <c r="AH21" s="206" t="n">
-        <f t="shared" si="65">IF(N21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N21=TRUE,1,0)</f>
       </c>
       <c r="AI21" s="206" t="n">
-        <f t="shared" si="65">IF(O21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O21=TRUE,1,0)</f>
       </c>
       <c r="AJ21" s="206" t="n">
-        <f t="shared" si="65">IF(P21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P21=TRUE,1,0)</f>
       </c>
       <c r="AK21" s="206" t="n">
-        <f t="shared" si="65">IF(Q21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q21=TRUE,1,0)</f>
       </c>
       <c r="AL21" s="206" t="n">
-        <f t="shared" si="65">IF(R21=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R21=TRUE,1,0)</f>
       </c>
       <c r="AM21" t="n">
         <f>IF(LEN(TRIM(W21))&gt;0,1,0)</f>
@@ -33382,97 +33137,51 @@
         <f>IF(ISBLANK('ONR 3'!I9),"",'ONR 3'!I9)</f>
       </c>
       <c r="J22" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J9),"",'ONR 3'!J9)</f>
-      </c>
-      <c r="K24" s="247" t="str">
-        <f t="shared" si="50">IF(ISBLANK('ONR 3'!K11),"",'ONR 3'!K11)</f>
+        <f>IF(ISBLANK('ONR 3'!J9),"",'ONR 3'!J9)</f>
       </c>
       <c r="K22" t="str" s="247">
         <f>IF(ISBLANK('ONR 3'!K9),"",'ONR 3'!K9)</f>
-      </c>
-      <c r="L24" s="247" t="b">
-        <f t="shared" si="51">IF(ISBLANK('ONR 3'!L11),"",'ONR 3'!L11)</f>
-        <v>0</v>
       </c>
       <c r="L22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!L9),"",'ONR 3'!L9)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="247" t="b">
-        <f t="shared" si="52">IF(ISBLANK('ONR 3'!M11),"",'ONR 3'!M11)</f>
-        <v>0</v>
-      </c>
       <c r="M22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!M9),"",'ONR 3'!M9)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="247" t="b">
-        <f t="shared" si="53">IF(ISBLANK('ONR 3'!N11),"",'ONR 3'!N11)</f>
-        <v>0</v>
-      </c>
       <c r="N22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!N9),"",'ONR 3'!N9)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="247" t="b">
-        <f t="shared" si="54">IF(ISBLANK('ONR 3'!O11),"",'ONR 3'!O11)</f>
-        <v>0</v>
-      </c>
       <c r="O22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!O9),"",'ONR 3'!O9)</f>
         <v>0</v>
       </c>
-      <c r="P24" s="247" t="b">
-        <f t="shared" si="55">IF(ISBLANK('ONR 3'!P11),"",'ONR 3'!P11)</f>
-        <v>0</v>
-      </c>
       <c r="P22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!P9),"",'ONR 3'!P9)</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="247" t="b">
-        <f t="shared" si="56">IF(ISBLANK('ONR 3'!Q11),"",'ONR 3'!Q11)</f>
-        <v>0</v>
-      </c>
       <c r="Q22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!Q9),"",'ONR 3'!Q9)</f>
         <v>0</v>
       </c>
-      <c r="R24" s="247" t="b">
-        <f t="shared" si="57">IF(ISBLANK('ONR 3'!R11),"",'ONR 3'!R11)</f>
-        <v>0</v>
-      </c>
       <c r="R22" t="b" s="247">
         <f>IF(ISBLANK('ONR 3'!R9),"",'ONR 3'!R9)</f>
         <v>0</v>
       </c>
-      <c r="S24" s="248" t="str">
-        <f t="shared" si="58">IF(ISBLANK('ONR 3'!S11),"",'ONR 3'!S11)</f>
-      </c>
       <c r="S22" t="str" s="248">
         <f>IF(ISBLANK('ONR 3'!S9),"",'ONR 3'!S9)</f>
       </c>
-      <c r="T24" s="249" t="str">
-        <f t="shared" si="59">IF(ISBLANK('ONR 3'!T11),"",'ONR 3'!T11)</f>
-      </c>
       <c r="T22" t="str" s="249">
         <f>IF(ISBLANK('ONR 3'!T9),"",'ONR 3'!T9)</f>
       </c>
-      <c r="U24" s="250" t="str">
-        <f t="shared" si="60">IF(ISBLANK('ONR 3'!U11),"",'ONR 3'!U11)</f>
-      </c>
       <c r="U22" t="str" s="250">
         <f>IF(ISBLANK('ONR 3'!U9),"",'ONR 3'!U9)</f>
       </c>
-      <c r="V24" s="235" t="str">
-        <f t="shared" si="61">IF(ISBLANK('ONR 3'!G11),"",'ONR 3'!G11)</f>
-      </c>
       <c r="V22" t="str" s="235">
         <f>IF(ISBLANK('ONR 3'!G9),"",'ONR 3'!G9)</f>
       </c>
-      <c r="W24" s="235" t="str">
-        <f>IF(ISBLANK('ONR 3'!V11),"",'ONR 3'!V11)</f>
-      </c>
       <c r="W22" t="str" s="235">
         <f>IF(ISBLANK('ONR 3'!V9),"",'ONR 3'!V9)</f>
       </c>
@@ -33480,42 +33189,34 @@
         <f>IF(ISBLANK('ONR 3'!W9),"",'ONR 3'!W9)</f>
       </c>
       <c r="Y22" s="236" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I9),"",'ONR 3'!I9)</f>
+        <f>IF(ISBLANK('ONR 3'!I9),"",'ONR 3'!I9)</f>
       </c>
       <c r="Z22" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D9),"",'ONR 3'!D9)</f>
+        <f>IF(ISBLANK('ONR 3'!D9),"",'ONR 3'!D9)</f>
       </c>
       <c r="AE22" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T22),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T22),0,1)</f>
       </c>
       <c r="AF22" s="206" t="n">
-        <f t="shared" si="65">IF(L22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L22=TRUE,1,0)</f>
       </c>
       <c r="AG22" s="206" t="n">
-        <f t="shared" si="65">IF(M22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M22=TRUE,1,0)</f>
       </c>
       <c r="AH22" s="206" t="n">
-        <f t="shared" si="65">IF(N22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N22=TRUE,1,0)</f>
       </c>
       <c r="AI22" s="206" t="n">
-        <f t="shared" si="65">IF(O22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O22=TRUE,1,0)</f>
       </c>
       <c r="AJ22" s="206" t="n">
-        <f t="shared" si="65">IF(P22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P22=TRUE,1,0)</f>
       </c>
       <c r="AK22" s="206" t="n">
-        <f t="shared" si="65">IF(Q22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q22=TRUE,1,0)</f>
       </c>
       <c r="AL22" s="206" t="n">
-        <f t="shared" si="65">IF(R22=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R22=TRUE,1,0)</f>
       </c>
       <c r="AM22" t="n">
         <f>IF(LEN(TRIM(W22))&gt;0,1,0)</f>
@@ -33551,94 +33252,79 @@
         <f>IF(ISBLANK('ONR 3'!I10),"",'ONR 3'!I10)</f>
       </c>
       <c r="J23" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J10),"",'ONR 3'!J10)</f>
-      </c>
-      <c r="K25" s="247" t="str">
-        <f t="shared" si="50">IF(ISBLANK('ONR 3'!K12),"",'ONR 3'!K12)</f>
-      </c>
-      <c r="L25" s="247" t="b">
-        <f t="shared" si="51">IF(ISBLANK('ONR 3'!L12),"",'ONR 3'!L12)</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="247" t="b">
-        <f t="shared" si="52">IF(ISBLANK('ONR 3'!M12),"",'ONR 3'!M12)</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="247" t="b">
-        <f t="shared" si="53">IF(ISBLANK('ONR 3'!N12),"",'ONR 3'!N12)</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="247" t="b">
-        <f t="shared" si="54">IF(ISBLANK('ONR 3'!O12),"",'ONR 3'!O12)</f>
-        <v>0</v>
-      </c>
-      <c r="P25" s="247" t="b">
-        <f t="shared" si="55">IF(ISBLANK('ONR 3'!P12),"",'ONR 3'!P12)</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="247" t="b">
-        <f t="shared" si="56">IF(ISBLANK('ONR 3'!Q12),"",'ONR 3'!Q12)</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="247" t="b">
-        <f t="shared" si="57">IF(ISBLANK('ONR 3'!R12),"",'ONR 3'!R12)</f>
-        <v>0</v>
-      </c>
-      <c r="S25" s="248" t="str">
-        <f t="shared" si="58">IF(ISBLANK('ONR 3'!S12),"",'ONR 3'!S12)</f>
-      </c>
-      <c r="T25" s="249" t="str">
-        <f t="shared" si="59">IF(ISBLANK('ONR 3'!T12),"",'ONR 3'!T12)</f>
-      </c>
-      <c r="U25" s="250" t="str">
-        <f t="shared" si="60">IF(ISBLANK('ONR 3'!U12),"",'ONR 3'!U12)</f>
-      </c>
-      <c r="V25" s="252" t="str">
-        <f t="shared" si="61">IF(ISBLANK('ONR 3'!G12),"",'ONR 3'!G12)</f>
-      </c>
-      <c r="W25" s="252" t="str">
-        <f>IF(ISBLANK('ONR 3'!V12),"",'ONR 3'!V12)</f>
+        <f>IF(ISBLANK('ONR 3'!J10),"",'ONR 3'!J10)</f>
+      </c>
+      <c r="K23" s="247" t="str">
+        <f>IF(ISBLANK('ONR 3'!K10),"",'ONR 3'!K10)</f>
+      </c>
+      <c r="L23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!L10),"",'ONR 3'!L10)</f>
+      </c>
+      <c r="M23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!M10),"",'ONR 3'!M10)</f>
+      </c>
+      <c r="N23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!N10),"",'ONR 3'!N10)</f>
+      </c>
+      <c r="O23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!O10),"",'ONR 3'!O10)</f>
+      </c>
+      <c r="P23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!P10),"",'ONR 3'!P10)</f>
+      </c>
+      <c r="Q23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!Q10),"",'ONR 3'!Q10)</f>
+      </c>
+      <c r="R23" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!R10),"",'ONR 3'!R10)</f>
+      </c>
+      <c r="S23" s="248" t="str">
+        <f>IF(ISBLANK('ONR 3'!S10),"",'ONR 3'!S10)</f>
+      </c>
+      <c r="T23" s="249" t="str">
+        <f>IF(ISBLANK('ONR 3'!T10),"",'ONR 3'!T10)</f>
+      </c>
+      <c r="U23" s="250" t="str">
+        <f>IF(ISBLANK('ONR 3'!U10),"",'ONR 3'!U10)</f>
+      </c>
+      <c r="V23" s="235" t="str">
+        <f>IF(ISBLANK('ONR 3'!G10),"",'ONR 3'!G10)</f>
+      </c>
+      <c r="W23" s="235" t="str">
+        <f>IF(ISBLANK('ONR 3'!V10),"",'ONR 3'!V10)</f>
       </c>
       <c r="X23" s="183" t="str">
         <f>IF(ISBLANK('ONR 3'!W10),"",'ONR 3'!W10)</f>
       </c>
       <c r="Y23" s="253" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I10),"",'ONR 3'!I10)</f>
+        <f>IF(ISBLANK('ONR 3'!I10),"",'ONR 3'!I10)</f>
       </c>
       <c r="Z23" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D10),"",'ONR 3'!D10)</f>
+        <f>IF(ISBLANK('ONR 3'!D10),"",'ONR 3'!D10)</f>
       </c>
       <c r="AE23" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T23),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T23),0,1)</f>
       </c>
       <c r="AF23" s="206" t="n">
-        <f t="shared" si="65">IF(L23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L23=TRUE,1,0)</f>
       </c>
       <c r="AG23" s="206" t="n">
-        <f t="shared" si="65">IF(M23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M23=TRUE,1,0)</f>
       </c>
       <c r="AH23" s="206" t="n">
-        <f t="shared" si="65">IF(N23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N23=TRUE,1,0)</f>
       </c>
       <c r="AI23" s="206" t="n">
-        <f t="shared" si="65">IF(O23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O23=TRUE,1,0)</f>
       </c>
       <c r="AJ23" s="206" t="n">
-        <f t="shared" si="65">IF(P23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P23=TRUE,1,0)</f>
       </c>
       <c r="AK23" s="206" t="n">
-        <f t="shared" si="65">IF(Q23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q23=TRUE,1,0)</f>
       </c>
       <c r="AL23" s="206" t="n">
-        <f t="shared" si="65">IF(R23=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R23=TRUE,1,0)</f>
       </c>
       <c r="AM23" t="n">
         <f>IF(LEN(TRIM(W23))&gt;0,1,0)</f>
@@ -33674,94 +33360,79 @@
         <f>IF(ISBLANK('ONR 3'!I11),"",'ONR 3'!I11)</f>
       </c>
       <c r="J24" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J11),"",'ONR 3'!J11)</f>
-      </c>
-      <c r="K26" s="247" t="str">
-        <f t="shared" si="50"/>
-      </c>
-      <c r="L26" s="247" t="b">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="247" t="b">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="247" t="b">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="247" t="b">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="247" t="b">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="247" t="b">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="247" t="b">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="248" t="str">
-        <f t="shared" si="58"/>
-      </c>
-      <c r="T26" s="249" t="str">
-        <f t="shared" si="59"/>
-      </c>
-      <c r="U26" s="250" t="str">
-        <f t="shared" si="60"/>
-      </c>
-      <c r="V26" s="252" t="str">
-        <f t="shared" si="61"/>
-      </c>
-      <c r="W26" s="145" t="str">
-        <f>IF(ISBLANK('ONR 3'!V13),"",'ONR 3'!V13)</f>
+        <f>IF(ISBLANK('ONR 3'!J11),"",'ONR 3'!J11)</f>
+      </c>
+      <c r="K24" s="247" t="str">
+        <f>IF(ISBLANK('ONR 3'!K11),"",'ONR 3'!K11)</f>
+      </c>
+      <c r="L24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!L11),"",'ONR 3'!L11)</f>
+      </c>
+      <c r="M24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!M11),"",'ONR 3'!M11)</f>
+      </c>
+      <c r="N24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!N11),"",'ONR 3'!N11)</f>
+      </c>
+      <c r="O24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!O11),"",'ONR 3'!O11)</f>
+      </c>
+      <c r="P24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!P11),"",'ONR 3'!P11)</f>
+      </c>
+      <c r="Q24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!Q11),"",'ONR 3'!Q11)</f>
+      </c>
+      <c r="R24" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!R11),"",'ONR 3'!R11)</f>
+      </c>
+      <c r="S24" s="248" t="str">
+        <f>IF(ISBLANK('ONR 3'!S11),"",'ONR 3'!S11)</f>
+      </c>
+      <c r="T24" s="249" t="str">
+        <f>IF(ISBLANK('ONR 3'!T11),"",'ONR 3'!T11)</f>
+      </c>
+      <c r="U24" s="250" t="str">
+        <f>IF(ISBLANK('ONR 3'!U11),"",'ONR 3'!U11)</f>
+      </c>
+      <c r="V24" s="235" t="str">
+        <f>IF(ISBLANK('ONR 3'!G11),"",'ONR 3'!G11)</f>
+      </c>
+      <c r="W24" s="235" t="str">
+        <f>IF(ISBLANK('ONR 3'!V11),"",'ONR 3'!V11)</f>
       </c>
       <c r="X24" s="183" t="str">
         <f>IF(ISBLANK('ONR 3'!W11),"",'ONR 3'!W11)</f>
       </c>
       <c r="Y24" s="253" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I11),"",'ONR 3'!I11)</f>
+        <f>IF(ISBLANK('ONR 3'!I11),"",'ONR 3'!I11)</f>
       </c>
       <c r="Z24" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D11),"",'ONR 3'!D11)</f>
+        <f>IF(ISBLANK('ONR 3'!D11),"",'ONR 3'!D11)</f>
       </c>
       <c r="AE24" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T24),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T24),0,1)</f>
       </c>
       <c r="AF24" s="206" t="n">
-        <f t="shared" si="65">IF(L24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L24=TRUE,1,0)</f>
       </c>
       <c r="AG24" s="206" t="n">
-        <f t="shared" si="65">IF(M24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M24=TRUE,1,0)</f>
       </c>
       <c r="AH24" s="206" t="n">
-        <f t="shared" si="65">IF(N24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N24=TRUE,1,0)</f>
       </c>
       <c r="AI24" s="206" t="n">
-        <f t="shared" si="65">IF(O24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O24=TRUE,1,0)</f>
       </c>
       <c r="AJ24" s="206" t="n">
-        <f t="shared" si="65">IF(P24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P24=TRUE,1,0)</f>
       </c>
       <c r="AK24" s="206" t="n">
-        <f t="shared" si="65">IF(Q24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q24=TRUE,1,0)</f>
       </c>
       <c r="AL24" s="206" t="n">
-        <f t="shared" si="65">IF(R24=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R24=TRUE,1,0)</f>
       </c>
       <c r="AM24" t="n">
         <f>IF(LEN(TRIM(W24))&gt;0,1,0)</f>
@@ -33797,87 +33468,79 @@
         <f>IF(ISBLANK('ONR 3'!I12),"",'ONR 3'!I12)</f>
       </c>
       <c r="J25" s="246" t="str">
-        <f t="shared" si="49">IF(ISBLANK('ONR 3'!J12),"",'ONR 3'!J12)</f>
-      </c>
-      <c r="K28" s="247">
-        <f t="shared" si="50"/>
-      </c>
-      <c r="L28" s="247">
-        <f t="shared" si="51"/>
-      </c>
-      <c r="M28" s="247">
-        <f t="shared" si="52"/>
-      </c>
-      <c r="N28" s="247">
-        <f t="shared" si="53"/>
-      </c>
-      <c r="O28" s="247">
-        <f t="shared" si="54"/>
-      </c>
-      <c r="P28" s="247">
-        <f t="shared" si="55"/>
-      </c>
-      <c r="Q28" s="247">
-        <f t="shared" si="56"/>
-      </c>
-      <c r="R28" s="247">
-        <f t="shared" si="57"/>
-      </c>
-      <c r="S28" s="248">
-        <f t="shared" si="58"/>
-      </c>
-      <c r="T28" s="249">
-        <f t="shared" si="59"/>
-      </c>
-      <c r="U28" s="250">
-        <f t="shared" si="60"/>
-      </c>
-      <c r="V28" s="241">
-        <f t="shared" si="61"/>
-      </c>
-      <c r="W28" s="148">
-        <f>'ONR 3'!V12</f>
+        <f>IF(ISBLANK('ONR 3'!J12),"",'ONR 3'!J12)</f>
+      </c>
+      <c r="K25" s="247" t="str">
+        <f>IF(ISBLANK('ONR 3'!K12),"",'ONR 3'!K12)</f>
+      </c>
+      <c r="L25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!L12),"",'ONR 3'!L12)</f>
+      </c>
+      <c r="M25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!M12),"",'ONR 3'!M12)</f>
+      </c>
+      <c r="N25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!N12),"",'ONR 3'!N12)</f>
+      </c>
+      <c r="O25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!O12),"",'ONR 3'!O12)</f>
+      </c>
+      <c r="P25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!P12),"",'ONR 3'!P12)</f>
+      </c>
+      <c r="Q25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!Q12),"",'ONR 3'!Q12)</f>
+      </c>
+      <c r="R25" s="247" t="b">
+        <f>IF(ISBLANK('ONR 3'!R12),"",'ONR 3'!R12)</f>
+      </c>
+      <c r="S25" s="248" t="str">
+        <f>IF(ISBLANK('ONR 3'!S12),"",'ONR 3'!S12)</f>
+      </c>
+      <c r="T25" s="249" t="str">
+        <f>IF(ISBLANK('ONR 3'!T12),"",'ONR 3'!T12)</f>
+      </c>
+      <c r="U25" s="250" t="str">
+        <f>IF(ISBLANK('ONR 3'!U12),"",'ONR 3'!U12)</f>
+      </c>
+      <c r="V25" s="252" t="str">
+        <f>IF(ISBLANK('ONR 3'!G12),"",'ONR 3'!G12)</f>
+      </c>
+      <c r="W25" s="252" t="str">
+        <f>IF(ISBLANK('ONR 3'!V12),"",'ONR 3'!V12)</f>
       </c>
       <c r="X25" s="183" t="str">
         <f>IF(ISBLANK('ONR 3'!W12),"",'ONR 3'!W12)</f>
       </c>
       <c r="Y25" s="254" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I12),"",'ONR 3'!I12)</f>
+        <f>IF(ISBLANK('ONR 3'!I12),"",'ONR 3'!I12)</f>
       </c>
       <c r="Z25" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D12),"",'ONR 3'!D12)</f>
+        <f>IF(ISBLANK('ONR 3'!D12),"",'ONR 3'!D12)</f>
       </c>
       <c r="AE25" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T25),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T25),0,1)</f>
       </c>
       <c r="AF25" s="206" t="n">
-        <f t="shared" si="65">IF(L25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L25=TRUE,1,0)</f>
       </c>
       <c r="AG25" s="206" t="n">
-        <f t="shared" si="65">IF(M25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M25=TRUE,1,0)</f>
       </c>
       <c r="AH25" s="206" t="n">
-        <f t="shared" si="65">IF(N25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N25=TRUE,1,0)</f>
       </c>
       <c r="AI25" s="206" t="n">
-        <f t="shared" si="65">IF(O25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O25=TRUE,1,0)</f>
       </c>
       <c r="AJ25" s="206" t="n">
-        <f t="shared" si="65">IF(P25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P25=TRUE,1,0)</f>
       </c>
       <c r="AK25" s="206" t="n">
-        <f t="shared" si="65">IF(Q25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q25=TRUE,1,0)</f>
       </c>
       <c r="AL25" s="206" t="n">
-        <f t="shared" si="65">IF(R25=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R25=TRUE,1,0)</f>
       </c>
       <c r="AM25" t="n">
         <f>IF(LEN(TRIM(W25))&gt;0,1,0)</f>
@@ -33913,94 +33576,79 @@
         <f>IF(ISBLANK('ONR 3'!I13),"",'ONR 3'!I13)</f>
       </c>
       <c r="J26" s="246" t="str">
-        <f t="shared" ref="J26" si="66">IF(ISBLANK('ONR 3'!J13),"",'ONR 3'!J13)</f>
+        <f>IF(ISBLANK('ONR 3'!J13),"",'ONR 3'!J13)</f>
       </c>
       <c r="K26" s="247" t="str">
-        <f t="shared" ref="K26" si="67">IF(ISBLANK('ONR 3'!K13),"",'ONR 3'!K13)</f>
+        <f>IF(ISBLANK('ONR 3'!K13),"",'ONR 3'!K13)</f>
       </c>
       <c r="L26" s="247" t="b">
-        <f t="shared" ref="L26" si="68">IF(ISBLANK('ONR 3'!L13),"",'ONR 3'!L13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!L13),"",'ONR 3'!L13)</f>
       </c>
       <c r="M26" s="247" t="b">
-        <f t="shared" ref="M26" si="69">IF(ISBLANK('ONR 3'!M13),"",'ONR 3'!M13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!M13),"",'ONR 3'!M13)</f>
       </c>
       <c r="N26" s="247" t="b">
-        <f t="shared" ref="N26" si="70">IF(ISBLANK('ONR 3'!N13),"",'ONR 3'!N13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!N13),"",'ONR 3'!N13)</f>
       </c>
       <c r="O26" s="247" t="b">
-        <f t="shared" ref="O26" si="71">IF(ISBLANK('ONR 3'!O13),"",'ONR 3'!O13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!O13),"",'ONR 3'!O13)</f>
       </c>
       <c r="P26" s="247" t="b">
-        <f t="shared" ref="P26" si="72">IF(ISBLANK('ONR 3'!P13),"",'ONR 3'!P13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!P13),"",'ONR 3'!P13)</f>
       </c>
       <c r="Q26" s="247" t="b">
-        <f t="shared" ref="Q26" si="73">IF(ISBLANK('ONR 3'!Q13),"",'ONR 3'!Q13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!Q13),"",'ONR 3'!Q13)</f>
       </c>
       <c r="R26" s="247" t="b">
-        <f t="shared" ref="R26" si="74">IF(ISBLANK('ONR 3'!R13),"",'ONR 3'!R13)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 3'!R13),"",'ONR 3'!R13)</f>
       </c>
       <c r="S26" s="248" t="str">
-        <f t="shared" ref="S26" si="75">IF(ISBLANK('ONR 3'!S13),"",'ONR 3'!S13)</f>
+        <f>IF(ISBLANK('ONR 3'!S13),"",'ONR 3'!S13)</f>
       </c>
       <c r="T26" s="249" t="str">
-        <f t="shared" ref="T26" si="76">IF(ISBLANK('ONR 3'!T13),"",'ONR 3'!T13)</f>
+        <f>IF(ISBLANK('ONR 3'!T13),"",'ONR 3'!T13)</f>
       </c>
       <c r="U26" s="250" t="str">
-        <f t="shared" ref="U26" si="77">IF(ISBLANK('ONR 3'!U13),"",'ONR 3'!U13)</f>
+        <f>IF(ISBLANK('ONR 3'!U13),"",'ONR 3'!U13)</f>
       </c>
       <c r="V26" s="255" t="str">
-        <f t="shared" si="61">IF(ISBLANK('ONR 3'!G13),"",'ONR 3'!G13)</f>
-      </c>
-      <c r="W29" s="215" t="str">
-        <f>'ONR 3'!V13</f>
+        <f>IF(ISBLANK('ONR 3'!G13),"",'ONR 3'!G13)</f>
+      </c>
+      <c r="W26" s="145" t="str">
+        <f>IF(ISBLANK('ONR 3'!V13),"",'ONR 3'!V13)</f>
       </c>
       <c r="X26" s="183" t="str">
         <f>IF(ISBLANK('ONR 3'!W13),"",'ONR 3'!W13)</f>
       </c>
       <c r="Y26" s="251" t="str">
-        <f t="shared" si="62">IF(ISBLANK('ONR 3'!I13),"",'ONR 3'!I13)</f>
+        <f>IF(ISBLANK('ONR 3'!I13),"",'ONR 3'!I13)</f>
       </c>
       <c r="Z26" s="251" t="str">
-        <f t="shared" si="63">IF(ISBLANK('ONR 3'!D13),"",'ONR 3'!D13)</f>
+        <f>IF(ISBLANK('ONR 3'!D13),"",'ONR 3'!D13)</f>
       </c>
       <c r="AE26" s="206" t="n">
-        <f t="shared" si="64">IF(ISNUMBER(T26),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T26),0,1)</f>
       </c>
       <c r="AF26" s="206" t="n">
-        <f t="shared" si="65">IF(L26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L26=TRUE,1,0)</f>
       </c>
       <c r="AG26" s="206" t="n">
-        <f t="shared" si="65">IF(M26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M26=TRUE,1,0)</f>
       </c>
       <c r="AH26" s="206" t="n">
-        <f t="shared" si="65">IF(N26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N26=TRUE,1,0)</f>
       </c>
       <c r="AI26" s="206" t="n">
-        <f t="shared" si="65">IF(O26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O26=TRUE,1,0)</f>
       </c>
       <c r="AJ26" s="206" t="n">
-        <f t="shared" si="65">IF(P26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P26=TRUE,1,0)</f>
       </c>
       <c r="AK26" s="206" t="n">
-        <f t="shared" si="65">IF(Q26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q26=TRUE,1,0)</f>
       </c>
       <c r="AL26" s="206" t="n">
-        <f t="shared" si="65">IF(R26=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R26=TRUE,1,0)</f>
       </c>
       <c r="AM26" t="n">
         <f>IF(LEN(TRIM(W26))&gt;0,1,0)</f>
@@ -34238,7 +33886,7 @@
         <f>IF(ISBLANK('ONR 4'!J7),"",'ONR 4'!J7)</f>
       </c>
       <c r="K29" s="227" t="str">
-        <f t="shared" ref="K29:K30" si="79">IF(ISBLANK('ONR 4'!K7),"",'ONR 4'!K7)</f>
+        <f>IF(ISBLANK('ONR 4'!K7),"",'ONR 4'!K7)</f>
       </c>
       <c r="L29" s="227" t="b">
         <f>IF(ISBLANK('ONR 4'!L7),"",'ONR 4'!L7)</f>
@@ -34269,13 +33917,13 @@
         <v>0</v>
       </c>
       <c r="S29" s="228" t="str">
-        <f t="shared" ref="S29:S30" si="80">IF(ISBLANK('ONR 4'!S7),"",'ONR 4'!S7)</f>
+        <f>IF(ISBLANK('ONR 4'!S7),"",'ONR 4'!S7)</f>
       </c>
       <c r="T29" s="226" t="str">
-        <f t="shared" ref="T29" si="81">IF(ISBLANK('ONR 4'!T7),"",'ONR 4'!T7)</f>
+        <f>IF(ISBLANK('ONR 4'!T7),"",'ONR 4'!T7)</f>
       </c>
       <c r="U29" s="242" t="str">
-        <f t="shared" ref="U29" si="82">IF(ISBLANK('ONR 4'!U7),"",'ONR 4'!U7)</f>
+        <f>IF(ISBLANK('ONR 4'!U7),"",'ONR 4'!U7)</f>
       </c>
       <c r="V29" s="229" t="str">
         <f>IF(ISBLANK('ONR 4'!G7),"",'ONR 4'!G7)</f>
@@ -34297,32 +33945,25 @@
         <v>1</v>
       </c>
       <c r="AF29" s="206" t="n">
-        <f t="shared" ref="AF29:AL32" si="83">IF(L29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L29=TRUE,1,0)</f>
       </c>
       <c r="AG29" s="206" t="n">
-        <f t="shared" si="83">IF(M29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M29=TRUE,1,0)</f>
       </c>
       <c r="AH29" s="206" t="n">
-        <f t="shared" si="83">IF(N29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N29=TRUE,1,0)</f>
       </c>
       <c r="AI29" s="206" t="n">
-        <f t="shared" si="83">IF(O29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O29=TRUE,1,0)</f>
       </c>
       <c r="AJ29" s="206" t="n">
-        <f t="shared" si="83">IF(P29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P29=TRUE,1,0)</f>
       </c>
       <c r="AK29" s="206" t="n">
-        <f t="shared" si="83">IF(Q29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q29=TRUE,1,0)</f>
       </c>
       <c r="AL29" s="206" t="n">
-        <f t="shared" si="83">IF(R29=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R29=TRUE,1,0)</f>
       </c>
       <c r="AM29" t="n">
         <f>IF(LEN(TRIM(W29))&gt;0,1,0)</f>
@@ -34358,59 +33999,41 @@
         <f>IF(ISBLANK('ONR 4'!I8),"",'ONR 4'!I8)</f>
       </c>
       <c r="J30" s="219" t="str">
-        <f t="shared" ref="J30:J38" si="84">IF(ISBLANK('ONR 4'!J8),"",'ONR 4'!J8)</f>
+        <f>IF(ISBLANK('ONR 4'!J8),"",'ONR 4'!J8)</f>
       </c>
       <c r="K30" s="233" t="str">
-        <f t="shared" si="79">IF(ISBLANK('ONR 4'!K8),"",'ONR 4'!K8)</f>
-      </c>
-      <c r="L33" s="233">
-        <f t="shared" ref="L33" si="85">OR(K30=31)</f>
+        <f>IF(ISBLANK('ONR 4'!K8),"",'ONR 4'!K8)</f>
       </c>
       <c r="L30" t="b" s="227">
         <f>IF(ISBLANK('ONR 4'!L8),"",'ONR 4'!L8)</f>
         <v>0</v>
       </c>
       <c r="M30" s="233" t="b">
-        <f t="shared" ref="M30" si="86">IF(ISBLANK('ONR 4'!M8),"",'ONR 4'!M8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!M8),"",'ONR 4'!M8)</f>
       </c>
       <c r="N30" s="233" t="b">
-        <f t="shared" ref="N30" si="87">IF(ISBLANK('ONR 4'!N8),"",'ONR 4'!N8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!N8),"",'ONR 4'!N8)</f>
       </c>
       <c r="O30" s="233" t="b">
-        <f t="shared" ref="O30" si="88">IF(ISBLANK('ONR 4'!O8),"",'ONR 4'!O8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!O8),"",'ONR 4'!O8)</f>
       </c>
       <c r="P30" s="233" t="b">
-        <f t="shared" ref="P30" si="89">IF(ISBLANK('ONR 4'!P8),"",'ONR 4'!P8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!P8),"",'ONR 4'!P8)</f>
       </c>
       <c r="Q30" s="233" t="b">
-        <f t="shared" ref="Q30" si="90">IF(ISBLANK('ONR 4'!Q8),"",'ONR 4'!Q8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!Q8),"",'ONR 4'!Q8)</f>
       </c>
       <c r="R30" s="233" t="b">
-        <f t="shared" ref="R30" si="91">IF(ISBLANK('ONR 4'!R8),"",'ONR 4'!R8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!R8),"",'ONR 4'!R8)</f>
       </c>
       <c r="S30" s="234" t="str">
-        <f t="shared" si="80">IF(ISBLANK('ONR 4'!S8),"",'ONR 4'!S8)</f>
-      </c>
-      <c r="T33" s="232">
-        <f t="shared" si="81"/>
+        <f>IF(ISBLANK('ONR 4'!S8),"",'ONR 4'!S8)</f>
       </c>
       <c r="T30" t="str" s="226">
         <f>IF(ISBLANK('ONR 4'!T8),"",'ONR 4'!T8)</f>
       </c>
-      <c r="U33" s="243">
-        <f t="shared" si="82"/>
-      </c>
       <c r="U30" t="str" s="242">
         <f>IF(ISBLANK('ONR 4'!U8),"",'ONR 4'!U8)</f>
-      </c>
-      <c r="V33" s="235">
-        <f>G30</f>
       </c>
       <c r="V30" t="str" s="229">
         <f>IF(ISBLANK('ONR 4'!G8),"",'ONR 4'!G8)</f>
@@ -34432,32 +34055,25 @@
         <v>1</v>
       </c>
       <c r="AF30" s="206" t="n">
-        <f t="shared" si="83">IF(L30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L30=TRUE,1,0)</f>
       </c>
       <c r="AG30" s="206" t="n">
-        <f t="shared" si="83">IF(M30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M30=TRUE,1,0)</f>
       </c>
       <c r="AH30" s="206" t="n">
-        <f t="shared" si="83">IF(N30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N30=TRUE,1,0)</f>
       </c>
       <c r="AI30" s="206" t="n">
-        <f t="shared" si="83">IF(O30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O30=TRUE,1,0)</f>
       </c>
       <c r="AJ30" s="206" t="n">
-        <f t="shared" si="83">IF(P30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P30=TRUE,1,0)</f>
       </c>
       <c r="AK30" s="206" t="n">
-        <f t="shared" si="83">IF(Q30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q30=TRUE,1,0)</f>
       </c>
       <c r="AL30" s="206" t="n">
-        <f t="shared" si="83">IF(R30=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R30=TRUE,1,0)</f>
       </c>
       <c r="AM30" t="n">
         <f>IF(LEN(TRIM(W30))&gt;0,1,0)</f>
@@ -34493,47 +34109,40 @@
         <f>IF(ISBLANK('ONR 4'!I9),"",'ONR 4'!I9)</f>
       </c>
       <c r="J31" s="219" t="str">
-        <f t="shared" ref="J31:J32" si="92">IF(ISBLANK('ONR 4'!J9),"",'ONR 4'!J9)</f>
+        <f>IF(ISBLANK('ONR 4'!J9),"",'ONR 4'!J9)</f>
       </c>
       <c r="K31" s="233" t="str">
-        <f t="shared" ref="K31:K35" si="93">IF(ISBLANK('ONR 4'!K9),"",'ONR 4'!K9)</f>
+        <f>IF(ISBLANK('ONR 4'!K9),"",'ONR 4'!K9)</f>
       </c>
       <c r="L31" s="233" t="b">
-        <f t="shared" ref="L31:L35" si="94">IF(ISBLANK('ONR 4'!L9),"",'ONR 4'!L9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!L9),"",'ONR 4'!L9)</f>
       </c>
       <c r="M31" s="233" t="b">
-        <f t="shared" ref="M31" si="95">IF(ISBLANK('ONR 4'!M9),"",'ONR 4'!M9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!M9),"",'ONR 4'!M9)</f>
       </c>
       <c r="N31" s="233" t="b">
-        <f t="shared" ref="N31" si="96">IF(ISBLANK('ONR 4'!N9),"",'ONR 4'!N9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!N9),"",'ONR 4'!N9)</f>
       </c>
       <c r="O31" s="233" t="b">
-        <f t="shared" ref="O31" si="97">IF(ISBLANK('ONR 4'!O9),"",'ONR 4'!O9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!O9),"",'ONR 4'!O9)</f>
       </c>
       <c r="P31" s="233" t="b">
-        <f t="shared" ref="P31" si="98">IF(ISBLANK('ONR 4'!P9),"",'ONR 4'!P9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!P9),"",'ONR 4'!P9)</f>
       </c>
       <c r="Q31" s="233" t="b">
-        <f t="shared" ref="Q31" si="99">IF(ISBLANK('ONR 4'!Q9),"",'ONR 4'!Q9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!Q9),"",'ONR 4'!Q9)</f>
       </c>
       <c r="R31" s="233" t="b">
-        <f t="shared" ref="R31" si="100">IF(ISBLANK('ONR 4'!R9),"",'ONR 4'!R9)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 4'!R9),"",'ONR 4'!R9)</f>
       </c>
       <c r="S31" s="234" t="str">
-        <f t="shared" ref="S31" si="101">IF(ISBLANK('ONR 4'!S9),"",'ONR 4'!S9)</f>
+        <f>IF(ISBLANK('ONR 4'!S9),"",'ONR 4'!S9)</f>
       </c>
       <c r="T31" s="232" t="str">
-        <f t="shared" ref="T31:T35" si="102">IF(ISBLANK('ONR 4'!T9),"",'ONR 4'!T9)</f>
+        <f>IF(ISBLANK('ONR 4'!T9),"",'ONR 4'!T9)</f>
       </c>
       <c r="U31" s="243" t="str">
-        <f t="shared" ref="U31:U35" si="103">IF(ISBLANK('ONR 4'!U9),"",'ONR 4'!U9)</f>
+        <f>IF(ISBLANK('ONR 4'!U9),"",'ONR 4'!U9)</f>
       </c>
       <c r="V31" s="235" t="str">
         <f>IF(ISBLANK('ONR 4'!G9),"",'ONR 4'!G9)</f>
@@ -34555,32 +34164,25 @@
         <v>1</v>
       </c>
       <c r="AF31" s="206" t="n">
-        <f t="shared" si="83">IF(L31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L31=TRUE,1,0)</f>
       </c>
       <c r="AG31" s="206" t="n">
-        <f t="shared" si="83">IF(M31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M31=TRUE,1,0)</f>
       </c>
       <c r="AH31" s="206" t="n">
-        <f t="shared" si="83">IF(N31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N31=TRUE,1,0)</f>
       </c>
       <c r="AI31" s="206" t="n">
-        <f t="shared" si="83">IF(O31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O31=TRUE,1,0)</f>
       </c>
       <c r="AJ31" s="206" t="n">
-        <f t="shared" si="83">IF(P31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P31=TRUE,1,0)</f>
       </c>
       <c r="AK31" s="206" t="n">
-        <f t="shared" si="83">IF(Q31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q31=TRUE,1,0)</f>
       </c>
       <c r="AL31" s="206" t="n">
-        <f t="shared" si="83">IF(R31=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R31=TRUE,1,0)</f>
       </c>
       <c r="AM31" t="n">
         <f>IF(LEN(TRIM(W31))&gt;0,1,0)</f>
@@ -34616,91 +34218,47 @@
         <f>IF(ISBLANK('ONR 4'!I10),"",'ONR 4'!I10)</f>
       </c>
       <c r="J32" s="219" t="n">
-        <f t="shared" si="92">IF(ISBLANK('ONR 4'!J10),"",'ONR 4'!J10)</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="233" t="str">
-        <f t="shared" si="93">IF(ISBLANK('ONR 5'!K8),"",'ONR 5'!K8)</f>
+        <f>IF(ISBLANK('ONR 4'!J10),"",'ONR 4'!J10)</f>
       </c>
       <c r="K32" t="str" s="233">
         <f>IF(ISBLANK('ONR 4'!K10),"",'ONR 4'!K10)</f>
-      </c>
-      <c r="L35" s="233" t="b">
-        <f t="shared" si="94">IF(ISBLANK('ONR 5'!L8),"",'ONR 5'!L8)</f>
-        <v>0</v>
       </c>
       <c r="L32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!L10),"",'ONR 4'!L10)</f>
         <v>0</v>
       </c>
-      <c r="M35" s="233" t="b">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
       <c r="M32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!M10),"",'ONR 4'!M10)</f>
         <v>0</v>
       </c>
-      <c r="N35" s="233" t="b">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
       <c r="N32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!N10),"",'ONR 4'!N10)</f>
         <v>0</v>
       </c>
-      <c r="O35" s="233" t="b">
-        <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
       <c r="O32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!O10),"",'ONR 4'!O10)</f>
         <v>0</v>
       </c>
-      <c r="P35" s="233" t="b">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
       <c r="P32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!P10),"",'ONR 4'!P10)</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="233" t="b">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="Q32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!Q10),"",'ONR 4'!Q10)</f>
         <v>0</v>
       </c>
-      <c r="R35" s="233" t="b">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
       <c r="R32" t="b" s="233">
         <f>IF(ISBLANK('ONR 4'!R10),"",'ONR 4'!R10)</f>
         <v>0</v>
       </c>
-      <c r="S35" s="234" t="str">
-        <f t="shared" si="101"/>
-      </c>
       <c r="S32" t="str" s="234">
         <f>IF(ISBLANK('ONR 4'!S10),"",'ONR 4'!S10)</f>
       </c>
-      <c r="T35" s="232" t="str">
-        <f t="shared" si="102">IF(ISBLANK('ONR 5'!T8),"",'ONR 5'!T8)</f>
-      </c>
       <c r="T32" t="str" s="232">
         <f>IF(ISBLANK('ONR 4'!T10),"",'ONR 4'!T10)</f>
       </c>
-      <c r="U35" s="243" t="str">
-        <f t="shared" si="103">IF(ISBLANK('ONR 5'!U8),"",'ONR 5'!U8)</f>
-      </c>
       <c r="U32" t="str" s="243">
         <f>IF(ISBLANK('ONR 4'!U10),"",'ONR 4'!U10)</f>
-      </c>
-      <c r="V35" s="235" t="str">
-        <f>IF(ISBLANK('ONR 5'!G8),"",'ONR 5'!G8)</f>
       </c>
       <c r="V32" t="str" s="235">
         <f>IF(ISBLANK('ONR 4'!G10),"",'ONR 4'!G10)</f>
@@ -34722,32 +34280,25 @@
         <v>1</v>
       </c>
       <c r="AF32" s="206" t="n">
-        <f t="shared" si="83">IF(L32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L32=TRUE,1,0)</f>
       </c>
       <c r="AG32" s="206" t="n">
-        <f t="shared" si="83">IF(M32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M32=TRUE,1,0)</f>
       </c>
       <c r="AH32" s="206" t="n">
-        <f t="shared" si="83">IF(N32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N32=TRUE,1,0)</f>
       </c>
       <c r="AI32" s="206" t="n">
-        <f t="shared" si="83">IF(O32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O32=TRUE,1,0)</f>
       </c>
       <c r="AJ32" s="206" t="n">
-        <f t="shared" si="83">IF(P32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P32=TRUE,1,0)</f>
       </c>
       <c r="AK32" s="206" t="n">
-        <f t="shared" si="83">IF(Q32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q32=TRUE,1,0)</f>
       </c>
       <c r="AL32" s="206" t="n">
-        <f t="shared" si="83">IF(R32=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R32=TRUE,1,0)</f>
       </c>
       <c r="AM32" t="n">
         <f>IF(LEN(TRIM(W32))&gt;0,1,0)</f>
@@ -34858,10 +34409,7 @@
         <f>IF(ISBLANK('ONR 5'!I7),"",'ONR 5'!I7)</f>
       </c>
       <c r="J34" s="220" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J7),"",'ONR 5'!J7)</f>
-      </c>
-      <c r="K37" s="227" t="str">
-        <f t="shared" ref="K37:K38" si="105">E34*10+F34</f>
+        <f>IF(ISBLANK('ONR 5'!J7),"",'ONR 5'!J7)</f>
       </c>
       <c r="K34" t="str" s="363">
         <f>IF(ISBLANK('ONR 5'!K7),"",'ONR 5'!K7)</f>
@@ -34895,16 +34443,16 @@
         <v>0</v>
       </c>
       <c r="S34" s="228" t="str">
-        <f t="shared" ref="S34:S38" si="106">IF(ISBLANK('ONR 5'!S7),"",'ONR 5'!S7)</f>
+        <f>IF(ISBLANK('ONR 5'!S7),"",'ONR 5'!S7)</f>
       </c>
       <c r="T34" s="226" t="str">
-        <f t="shared" ref="T34:T38" si="107">IF(ISBLANK('ONR 5'!T7),"",'ONR 5'!T7)</f>
+        <f>IF(ISBLANK('ONR 5'!T7),"",'ONR 5'!T7)</f>
       </c>
       <c r="U34" s="242" t="str">
-        <f t="shared" ref="U34:U38" si="108">IF(ISBLANK('ONR 5'!U7),"",'ONR 5'!U7)</f>
+        <f>IF(ISBLANK('ONR 5'!U7),"",'ONR 5'!U7)</f>
       </c>
       <c r="V34" s="229" t="str">
-        <f t="shared" ref="V34:V38" si="109">IF(ISBLANK('ONR 5'!G7),"",'ONR 5'!G7)</f>
+        <f>IF(ISBLANK('ONR 5'!G7),"",'ONR 5'!G7)</f>
       </c>
       <c r="W34" s="203" t="str">
         <f>IF(ISBLANK('ONR 5'!V7),"",'ONR 5'!V7)</f>
@@ -34913,42 +34461,34 @@
         <f>IF(ISBLANK('ONR 5'!W7),"",'ONR 5'!W7)</f>
       </c>
       <c r="Y34" s="257" t="str">
-        <f t="shared" ref="Y34:Y38" si="110">IF(ISBLANK('ONR 5'!I7),"",'ONR 5'!I7)</f>
+        <f>IF(ISBLANK('ONR 5'!I7),"",'ONR 5'!I7)</f>
       </c>
       <c r="Z34" s="256" t="str">
         <f>IF(ISBLANK('ONR 5'!D7),"",'ONR 5'!D7)</f>
       </c>
       <c r="AE34" s="206" t="n">
-        <f t="shared" ref="AE34:AE38" si="111">IF(ISNUMBER(T34),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T34),0,1)</f>
       </c>
       <c r="AF34" s="206" t="n">
-        <f t="shared" ref="AF34:AF38" si="112">IF(L34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L34=TRUE,1,0)</f>
       </c>
       <c r="AG34" s="206" t="n">
-        <f t="shared" ref="AG34:AG38" si="113">IF(M34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M34=TRUE,1,0)</f>
       </c>
       <c r="AH34" s="206" t="n">
-        <f t="shared" ref="AH34:AH38" si="114">IF(N34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N34=TRUE,1,0)</f>
       </c>
       <c r="AI34" s="206" t="n">
-        <f t="shared" ref="AI34:AI38" si="115">IF(O34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O34=TRUE,1,0)</f>
       </c>
       <c r="AJ34" s="206" t="n">
-        <f t="shared" ref="AJ34:AJ38" si="116">IF(P34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P34=TRUE,1,0)</f>
       </c>
       <c r="AK34" s="206" t="n">
-        <f t="shared" ref="AK34:AK38" si="117">IF(Q34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q34=TRUE,1,0)</f>
       </c>
       <c r="AL34" s="206" t="n">
-        <f t="shared" ref="AL34:AL38" si="118">IF(R34=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R34=TRUE,1,0)</f>
       </c>
       <c r="AM34" t="n">
         <f>IF(LEN(TRIM(W34))&gt;0,1,0)</f>
@@ -34984,53 +34524,43 @@
         <f>IF(ISBLANK('ONR 5'!I8),"",'ONR 5'!I8)</f>
       </c>
       <c r="J35" s="220" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J8),"",'ONR 5'!J8)</f>
-      </c>
-      <c r="K38" s="233" t="str">
-        <f t="shared" si="105"/>
-      </c>
-      <c r="L38" s="233" t="b">
-        <f t="shared" ref="L38:L38" si="119">OR(K35=31)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!J8),"",'ONR 5'!J8)</f>
+      </c>
+      <c r="K35" s="233" t="str">
+        <f>IF(ISBLANK('ONR 5'!K8),"",'ONR 5'!K8)</f>
+      </c>
+      <c r="L35" s="233" t="b">
+        <f>IF(ISBLANK('ONR 5'!L8),"",'ONR 5'!L8)</f>
       </c>
       <c r="M35" s="233" t="b">
-        <f t="shared" ref="M35:M38" si="120">IF(ISBLANK('ONR 5'!M8),"",'ONR 5'!M8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!M8),"",'ONR 5'!M8)</f>
       </c>
       <c r="N35" s="233" t="b">
-        <f t="shared" ref="N35:N38" si="121">IF(ISBLANK('ONR 5'!N8),"",'ONR 5'!N8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!N8),"",'ONR 5'!N8)</f>
       </c>
       <c r="O35" s="233" t="b">
-        <f t="shared" ref="O35:O38" si="122">IF(ISBLANK('ONR 5'!O8),"",'ONR 5'!O8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!O8),"",'ONR 5'!O8)</f>
       </c>
       <c r="P35" s="233" t="b">
-        <f t="shared" ref="P35:P38" si="123">IF(ISBLANK('ONR 5'!P8),"",'ONR 5'!P8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!P8),"",'ONR 5'!P8)</f>
       </c>
       <c r="Q35" s="233" t="b">
-        <f t="shared" ref="Q35:Q38" si="124">IF(ISBLANK('ONR 5'!Q8),"",'ONR 5'!Q8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!Q8),"",'ONR 5'!Q8)</f>
       </c>
       <c r="R35" s="233" t="b">
-        <f t="shared" ref="R35:R38" si="125">IF(ISBLANK('ONR 5'!R8),"",'ONR 5'!R8)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!R8),"",'ONR 5'!R8)</f>
       </c>
       <c r="S35" s="234" t="str">
-        <f t="shared" si="106">IF(ISBLANK('ONR 5'!S8),"",'ONR 5'!S8)</f>
-      </c>
-      <c r="T38" s="232" t="str">
-        <f t="shared" si="107"/>
-      </c>
-      <c r="U38" s="243" t="str">
-        <f t="shared" si="108"/>
-      </c>
-      <c r="V38" s="235" t="str">
-        <f t="shared" si="109"/>
-      </c>
-      <c r="W38" s="142" t="str">
-        <f>'ONR 5'!V8</f>
+        <f>IF(ISBLANK('ONR 5'!S8),"",'ONR 5'!S8)</f>
+      </c>
+      <c r="T35" s="232" t="str">
+        <f>IF(ISBLANK('ONR 5'!T8),"",'ONR 5'!T8)</f>
+      </c>
+      <c r="U35" s="243" t="str">
+        <f>IF(ISBLANK('ONR 5'!U8),"",'ONR 5'!U8)</f>
+      </c>
+      <c r="V35" s="235" t="str">
+        <f>IF(ISBLANK('ONR 5'!G8),"",'ONR 5'!G8)</f>
       </c>
       <c r="W35" t="str" s="203">
         <f>IF(ISBLANK('ONR 5'!V8),"",'ONR 5'!V8)</f>
@@ -35039,45 +34569,34 @@
         <f>IF(ISBLANK('ONR 5'!W8),"",'ONR 5'!W8)</f>
       </c>
       <c r="Y35" s="258" t="str">
-        <f t="shared" si="110">IF(ISBLANK('ONR 5'!I8),"",'ONR 5'!I8)</f>
-      </c>
-      <c r="Z38" s="256" t="str">
-        <f t="shared" ref="Z38:Z38" si="126">D35</f>
+        <f>IF(ISBLANK('ONR 5'!I8),"",'ONR 5'!I8)</f>
       </c>
       <c r="Z35" t="str" s="256">
         <f>IF(ISBLANK('ONR 5'!D8),"",'ONR 5'!D8)</f>
       </c>
       <c r="AE35" s="206" t="n">
-        <f t="shared" si="111">IF(ISNUMBER(T35),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T35),0,1)</f>
       </c>
       <c r="AF35" s="206" t="n">
-        <f t="shared" si="112">IF(L35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L35=TRUE,1,0)</f>
       </c>
       <c r="AG35" s="206" t="n">
-        <f t="shared" si="113">IF(M35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M35=TRUE,1,0)</f>
       </c>
       <c r="AH35" s="206" t="n">
-        <f t="shared" si="114">IF(N35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N35=TRUE,1,0)</f>
       </c>
       <c r="AI35" s="206" t="n">
-        <f t="shared" si="115">IF(O35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O35=TRUE,1,0)</f>
       </c>
       <c r="AJ35" s="206" t="n">
-        <f t="shared" si="116">IF(P35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P35=TRUE,1,0)</f>
       </c>
       <c r="AK35" s="206" t="n">
-        <f t="shared" si="117">IF(Q35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q35=TRUE,1,0)</f>
       </c>
       <c r="AL35" s="206" t="n">
-        <f t="shared" si="118">IF(R35=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R35=TRUE,1,0)</f>
       </c>
       <c r="AM35" t="n">
         <f>IF(LEN(TRIM(W35))&gt;0,1,0)</f>
@@ -35113,97 +34632,51 @@
         <f>IF(ISBLANK('ONR 5'!I9),"",'ONR 5'!I9)</f>
       </c>
       <c r="J36" s="220" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J9),"",'ONR 5'!J9)</f>
-      </c>
-      <c r="K39" s="233" t="str">
-        <f t="shared" si="105"/>
+        <f>IF(ISBLANK('ONR 5'!J9),"",'ONR 5'!J9)</f>
       </c>
       <c r="K36" t="str" s="233">
         <f>IF(ISBLANK('ONR 5'!K9),"",'ONR 5'!K9)</f>
-      </c>
-      <c r="L39" s="233" t="b">
-        <f t="shared" si="119"/>
-        <v>0</v>
       </c>
       <c r="L36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!L9),"",'ONR 5'!L9)</f>
         <v>0</v>
       </c>
-      <c r="M39" s="233" t="b">
-        <f t="shared" si="120"/>
-        <v>0</v>
-      </c>
       <c r="M36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!M9),"",'ONR 5'!M9)</f>
         <v>0</v>
       </c>
-      <c r="N39" s="233" t="b">
-        <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
       <c r="N36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!N9),"",'ONR 5'!N9)</f>
         <v>0</v>
       </c>
-      <c r="O39" s="233" t="b">
-        <f t="shared" si="122"/>
-        <v>0</v>
-      </c>
       <c r="O36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!O9),"",'ONR 5'!O9)</f>
         <v>0</v>
       </c>
-      <c r="P39" s="233" t="b">
-        <f t="shared" si="123"/>
-        <v>0</v>
-      </c>
       <c r="P36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!P9),"",'ONR 5'!P9)</f>
         <v>0</v>
       </c>
-      <c r="Q39" s="233" t="b">
-        <f t="shared" si="124"/>
-        <v>0</v>
-      </c>
       <c r="Q36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!Q9),"",'ONR 5'!Q9)</f>
         <v>0</v>
       </c>
-      <c r="R39" s="233" t="b">
-        <f t="shared" si="125"/>
-        <v>0</v>
-      </c>
       <c r="R36" t="b" s="233">
         <f>IF(ISBLANK('ONR 5'!R9),"",'ONR 5'!R9)</f>
         <v>0</v>
       </c>
-      <c r="S39" s="234" t="str">
-        <f t="shared" si="106"/>
-      </c>
       <c r="S36" t="str" s="234">
         <f>IF(ISBLANK('ONR 5'!S9),"",'ONR 5'!S9)</f>
       </c>
-      <c r="T39" s="232" t="str">
-        <f t="shared" si="107"/>
-      </c>
       <c r="T36" t="str" s="232">
         <f>IF(ISBLANK('ONR 5'!T9),"",'ONR 5'!T9)</f>
       </c>
-      <c r="U39" s="243" t="str">
-        <f t="shared" si="108"/>
-      </c>
       <c r="U36" t="str" s="243">
         <f>IF(ISBLANK('ONR 5'!U9),"",'ONR 5'!U9)</f>
       </c>
-      <c r="V39" s="235" t="str">
-        <f t="shared" si="109"/>
-      </c>
       <c r="V36" t="str" s="235">
         <f>IF(ISBLANK('ONR 5'!G9),"",'ONR 5'!G9)</f>
       </c>
-      <c r="W39" s="142" t="str">
-        <f>'ONR 5'!V9</f>
-      </c>
       <c r="W36" t="str" s="142">
         <f>IF(ISBLANK('ONR 5'!V9),"",'ONR 5'!V9)</f>
       </c>
@@ -35211,42 +34684,34 @@
         <f>IF(ISBLANK('ONR 5'!W9),"",'ONR 5'!W9)</f>
       </c>
       <c r="Y36" s="258" t="str">
-        <f t="shared" si="110">IF(ISBLANK('ONR 5'!I9),"",'ONR 5'!I9)</f>
+        <f>IF(ISBLANK('ONR 5'!I9),"",'ONR 5'!I9)</f>
       </c>
       <c r="Z36" s="256" t="str">
-        <f t="shared" si="126">IF(ISBLANK('ONR 5'!D9),"",'ONR 5'!D9)</f>
+        <f>IF(ISBLANK('ONR 5'!D9),"",'ONR 5'!D9)</f>
       </c>
       <c r="AE36" s="206" t="n">
-        <f t="shared" si="111">IF(ISNUMBER(T36),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T36),0,1)</f>
       </c>
       <c r="AF36" s="206" t="n">
-        <f t="shared" si="112">IF(L36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L36=TRUE,1,0)</f>
       </c>
       <c r="AG36" s="206" t="n">
-        <f t="shared" si="113">IF(M36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M36=TRUE,1,0)</f>
       </c>
       <c r="AH36" s="206" t="n">
-        <f t="shared" si="114">IF(N36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N36=TRUE,1,0)</f>
       </c>
       <c r="AI36" s="206" t="n">
-        <f t="shared" si="115">IF(O36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O36=TRUE,1,0)</f>
       </c>
       <c r="AJ36" s="206" t="n">
-        <f t="shared" si="116">IF(P36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P36=TRUE,1,0)</f>
       </c>
       <c r="AK36" s="206" t="n">
-        <f t="shared" si="117">IF(Q36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q36=TRUE,1,0)</f>
       </c>
       <c r="AL36" s="206" t="n">
-        <f t="shared" si="118">IF(R36=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R36=TRUE,1,0)</f>
       </c>
       <c r="AM36" t="n">
         <f>IF(LEN(TRIM(W36))&gt;0,1,0)</f>
@@ -35282,50 +34747,43 @@
         <f>IF(ISBLANK('ONR 5'!I10),"",'ONR 5'!I10)</f>
       </c>
       <c r="J37" s="220" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J10),"",'ONR 5'!J10)</f>
+        <f>IF(ISBLANK('ONR 5'!J10),"",'ONR 5'!J10)</f>
       </c>
       <c r="K37" s="233" t="str">
-        <f t="shared" ref="K37:K38" si="105">IF(ISBLANK('ONR 5'!K10),"",'ONR 5'!K10)</f>
+        <f>IF(ISBLANK('ONR 5'!K10),"",'ONR 5'!K10)</f>
       </c>
       <c r="L37" s="233" t="b">
-        <f t="shared" si="119">IF(ISBLANK('ONR 5'!L10),"",'ONR 5'!L10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!L10),"",'ONR 5'!L10)</f>
       </c>
       <c r="M37" s="233" t="b">
-        <f t="shared" si="120">IF(ISBLANK('ONR 5'!M10),"",'ONR 5'!M10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!M10),"",'ONR 5'!M10)</f>
       </c>
       <c r="N37" s="233" t="b">
-        <f t="shared" si="121">IF(ISBLANK('ONR 5'!N10),"",'ONR 5'!N10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!N10),"",'ONR 5'!N10)</f>
       </c>
       <c r="O37" s="233" t="b">
-        <f t="shared" si="122">IF(ISBLANK('ONR 5'!O10),"",'ONR 5'!O10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!O10),"",'ONR 5'!O10)</f>
       </c>
       <c r="P37" s="233" t="b">
-        <f t="shared" si="123">IF(ISBLANK('ONR 5'!P10),"",'ONR 5'!P10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!P10),"",'ONR 5'!P10)</f>
       </c>
       <c r="Q37" s="233" t="b">
-        <f t="shared" si="124">IF(ISBLANK('ONR 5'!Q10),"",'ONR 5'!Q10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!Q10),"",'ONR 5'!Q10)</f>
       </c>
       <c r="R37" s="233" t="b">
-        <f t="shared" si="125">IF(ISBLANK('ONR 5'!R10),"",'ONR 5'!R10)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!R10),"",'ONR 5'!R10)</f>
       </c>
       <c r="S37" s="234" t="str">
-        <f t="shared" si="106">IF(ISBLANK('ONR 5'!S10),"",'ONR 5'!S10)</f>
+        <f>IF(ISBLANK('ONR 5'!S10),"",'ONR 5'!S10)</f>
       </c>
       <c r="T37" s="232" t="str">
-        <f t="shared" si="107">IF(ISBLANK('ONR 5'!T10),"",'ONR 5'!T10)</f>
+        <f>IF(ISBLANK('ONR 5'!T10),"",'ONR 5'!T10)</f>
       </c>
       <c r="U37" s="243" t="str">
-        <f t="shared" si="108">IF(ISBLANK('ONR 5'!U10),"",'ONR 5'!U10)</f>
+        <f>IF(ISBLANK('ONR 5'!U10),"",'ONR 5'!U10)</f>
       </c>
       <c r="V37" s="235" t="str">
-        <f t="shared" si="109">IF(ISBLANK('ONR 5'!G10),"",'ONR 5'!G10)</f>
+        <f>IF(ISBLANK('ONR 5'!G10),"",'ONR 5'!G10)</f>
       </c>
       <c r="W37" s="142" t="str">
         <f>IF(ISBLANK('ONR 5'!V10),"",'ONR 5'!V10)</f>
@@ -35334,42 +34792,34 @@
         <f>IF(ISBLANK('ONR 5'!W10),"",'ONR 5'!W10)</f>
       </c>
       <c r="Y37" s="258" t="str">
-        <f t="shared" si="110">IF(ISBLANK('ONR 5'!I10),"",'ONR 5'!I10)</f>
+        <f>IF(ISBLANK('ONR 5'!I10),"",'ONR 5'!I10)</f>
       </c>
       <c r="Z37" s="256" t="str">
-        <f t="shared" si="126">IF(ISBLANK('ONR 5'!D10),"",'ONR 5'!D10)</f>
+        <f>IF(ISBLANK('ONR 5'!D10),"",'ONR 5'!D10)</f>
       </c>
       <c r="AE37" s="206" t="n">
-        <f t="shared" si="111">IF(ISNUMBER(T37),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T37),0,1)</f>
       </c>
       <c r="AF37" s="206" t="n">
-        <f t="shared" si="112">IF(L37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L37=TRUE,1,0)</f>
       </c>
       <c r="AG37" s="206" t="n">
-        <f t="shared" si="113">IF(M37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M37=TRUE,1,0)</f>
       </c>
       <c r="AH37" s="206" t="n">
-        <f t="shared" si="114">IF(N37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N37=TRUE,1,0)</f>
       </c>
       <c r="AI37" s="206" t="n">
-        <f t="shared" si="115">IF(O37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O37=TRUE,1,0)</f>
       </c>
       <c r="AJ37" s="206" t="n">
-        <f t="shared" si="116">IF(P37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P37=TRUE,1,0)</f>
       </c>
       <c r="AK37" s="206" t="n">
-        <f t="shared" si="117">IF(Q37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q37=TRUE,1,0)</f>
       </c>
       <c r="AL37" s="206" t="n">
-        <f t="shared" si="118">IF(R37=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R37=TRUE,1,0)</f>
       </c>
       <c r="AM37" t="n">
         <f>IF(LEN(TRIM(W37))&gt;0,1,0)</f>
@@ -35405,50 +34855,43 @@
         <f>IF(ISBLANK('ONR 5'!I11),"",'ONR 5'!I11)</f>
       </c>
       <c r="J38" s="219" t="str">
-        <f t="shared" si="84">IF(ISBLANK('ONR 5'!J11),"",'ONR 5'!J11)</f>
+        <f>IF(ISBLANK('ONR 5'!J11),"",'ONR 5'!J11)</f>
       </c>
       <c r="K38" s="233" t="str">
-        <f t="shared" si="105">IF(ISBLANK('ONR 5'!K11),"",'ONR 5'!K11)</f>
+        <f>IF(ISBLANK('ONR 5'!K11),"",'ONR 5'!K11)</f>
       </c>
       <c r="L38" s="233" t="b">
-        <f t="shared" ref="L37:L38" si="119">IF(ISBLANK('ONR 5'!L11),"",'ONR 5'!L11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!L11),"",'ONR 5'!L11)</f>
       </c>
       <c r="M38" s="233" t="b">
-        <f t="shared" si="120">IF(ISBLANK('ONR 5'!M11),"",'ONR 5'!M11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!M11),"",'ONR 5'!M11)</f>
       </c>
       <c r="N38" s="233" t="b">
-        <f t="shared" si="121">IF(ISBLANK('ONR 5'!N11),"",'ONR 5'!N11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!N11),"",'ONR 5'!N11)</f>
       </c>
       <c r="O38" s="233" t="b">
-        <f t="shared" si="122">IF(ISBLANK('ONR 5'!O11),"",'ONR 5'!O11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!O11),"",'ONR 5'!O11)</f>
       </c>
       <c r="P38" s="233" t="b">
-        <f t="shared" si="123">IF(ISBLANK('ONR 5'!P11),"",'ONR 5'!P11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!P11),"",'ONR 5'!P11)</f>
       </c>
       <c r="Q38" s="233" t="b">
-        <f t="shared" si="124">IF(ISBLANK('ONR 5'!Q11),"",'ONR 5'!Q11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!Q11),"",'ONR 5'!Q11)</f>
       </c>
       <c r="R38" s="233" t="b">
-        <f t="shared" si="125">IF(ISBLANK('ONR 5'!R11),"",'ONR 5'!R11)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!R11),"",'ONR 5'!R11)</f>
       </c>
       <c r="S38" s="234" t="str">
-        <f t="shared" si="106">IF(ISBLANK('ONR 5'!S11),"",'ONR 5'!S11)</f>
+        <f>IF(ISBLANK('ONR 5'!S11),"",'ONR 5'!S11)</f>
       </c>
       <c r="T38" s="232" t="str">
-        <f t="shared" si="107">IF(ISBLANK('ONR 5'!T11),"",'ONR 5'!T11)</f>
+        <f>IF(ISBLANK('ONR 5'!T11),"",'ONR 5'!T11)</f>
       </c>
       <c r="U38" s="243" t="str">
-        <f t="shared" si="108">IF(ISBLANK('ONR 5'!U11),"",'ONR 5'!U11)</f>
+        <f>IF(ISBLANK('ONR 5'!U11),"",'ONR 5'!U11)</f>
       </c>
       <c r="V38" s="235" t="str">
-        <f t="shared" si="109">IF(ISBLANK('ONR 5'!G11),"",'ONR 5'!G11)</f>
+        <f>IF(ISBLANK('ONR 5'!G11),"",'ONR 5'!G11)</f>
       </c>
       <c r="W38" s="142" t="str">
         <f>IF(ISBLANK('ONR 5'!V11),"",'ONR 5'!V11)</f>
@@ -35457,42 +34900,34 @@
         <f>IF(ISBLANK('ONR 5'!W11),"",'ONR 5'!W11)</f>
       </c>
       <c r="Y38" s="258" t="str">
-        <f t="shared" si="110">IF(ISBLANK('ONR 5'!I11),"",'ONR 5'!I11)</f>
+        <f>IF(ISBLANK('ONR 5'!I11),"",'ONR 5'!I11)</f>
       </c>
       <c r="Z38" s="236" t="str">
-        <f t="shared" ref="Z36:Z38" si="126">IF(ISBLANK('ONR 5'!D11),"",'ONR 5'!D11)</f>
+        <f>IF(ISBLANK('ONR 5'!D11),"",'ONR 5'!D11)</f>
       </c>
       <c r="AE38" s="206" t="n">
-        <f t="shared" si="111">IF(ISNUMBER(T38),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T38),0,1)</f>
       </c>
       <c r="AF38" s="206" t="n">
-        <f t="shared" si="112">IF(L38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L38=TRUE,1,0)</f>
       </c>
       <c r="AG38" s="206" t="n">
-        <f t="shared" si="113">IF(M38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M38=TRUE,1,0)</f>
       </c>
       <c r="AH38" s="206" t="n">
-        <f t="shared" si="114">IF(N38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N38=TRUE,1,0)</f>
       </c>
       <c r="AI38" s="206" t="n">
-        <f t="shared" si="115">IF(O38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O38=TRUE,1,0)</f>
       </c>
       <c r="AJ38" s="206" t="n">
-        <f t="shared" si="116">IF(P38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P38=TRUE,1,0)</f>
       </c>
       <c r="AK38" s="206" t="n">
-        <f t="shared" si="117">IF(Q38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q38=TRUE,1,0)</f>
       </c>
       <c r="AL38" s="206" t="n">
-        <f t="shared" si="118">IF(R38=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R38=TRUE,1,0)</f>
       </c>
       <c r="AM38" t="n">
         <f>IF(LEN(TRIM(W38))&gt;0,1,0)</f>
@@ -35527,50 +34962,43 @@
         <f>IF(ISBLANK('ONR 5'!I12),"",'ONR 5'!I12)</f>
       </c>
       <c r="J39" s="219" t="str">
-        <f t="shared" ref="J39" si="127">IF(ISBLANK('ONR 5'!J12),"",'ONR 5'!J12)</f>
+        <f>IF(ISBLANK('ONR 5'!J12),"",'ONR 5'!J12)</f>
       </c>
       <c r="K39" s="233" t="str">
-        <f t="shared" ref="K39" si="128">IF(ISBLANK('ONR 5'!K12),"",'ONR 5'!K12)</f>
+        <f>IF(ISBLANK('ONR 5'!K12),"",'ONR 5'!K12)</f>
       </c>
       <c r="L39" s="233" t="b">
-        <f t="shared" ref="L39" si="129">IF(ISBLANK('ONR 5'!L12),"",'ONR 5'!L12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!L12),"",'ONR 5'!L12)</f>
       </c>
       <c r="M39" s="233" t="b">
-        <f t="shared" ref="M39" si="130">IF(ISBLANK('ONR 5'!M12),"",'ONR 5'!M12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!M12),"",'ONR 5'!M12)</f>
       </c>
       <c r="N39" s="233" t="b">
-        <f t="shared" ref="N39" si="131">IF(ISBLANK('ONR 5'!N12),"",'ONR 5'!N12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!N12),"",'ONR 5'!N12)</f>
       </c>
       <c r="O39" s="233" t="b">
-        <f t="shared" ref="O39" si="132">IF(ISBLANK('ONR 5'!O12),"",'ONR 5'!O12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!O12),"",'ONR 5'!O12)</f>
       </c>
       <c r="P39" s="233" t="b">
-        <f t="shared" ref="P39" si="133">IF(ISBLANK('ONR 5'!P12),"",'ONR 5'!P12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!P12),"",'ONR 5'!P12)</f>
       </c>
       <c r="Q39" s="233" t="b">
-        <f t="shared" ref="Q39" si="134">IF(ISBLANK('ONR 5'!Q12),"",'ONR 5'!Q12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!Q12),"",'ONR 5'!Q12)</f>
       </c>
       <c r="R39" s="233" t="b">
-        <f t="shared" ref="R39" si="135">IF(ISBLANK('ONR 5'!R12),"",'ONR 5'!R12)</f>
-        <v>0</v>
+        <f>IF(ISBLANK('ONR 5'!R12),"",'ONR 5'!R12)</f>
       </c>
       <c r="S39" s="234" t="str">
-        <f t="shared" ref="S39" si="136">IF(ISBLANK('ONR 5'!S12),"",'ONR 5'!S12)</f>
+        <f>IF(ISBLANK('ONR 5'!S12),"",'ONR 5'!S12)</f>
       </c>
       <c r="T39" s="232" t="str">
-        <f t="shared" ref="T39" si="137">IF(ISBLANK('ONR 5'!T12),"",'ONR 5'!T12)</f>
+        <f>IF(ISBLANK('ONR 5'!T12),"",'ONR 5'!T12)</f>
       </c>
       <c r="U39" s="243" t="str">
-        <f t="shared" ref="U39" si="138">IF(ISBLANK('ONR 5'!U12),"",'ONR 5'!U12)</f>
+        <f>IF(ISBLANK('ONR 5'!U12),"",'ONR 5'!U12)</f>
       </c>
       <c r="V39" s="235" t="str">
-        <f t="shared" ref="V39" si="139">IF(ISBLANK('ONR 5'!G12),"",'ONR 5'!G12)</f>
+        <f>IF(ISBLANK('ONR 5'!G12),"",'ONR 5'!G12)</f>
       </c>
       <c r="W39" s="142" t="str">
         <f>IF(ISBLANK('ONR 5'!V12),"",'ONR 5'!V12)</f>
@@ -35579,42 +35007,34 @@
         <f>IF(ISBLANK('ONR 5'!W12),"",'ONR 5'!W12)</f>
       </c>
       <c r="Y39" s="258" t="str">
-        <f t="shared" ref="Y39" si="140">IF(ISBLANK('ONR 5'!I12),"",'ONR 5'!I12)</f>
+        <f>IF(ISBLANK('ONR 5'!I12),"",'ONR 5'!I12)</f>
       </c>
       <c r="Z39" s="236" t="str">
-        <f t="shared" ref="Z39" si="141">IF(ISBLANK('ONR 5'!D12),"",'ONR 5'!D12)</f>
+        <f>IF(ISBLANK('ONR 5'!D12),"",'ONR 5'!D12)</f>
       </c>
       <c r="AE39" s="206" t="n">
-        <f t="shared" ref="AE39" si="142">IF(ISNUMBER(T39),0,1)</f>
-        <v>1</v>
+        <f>IF(ISNUMBER(T39),0,1)</f>
       </c>
       <c r="AF39" s="206" t="n">
-        <f t="shared" ref="AF39" si="143">IF(L39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(L39=TRUE,1,0)</f>
       </c>
       <c r="AG39" s="206" t="n">
-        <f t="shared" ref="AG39" si="144">IF(M39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(M39=TRUE,1,0)</f>
       </c>
       <c r="AH39" s="206" t="n">
-        <f t="shared" ref="AH39" si="145">IF(N39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(N39=TRUE,1,0)</f>
       </c>
       <c r="AI39" s="206" t="n">
-        <f t="shared" ref="AI39" si="146">IF(O39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(O39=TRUE,1,0)</f>
       </c>
       <c r="AJ39" s="206" t="n">
-        <f t="shared" ref="AJ39" si="147">IF(P39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(P39=TRUE,1,0)</f>
       </c>
       <c r="AK39" s="206" t="n">
-        <f t="shared" ref="AK39" si="148">IF(Q39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(Q39=TRUE,1,0)</f>
       </c>
       <c r="AL39" s="206" t="n">
-        <f t="shared" ref="AL39" si="149">IF(R39=TRUE,1,0)</f>
-        <v>0</v>
+        <f>IF(R39=TRUE,1,0)</f>
       </c>
       <c r="AM39" t="n">
         <f>IF(LEN(TRIM(W39))&gt;0,1,0)</f>

--- a/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
+++ b/secteurs/collectivites/GPC-ONR_collectivites_Template.xlsx
@@ -27567,12 +27567,12 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>76199</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>24037</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
+      <xdr:rowOff>54000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4254500" cy="638175"/>
+    <xdr:ext cx="3600000" cy="540000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
@@ -30039,11 +30039,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>123824</xdr:colOff>
+      <xdr:colOff>120014</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:rowOff>54000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4254500" cy="638175"/>
+    <xdr:ext cx="3873146" cy="580972"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
@@ -30273,12 +30273,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>54002</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>117399</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4254500" cy="638175"/>
+    <xdr:ext cx="3006673" cy="451001"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
@@ -30365,12 +30365,12 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>650874</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>266699</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>483967</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>54000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4254500" cy="638175"/>
+    <xdr:ext cx="3005333" cy="450800"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
@@ -30430,9 +30430,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>7156450</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>4235425</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>55562</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
@@ -30461,12 +30461,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>54002</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>117399</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4254500" cy="638175"/>
+    <xdr:ext cx="3006673" cy="451001"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
@@ -30493,12 +30493,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>54002</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>117399</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4254500" cy="638175"/>
+    <xdr:ext cx="3006673" cy="451001"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
@@ -30525,12 +30525,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>54002</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>117399</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4254500" cy="638175"/>
+    <xdr:ext cx="3006673" cy="451001"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
@@ -30557,12 +30557,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>54002</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>117399</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4254500" cy="638175"/>
+    <xdr:ext cx="3006673" cy="451001"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
@@ -30589,12 +30589,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>54002</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>117399</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4254500" cy="638175"/>
+    <xdr:ext cx="3006673" cy="451001"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Logos INR, LaNum Pays Basque et NÉONUM"/>
@@ -30621,10 +30621,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>212725</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1273150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>2076425</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4254500" cy="638175"/>
     <xdr:pic>
@@ -42472,7 +42472,7 @@
     <col min="16132" max="16384" width="10.6640625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="6.75" customHeight="1"/>
+    <row r="1" spans="2:3" ht="59" customHeight="1"/>
     <row r="2" spans="2:3" ht="70.5" customHeight="1">
       <c r="B2" s="326" t="s">
         <v>1</v>
